--- a/compare/output/dscale_per_capita_co2_downscaled_SSP460.xlsx
+++ b/compare/output/dscale_per_capita_co2_downscaled_SSP460.xlsx
@@ -535,7 +535,7 @@
         <v>0.01965814329545048</v>
       </c>
       <c r="H2" t="n">
-        <v>0.02010435763852895</v>
+        <v>0.02010443168254664</v>
       </c>
       <c r="I2" t="n">
         <v>0.02000805106284264</v>
@@ -760,7 +760,7 @@
         <v>0.04834835897794475</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0616596921250006</v>
+        <v>0.06165982103252607</v>
       </c>
       <c r="H5" t="n">
         <v>0.07407013752544218</v>
@@ -836,13 +836,13 @@
         <v>0.06287562177656994</v>
       </c>
       <c r="G6" t="n">
-        <v>0.05874699429170867</v>
+        <v>0.05874700280646303</v>
       </c>
       <c r="H6" t="n">
-        <v>0.05542640695949975</v>
+        <v>0.05542642224838321</v>
       </c>
       <c r="I6" t="n">
-        <v>0.05303776137667358</v>
+        <v>0.05303778917253796</v>
       </c>
       <c r="J6" t="n">
         <v>0.07952505113451723</v>
@@ -909,16 +909,16 @@
         <v>0.1248885194977311</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1712113380460114</v>
+        <v>0.1712113188664332</v>
       </c>
       <c r="G7" t="n">
-        <v>0.185117040650206</v>
+        <v>0.1851170235279856</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2003801187405647</v>
+        <v>0.2003800879691942</v>
       </c>
       <c r="I7" t="n">
-        <v>0.212737796543753</v>
+        <v>0.2127376988236877</v>
       </c>
       <c r="J7" t="n">
         <v>0.1232122777658454</v>
@@ -988,13 +988,13 @@
         <v>0.06200331240482485</v>
       </c>
       <c r="G8" t="n">
-        <v>0.06409166364944574</v>
+        <v>0.06409169549346608</v>
       </c>
       <c r="H8" t="n">
         <v>0.06648119204152055</v>
       </c>
       <c r="I8" t="n">
-        <v>0.06782303654300208</v>
+        <v>0.06782306165018465</v>
       </c>
       <c r="J8" t="n">
         <v>0.08741979340540178</v>
@@ -1061,13 +1061,13 @@
         <v>0.9773722364156683</v>
       </c>
       <c r="F9" t="n">
-        <v>1.125633238739207</v>
+        <v>1.125632501450615</v>
       </c>
       <c r="G9" t="n">
         <v>0.9697236136210341</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8694054237698051</v>
+        <v>0.8694047039787172</v>
       </c>
       <c r="I9" t="n">
         <v>0.8007406333979462</v>
@@ -1140,13 +1140,13 @@
         <v>0.03445034660774311</v>
       </c>
       <c r="G10" t="n">
-        <v>0.03029902042098372</v>
+        <v>0.03029908349348493</v>
       </c>
       <c r="H10" t="n">
         <v>0.02796241871815277</v>
       </c>
       <c r="I10" t="n">
-        <v>0.02623899824660742</v>
+        <v>0.02623904889341784</v>
       </c>
       <c r="J10" t="n">
         <v>0.0801525451376352</v>
@@ -1216,13 +1216,13 @@
         <v>0.1839031973876311</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1816350305530745</v>
+        <v>0.181635014307488</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1829245655095558</v>
+        <v>0.1829245361751347</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1820760923514467</v>
+        <v>0.182076052162532</v>
       </c>
       <c r="J11" t="n">
         <v>0.1388072780275705</v>
@@ -1371,10 +1371,10 @@
         <v>0.05037439222598684</v>
       </c>
       <c r="H13" t="n">
-        <v>0.04813676749547331</v>
+        <v>0.04813679829715958</v>
       </c>
       <c r="I13" t="n">
-        <v>0.04655859929195561</v>
+        <v>0.04655863906973044</v>
       </c>
       <c r="J13" t="n">
         <v>0.09280566786333737</v>
@@ -1438,58 +1438,58 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1.16962811356355</v>
+        <v>1.169628139945211</v>
       </c>
       <c r="F14" t="n">
-        <v>1.299416338922994</v>
+        <v>1.299416388744683</v>
       </c>
       <c r="G14" t="n">
-        <v>1.367033239540226</v>
+        <v>1.367033334826146</v>
       </c>
       <c r="H14" t="n">
-        <v>1.47195235895327</v>
+        <v>1.47195249734009</v>
       </c>
       <c r="I14" t="n">
-        <v>1.579347033986298</v>
+        <v>1.579347191477136</v>
       </c>
       <c r="J14" t="n">
-        <v>1.675015479233537</v>
+        <v>1.675015700049993</v>
       </c>
       <c r="K14" t="n">
-        <v>1.765867960825349</v>
+        <v>1.765868222588836</v>
       </c>
       <c r="L14" t="n">
-        <v>1.842564304043875</v>
+        <v>1.842564608269415</v>
       </c>
       <c r="M14" t="n">
-        <v>1.927177938294051</v>
+        <v>1.927178287717229</v>
       </c>
       <c r="N14" t="n">
-        <v>2.016613451847286</v>
+        <v>2.016613850377242</v>
       </c>
       <c r="O14" t="n">
-        <v>2.078082541801604</v>
+        <v>2.078083016652806</v>
       </c>
       <c r="P14" t="n">
-        <v>2.150972631575035</v>
+        <v>2.150973165892256</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.205763605155524</v>
+        <v>2.205764204557034</v>
       </c>
       <c r="R14" t="n">
-        <v>2.241938391541001</v>
+        <v>2.241939036978083</v>
       </c>
       <c r="S14" t="n">
-        <v>2.289633473758724</v>
+        <v>2.289634195033815</v>
       </c>
       <c r="T14" t="n">
-        <v>2.355164751614319</v>
+        <v>2.355165554758361</v>
       </c>
       <c r="U14" t="n">
-        <v>2.421800636832269</v>
+        <v>2.421801528598094</v>
       </c>
       <c r="V14" t="n">
-        <v>2.49973707816961</v>
+        <v>2.499738066488265</v>
       </c>
     </row>
     <row r="15">
@@ -1514,58 +1514,58 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.7350389208816349</v>
+        <v>0.7350389094640362</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8957788623931091</v>
+        <v>0.8957788516856765</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9817285321972816</v>
+        <v>0.9817285118641682</v>
       </c>
       <c r="H15" t="n">
-        <v>1.068905528762172</v>
+        <v>1.068905509244531</v>
       </c>
       <c r="I15" t="n">
-        <v>1.140047578898923</v>
+        <v>1.14004756003712</v>
       </c>
       <c r="J15" t="n">
-        <v>1.193546685364797</v>
+        <v>1.193546648653808</v>
       </c>
       <c r="K15" t="n">
-        <v>1.243211485947679</v>
+        <v>1.24321144094569</v>
       </c>
       <c r="L15" t="n">
-        <v>1.287216971480525</v>
+        <v>1.287216926999468</v>
       </c>
       <c r="M15" t="n">
-        <v>1.339499440084629</v>
+        <v>1.339499386970127</v>
       </c>
       <c r="N15" t="n">
-        <v>1.394573202358818</v>
+        <v>1.394573131427588</v>
       </c>
       <c r="O15" t="n">
-        <v>1.428196539818359</v>
+        <v>1.428196459398891</v>
       </c>
       <c r="P15" t="n">
-        <v>1.468399263262276</v>
+        <v>1.468399172620332</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.496123412596318</v>
+        <v>1.496123310795178</v>
       </c>
       <c r="R15" t="n">
-        <v>1.511719515880422</v>
+        <v>1.511719401844718</v>
       </c>
       <c r="S15" t="n">
-        <v>1.535360628883837</v>
+        <v>1.535360511247504</v>
       </c>
       <c r="T15" t="n">
-        <v>1.570570008724856</v>
+        <v>1.570569876760769</v>
       </c>
       <c r="U15" t="n">
-        <v>1.605547872421238</v>
+        <v>1.605547724713743</v>
       </c>
       <c r="V15" t="n">
-        <v>1.646643696209764</v>
+        <v>1.646643531128865</v>
       </c>
     </row>
     <row r="16">
@@ -1593,55 +1593,55 @@
         <v>2.134738438105125</v>
       </c>
       <c r="F16" t="n">
-        <v>2.073380357341293</v>
+        <v>2.07338049335628</v>
       </c>
       <c r="G16" t="n">
-        <v>1.852903471306957</v>
+        <v>1.852903600825604</v>
       </c>
       <c r="H16" t="n">
-        <v>1.752494223231186</v>
+        <v>1.752494347965736</v>
       </c>
       <c r="I16" t="n">
-        <v>1.709593154944961</v>
+        <v>1.709593275522726</v>
       </c>
       <c r="J16" t="n">
-        <v>1.6960156309933</v>
+        <v>1.696015747935732</v>
       </c>
       <c r="K16" t="n">
-        <v>1.709583243806441</v>
+        <v>1.709583357914004</v>
       </c>
       <c r="L16" t="n">
-        <v>1.733675715333822</v>
+        <v>1.73367582768845</v>
       </c>
       <c r="M16" t="n">
-        <v>1.781173252923963</v>
+        <v>1.781173476299872</v>
       </c>
       <c r="N16" t="n">
-        <v>1.839047771184401</v>
+        <v>1.839047883206576</v>
       </c>
       <c r="O16" t="n">
-        <v>1.86898031707359</v>
+        <v>1.86898043020426</v>
       </c>
       <c r="P16" t="n">
-        <v>1.902760517701261</v>
+        <v>1.9027606325133</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.915269758940412</v>
+        <v>1.915269875927827</v>
       </c>
       <c r="R16" t="n">
-        <v>1.910454721928265</v>
+        <v>1.910454841571466</v>
       </c>
       <c r="S16" t="n">
-        <v>1.917571359182533</v>
+        <v>1.917571481963693</v>
       </c>
       <c r="T16" t="n">
-        <v>1.942974074159759</v>
+        <v>1.942974200579788</v>
       </c>
       <c r="U16" t="n">
-        <v>1.972864456284106</v>
+        <v>1.972864586891011</v>
       </c>
       <c r="V16" t="n">
-        <v>2.013698589338659</v>
+        <v>2.013698724714928</v>
       </c>
     </row>
     <row r="17">
@@ -1666,58 +1666,58 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.4937192296129715</v>
+        <v>0.4937191995802628</v>
       </c>
       <c r="F17" t="n">
-        <v>0.558802572618544</v>
+        <v>0.5588025145144121</v>
       </c>
       <c r="G17" t="n">
-        <v>0.5778635731475359</v>
+        <v>0.5778635163356808</v>
       </c>
       <c r="H17" t="n">
-        <v>0.6028929101103629</v>
+        <v>0.6028927978188497</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6224311919551173</v>
+        <v>0.6224310521510946</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6302481610920131</v>
+        <v>0.6302479647997496</v>
       </c>
       <c r="K17" t="n">
-        <v>0.6348110913327321</v>
+        <v>0.6348108650067162</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6390668220958244</v>
+        <v>0.6390665636852789</v>
       </c>
       <c r="M17" t="n">
-        <v>0.65414584340438</v>
+        <v>0.654145521130887</v>
       </c>
       <c r="N17" t="n">
-        <v>0.6781486452988572</v>
+        <v>0.6781482843019282</v>
       </c>
       <c r="O17" t="n">
-        <v>0.6973006784450806</v>
+        <v>0.697300275088909</v>
       </c>
       <c r="P17" t="n">
-        <v>0.7224915555789722</v>
+        <v>0.7224911058095432</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.7420017915138292</v>
+        <v>0.7420012910909719</v>
       </c>
       <c r="R17" t="n">
-        <v>0.7557520944626785</v>
+        <v>0.755751573926846</v>
       </c>
       <c r="S17" t="n">
-        <v>0.7747849665688166</v>
+        <v>0.7747843886433308</v>
       </c>
       <c r="T17" t="n">
-        <v>0.8027564297578591</v>
+        <v>0.8027557904767421</v>
       </c>
       <c r="U17" t="n">
-        <v>0.8348234875943572</v>
+        <v>0.8348227829618289</v>
       </c>
       <c r="V17" t="n">
-        <v>0.8734002828404812</v>
+        <v>0.8733995494598041</v>
       </c>
     </row>
     <row r="18">
@@ -1754,16 +1754,16 @@
         <v>1.048411524257268</v>
       </c>
       <c r="I18" t="n">
-        <v>1.125857722048067</v>
+        <v>1.1258576384535</v>
       </c>
       <c r="J18" t="n">
-        <v>1.223230125034408</v>
+        <v>1.223230041622528</v>
       </c>
       <c r="K18" t="n">
-        <v>1.339422068118962</v>
+        <v>1.339421984387416</v>
       </c>
       <c r="L18" t="n">
-        <v>1.462247933240866</v>
+        <v>1.462247848615659</v>
       </c>
       <c r="M18" t="n">
         <v>1.587683815293846</v>
@@ -1781,10 +1781,10 @@
         <v>1.808901075680374</v>
       </c>
       <c r="R18" t="n">
-        <v>1.802744440108593</v>
+        <v>1.802744335434081</v>
       </c>
       <c r="S18" t="n">
-        <v>1.806100027588729</v>
+        <v>1.806099917454083</v>
       </c>
       <c r="T18" t="n">
         <v>1.825635460434235</v>
@@ -1793,7 +1793,7 @@
         <v>1.848503351739571</v>
       </c>
       <c r="V18" t="n">
-        <v>1.881938639962291</v>
+        <v>1.881938510894128</v>
       </c>
     </row>
     <row r="19">
@@ -1827,7 +1827,7 @@
         <v>0.4971679979670492</v>
       </c>
       <c r="H19" t="n">
-        <v>0.4839007111391579</v>
+        <v>0.4839006814005572</v>
       </c>
       <c r="I19" t="n">
         <v>0.4752349209431538</v>
@@ -2058,7 +2058,7 @@
         <v>0.09099135288452921</v>
       </c>
       <c r="I22" t="n">
-        <v>0.09123087623883815</v>
+        <v>0.09123090244654153</v>
       </c>
       <c r="J22" t="n">
         <v>0.1310799063450954</v>
@@ -2204,7 +2204,7 @@
         <v>0.5709662563136653</v>
       </c>
       <c r="G24" t="n">
-        <v>0.5911586027299672</v>
+        <v>0.5911582511022651</v>
       </c>
       <c r="H24" t="n">
         <v>0.6004620175693746</v>
@@ -2356,13 +2356,13 @@
         <v>0.08297916895086471</v>
       </c>
       <c r="G26" t="n">
-        <v>0.07794599211147003</v>
+        <v>0.07794600672581287</v>
       </c>
       <c r="H26" t="n">
-        <v>0.07303665432283564</v>
+        <v>0.07303666716048837</v>
       </c>
       <c r="I26" t="n">
-        <v>0.0696099092217921</v>
+        <v>0.06960993202551691</v>
       </c>
       <c r="J26" t="n">
         <v>0.1342241887851385</v>
@@ -2438,7 +2438,7 @@
         <v>0.1031927009903008</v>
       </c>
       <c r="I27" t="n">
-        <v>0.09947535528886074</v>
+        <v>0.09947542996075245</v>
       </c>
       <c r="J27" t="n">
         <v>0.2143386544190419</v>
@@ -2508,13 +2508,13 @@
         <v>0.3344467998984639</v>
       </c>
       <c r="G28" t="n">
-        <v>0.3839656575460077</v>
+        <v>0.383965582888499</v>
       </c>
       <c r="H28" t="n">
-        <v>0.4555066594401084</v>
+        <v>0.4555065858998278</v>
       </c>
       <c r="I28" t="n">
-        <v>0.5521090760675476</v>
+        <v>0.5521087845372321</v>
       </c>
       <c r="J28" t="n">
         <v>0.04114317791190922</v>
@@ -2961,16 +2961,16 @@
         <v>0.01097197983063668</v>
       </c>
       <c r="F34" t="n">
-        <v>0.02194555457120173</v>
+        <v>0.02194554321472898</v>
       </c>
       <c r="G34" t="n">
-        <v>0.03735659927956921</v>
+        <v>0.03735658930958883</v>
       </c>
       <c r="H34" t="n">
-        <v>0.05397616713242633</v>
+        <v>0.05397614945094582</v>
       </c>
       <c r="I34" t="n">
-        <v>0.06697740825660692</v>
+        <v>0.06697738438116035</v>
       </c>
       <c r="J34" t="n">
         <v>0.1699417021578751</v>
@@ -3037,7 +3037,7 @@
         <v>0.300826432605834</v>
       </c>
       <c r="F35" t="n">
-        <v>0.4343410154481732</v>
+        <v>0.4343412085696497</v>
       </c>
       <c r="G35" t="n">
         <v>0.5433772150979101</v>
@@ -3046,7 +3046,7 @@
         <v>0.6245411558617041</v>
       </c>
       <c r="I35" t="n">
-        <v>0.6544691450784734</v>
+        <v>0.6544692875967485</v>
       </c>
       <c r="J35" t="n">
         <v>0.2785325557353712</v>
@@ -3195,7 +3195,7 @@
         <v>0.9384833715432271</v>
       </c>
       <c r="H37" t="n">
-        <v>0.8962227660938478</v>
+        <v>0.8962232532400091</v>
       </c>
       <c r="I37" t="n">
         <v>0.8533335361424236</v>
@@ -3268,13 +3268,13 @@
         <v>0.1685686918935093</v>
       </c>
       <c r="G38" t="n">
-        <v>0.1726094126142774</v>
+        <v>0.1726094417796973</v>
       </c>
       <c r="H38" t="n">
         <v>0.1756911608636043</v>
       </c>
       <c r="I38" t="n">
-        <v>0.1763623828631985</v>
+        <v>0.1763624066775419</v>
       </c>
       <c r="J38" t="n">
         <v>0.1244156728612241</v>
@@ -3797,7 +3797,7 @@
         <v>0.1693786652675901</v>
       </c>
       <c r="F45" t="n">
-        <v>0.2173041216602832</v>
+        <v>0.217304352196247</v>
       </c>
       <c r="G45" t="n">
         <v>0.2341146145359378</v>
@@ -3876,13 +3876,13 @@
         <v>0.0325398505954471</v>
       </c>
       <c r="G46" t="n">
-        <v>0.03359516188572894</v>
+        <v>0.03359512482228076</v>
       </c>
       <c r="H46" t="n">
         <v>0.03513839709080867</v>
       </c>
       <c r="I46" t="n">
-        <v>0.0374368017658708</v>
+        <v>0.03743677594300584</v>
       </c>
       <c r="J46" t="n">
         <v>0.06854220188218833</v>
@@ -3955,10 +3955,10 @@
         <v>0.2344612402621518</v>
       </c>
       <c r="H47" t="n">
-        <v>0.2459831167124989</v>
+        <v>0.2459831204447669</v>
       </c>
       <c r="I47" t="n">
-        <v>0.2498145769657314</v>
+        <v>0.2498145835337961</v>
       </c>
       <c r="J47" t="n">
         <v>0.2319504199322088</v>
@@ -4478,58 +4478,58 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4.662031171939856</v>
+        <v>4.662031753335446</v>
       </c>
       <c r="F54" t="n">
-        <v>5.189882857772806</v>
+        <v>5.189884097742133</v>
       </c>
       <c r="G54" t="n">
-        <v>5.166333428859724</v>
+        <v>5.166335140323656</v>
       </c>
       <c r="H54" t="n">
-        <v>5.041762257512642</v>
+        <v>5.041764363658963</v>
       </c>
       <c r="I54" t="n">
-        <v>4.878232389348597</v>
+        <v>4.87823485873154</v>
       </c>
       <c r="J54" t="n">
-        <v>4.649300979190545</v>
+        <v>4.649303723169719</v>
       </c>
       <c r="K54" t="n">
-        <v>4.460243952769239</v>
+        <v>4.460246987385101</v>
       </c>
       <c r="L54" t="n">
-        <v>4.241651905392506</v>
+        <v>4.241655161771635</v>
       </c>
       <c r="M54" t="n">
-        <v>4.110726448027466</v>
+        <v>4.110729980531345</v>
       </c>
       <c r="N54" t="n">
-        <v>4.088795070598087</v>
+        <v>4.088799016876454</v>
       </c>
       <c r="O54" t="n">
-        <v>4.118750786483915</v>
+        <v>4.118755235833258</v>
       </c>
       <c r="P54" t="n">
-        <v>4.197933336858942</v>
+        <v>4.197938436399822</v>
       </c>
       <c r="Q54" t="n">
-        <v>4.253722597569894</v>
+        <v>4.253728421236254</v>
       </c>
       <c r="R54" t="n">
-        <v>4.291256104595632</v>
+        <v>4.291262821430788</v>
       </c>
       <c r="S54" t="n">
-        <v>4.324143565775713</v>
+        <v>4.324151389626981</v>
       </c>
       <c r="T54" t="n">
-        <v>4.36382338528207</v>
+        <v>4.363832697159081</v>
       </c>
       <c r="U54" t="n">
-        <v>4.42087476617457</v>
+        <v>4.420886195923877</v>
       </c>
       <c r="V54" t="n">
-        <v>4.493836874042161</v>
+        <v>4.493851531631337</v>
       </c>
     </row>
     <row r="55">
@@ -4554,58 +4554,58 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2.15276545400769</v>
+        <v>2.15276240931155</v>
       </c>
       <c r="F55" t="n">
-        <v>2.279683671080573</v>
+        <v>2.279677023944024</v>
       </c>
       <c r="G55" t="n">
-        <v>2.19046072351096</v>
+        <v>2.190451334891844</v>
       </c>
       <c r="H55" t="n">
-        <v>2.089478188803173</v>
+        <v>2.089466376986709</v>
       </c>
       <c r="I55" t="n">
-        <v>1.99578685726562</v>
+        <v>1.9957728995917</v>
       </c>
       <c r="J55" t="n">
-        <v>1.892779023317124</v>
+        <v>1.892763152917026</v>
       </c>
       <c r="K55" t="n">
-        <v>1.817447118076609</v>
+        <v>1.817429166799639</v>
       </c>
       <c r="L55" t="n">
-        <v>1.737083250385617</v>
+        <v>1.737063557762402</v>
       </c>
       <c r="M55" t="n">
-        <v>1.695773960569979</v>
+        <v>1.69575177896474</v>
       </c>
       <c r="N55" t="n">
-        <v>1.701426135540326</v>
+        <v>1.701401073197748</v>
       </c>
       <c r="O55" t="n">
-        <v>1.729083934898784</v>
+        <v>1.729055391007265</v>
       </c>
       <c r="P55" t="n">
-        <v>1.778921572692815</v>
+        <v>1.778888399326863</v>
       </c>
       <c r="Q55" t="n">
-        <v>1.821170230721553</v>
+        <v>1.821131580925581</v>
       </c>
       <c r="R55" t="n">
-        <v>1.858464367954229</v>
+        <v>1.858419658447986</v>
       </c>
       <c r="S55" t="n">
-        <v>1.896574366288746</v>
+        <v>1.896522003191069</v>
       </c>
       <c r="T55" t="n">
-        <v>1.939433937568325</v>
+        <v>1.939371627563144</v>
       </c>
       <c r="U55" t="n">
-        <v>1.989142668788335</v>
+        <v>1.989066052278814</v>
       </c>
       <c r="V55" t="n">
-        <v>2.046620907753685</v>
+        <v>2.046522999154742</v>
       </c>
     </row>
     <row r="56">
@@ -4782,58 +4782,58 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1.080054017110908</v>
+        <v>1.080056761882804</v>
       </c>
       <c r="F58" t="n">
-        <v>1.103746577858123</v>
+        <v>1.103749182723491</v>
       </c>
       <c r="G58" t="n">
-        <v>1.175253821989006</v>
+        <v>1.175261307523211</v>
       </c>
       <c r="H58" t="n">
-        <v>1.22820746001153</v>
+        <v>1.228214696652089</v>
       </c>
       <c r="I58" t="n">
-        <v>1.251316311464058</v>
+        <v>1.251325701113378</v>
       </c>
       <c r="J58" t="n">
-        <v>1.236242707386396</v>
+        <v>1.236256515885528</v>
       </c>
       <c r="K58" t="n">
-        <v>1.194131361516857</v>
+        <v>1.194147268149468</v>
       </c>
       <c r="L58" t="n">
-        <v>1.14214703198822</v>
+        <v>1.142165099325185</v>
       </c>
       <c r="M58" t="n">
-        <v>1.114338026960701</v>
+        <v>1.114358345693896</v>
       </c>
       <c r="N58" t="n">
-        <v>1.106345226615236</v>
+        <v>1.10636791650122</v>
       </c>
       <c r="O58" t="n">
-        <v>1.107576641866151</v>
+        <v>1.107604215015418</v>
       </c>
       <c r="P58" t="n">
-        <v>1.133488446200203</v>
+        <v>1.133521249525523</v>
       </c>
       <c r="Q58" t="n">
-        <v>1.160327498316822</v>
+        <v>1.16036597095316</v>
       </c>
       <c r="R58" t="n">
-        <v>1.180936842706479</v>
+        <v>1.180981541770033</v>
       </c>
       <c r="S58" t="n">
-        <v>1.197491726718832</v>
+        <v>1.197543273641996</v>
       </c>
       <c r="T58" t="n">
-        <v>1.209368004965886</v>
+        <v>1.209429809829123</v>
       </c>
       <c r="U58" t="n">
-        <v>1.216028726970058</v>
+        <v>1.216104649854903</v>
       </c>
       <c r="V58" t="n">
-        <v>1.220285565755739</v>
+        <v>1.22038008483087</v>
       </c>
     </row>
     <row r="59">
@@ -4861,55 +4861,55 @@
         <v>0.2529728717223778</v>
       </c>
       <c r="F59" t="n">
-        <v>0.2605164940359029</v>
+        <v>0.2605138050831962</v>
       </c>
       <c r="G59" t="n">
-        <v>0.2790037775849957</v>
+        <v>0.2789987774724931</v>
       </c>
       <c r="H59" t="n">
-        <v>0.2870114386831198</v>
+        <v>0.2870090918051716</v>
       </c>
       <c r="I59" t="n">
-        <v>0.2859510963762255</v>
+        <v>0.285946652208307</v>
       </c>
       <c r="J59" t="n">
-        <v>0.2762726422638668</v>
+        <v>0.2762684110536137</v>
       </c>
       <c r="K59" t="n">
-        <v>0.2616731733846592</v>
+        <v>0.2616671080856501</v>
       </c>
       <c r="L59" t="n">
-        <v>0.2468232247660545</v>
+        <v>0.2468174100462852</v>
       </c>
       <c r="M59" t="n">
-        <v>0.239821629061557</v>
+        <v>0.2398160339882056</v>
       </c>
       <c r="N59" t="n">
-        <v>0.2396040530737369</v>
+        <v>0.2395968527295604</v>
       </c>
       <c r="O59" t="n">
-        <v>0.2426296436160123</v>
+        <v>0.2426209424101992</v>
       </c>
       <c r="P59" t="n">
-        <v>0.251272790309795</v>
+        <v>0.2512626921387421</v>
       </c>
       <c r="Q59" t="n">
-        <v>0.2595710765377077</v>
+        <v>0.2595596906285835</v>
       </c>
       <c r="R59" t="n">
-        <v>0.2657274886280817</v>
+        <v>0.2657164936794753</v>
       </c>
       <c r="S59" t="n">
-        <v>0.270592869805003</v>
+        <v>0.2705807487765337</v>
       </c>
       <c r="T59" t="n">
-        <v>0.2745059963732673</v>
+        <v>0.2744899359627632</v>
       </c>
       <c r="U59" t="n">
-        <v>0.2775123314306426</v>
+        <v>0.2774926629568179</v>
       </c>
       <c r="V59" t="n">
-        <v>0.280234459055387</v>
+        <v>0.2802115099308962</v>
       </c>
     </row>
     <row r="60">
@@ -4949,43 +4949,43 @@
         <v>0.67132123931687</v>
       </c>
       <c r="J60" t="n">
-        <v>0.6489776853651554</v>
+        <v>0.6489814521840016</v>
       </c>
       <c r="K60" t="n">
-        <v>0.6204779135447579</v>
+        <v>0.6204817876817939</v>
       </c>
       <c r="L60" t="n">
-        <v>0.5891833566652359</v>
+        <v>0.5891873678805941</v>
       </c>
       <c r="M60" t="n">
-        <v>0.5677375992519057</v>
+        <v>0.5677417738851642</v>
       </c>
       <c r="N60" t="n">
-        <v>0.5553772070626003</v>
+        <v>0.5553815688463954</v>
       </c>
       <c r="O60" t="n">
-        <v>0.5473779575476663</v>
+        <v>0.5473825331387182</v>
       </c>
       <c r="P60" t="n">
-        <v>0.554593230217872</v>
+        <v>0.5545980471967591</v>
       </c>
       <c r="Q60" t="n">
-        <v>0.5632465886592324</v>
+        <v>0.5632567679677519</v>
       </c>
       <c r="R60" t="n">
-        <v>0.5694706101451544</v>
+        <v>0.5694760082266763</v>
       </c>
       <c r="S60" t="n">
-        <v>0.5736508921288158</v>
+        <v>0.573662381231402</v>
       </c>
       <c r="T60" t="n">
-        <v>0.5753554792841383</v>
+        <v>0.5753616082373131</v>
       </c>
       <c r="U60" t="n">
-        <v>0.5745133461624056</v>
+        <v>0.5745198916074304</v>
       </c>
       <c r="V60" t="n">
-        <v>0.5720447094514775</v>
+        <v>0.5720586898928399</v>
       </c>
     </row>
     <row r="61">
@@ -5013,55 +5013,55 @@
         <v>0.5470886271818459</v>
       </c>
       <c r="F61" t="n">
-        <v>0.5529508713835732</v>
+        <v>0.5529506827234075</v>
       </c>
       <c r="G61" t="n">
-        <v>0.5549204024711656</v>
+        <v>0.5549202230944317</v>
       </c>
       <c r="H61" t="n">
-        <v>0.5436888921890712</v>
+        <v>0.5436885476224645</v>
       </c>
       <c r="I61" t="n">
-        <v>0.5229639081443674</v>
+        <v>0.5229634081463674</v>
       </c>
       <c r="J61" t="n">
-        <v>0.4954431365964562</v>
+        <v>0.495442324683155</v>
       </c>
       <c r="K61" t="n">
-        <v>0.4642531603290108</v>
+        <v>0.4642520448437811</v>
       </c>
       <c r="L61" t="n">
-        <v>0.4334247336458614</v>
+        <v>0.4334234737483824</v>
       </c>
       <c r="M61" t="n">
-        <v>0.4142004755143615</v>
+        <v>0.4141989095709989</v>
       </c>
       <c r="N61" t="n">
-        <v>0.4057619355699369</v>
+        <v>0.4057600566676917</v>
       </c>
       <c r="O61" t="n">
-        <v>0.4032591719305683</v>
+        <v>0.4032571218790331</v>
       </c>
       <c r="P61" t="n">
-        <v>0.4108331484224556</v>
+        <v>0.4108307487138762</v>
       </c>
       <c r="Q61" t="n">
-        <v>0.4186737490541806</v>
+        <v>0.4186709702370707</v>
       </c>
       <c r="R61" t="n">
-        <v>0.4236090361345503</v>
+        <v>0.4236056732012384</v>
       </c>
       <c r="S61" t="n">
-        <v>0.4262024536044765</v>
+        <v>0.4261984513277031</v>
       </c>
       <c r="T61" t="n">
-        <v>0.4265959566582372</v>
+        <v>0.4265910702040493</v>
       </c>
       <c r="U61" t="n">
-        <v>0.425399110163269</v>
+        <v>0.4253926842576463</v>
       </c>
       <c r="V61" t="n">
-        <v>0.4236737493279152</v>
+        <v>0.4236652306404904</v>
       </c>
     </row>
     <row r="62">
@@ -5086,58 +5086,58 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>0.9262199186348113</v>
+        <v>0.9262208133476846</v>
       </c>
       <c r="F62" t="n">
-        <v>1.075838007427212</v>
+        <v>1.075840634764749</v>
       </c>
       <c r="G62" t="n">
-        <v>1.201149814875187</v>
+        <v>1.201154894378652</v>
       </c>
       <c r="H62" t="n">
-        <v>1.263340970393894</v>
+        <v>1.263348847892152</v>
       </c>
       <c r="I62" t="n">
-        <v>1.271160583705016</v>
+        <v>1.271170995082098</v>
       </c>
       <c r="J62" t="n">
-        <v>1.235755004574892</v>
+        <v>1.235767499241615</v>
       </c>
       <c r="K62" t="n">
-        <v>1.173639579372236</v>
+        <v>1.173653680815869</v>
       </c>
       <c r="L62" t="n">
-        <v>1.10936316530702</v>
+        <v>1.109378804581782</v>
       </c>
       <c r="M62" t="n">
-        <v>1.075291787774097</v>
+        <v>1.075309500384669</v>
       </c>
       <c r="N62" t="n">
-        <v>1.064335062327504</v>
+        <v>1.064355364660889</v>
       </c>
       <c r="O62" t="n">
-        <v>1.061436766948886</v>
+        <v>1.06145994388606</v>
       </c>
       <c r="P62" t="n">
-        <v>1.080236481885231</v>
+        <v>1.08026372132096</v>
       </c>
       <c r="Q62" t="n">
-        <v>1.098797090495667</v>
+        <v>1.09882876562202</v>
       </c>
       <c r="R62" t="n">
-        <v>1.111182106035455</v>
+        <v>1.11121896524048</v>
       </c>
       <c r="S62" t="n">
-        <v>1.124643787440203</v>
+        <v>1.124687141102925</v>
       </c>
       <c r="T62" t="n">
-        <v>1.138431200797101</v>
+        <v>1.138483318916907</v>
       </c>
       <c r="U62" t="n">
-        <v>1.148914781333038</v>
+        <v>1.148978418594903</v>
       </c>
       <c r="V62" t="n">
-        <v>1.157276652802989</v>
+        <v>1.157357188690879</v>
       </c>
     </row>
     <row r="63">
@@ -5162,58 +5162,58 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0.8004727798346798</v>
+        <v>0.8004733526696977</v>
       </c>
       <c r="F63" t="n">
-        <v>0.8520668581293988</v>
+        <v>0.8520682261546362</v>
       </c>
       <c r="G63" t="n">
-        <v>0.8689574756324995</v>
+        <v>0.8689596748654069</v>
       </c>
       <c r="H63" t="n">
-        <v>0.8615877280438784</v>
+        <v>0.8615907284802276</v>
       </c>
       <c r="I63" t="n">
-        <v>0.8442925952987842</v>
+        <v>0.8442964675221475</v>
       </c>
       <c r="J63" t="n">
-        <v>0.8224091742217758</v>
+        <v>0.8224139208872433</v>
       </c>
       <c r="K63" t="n">
-        <v>0.7983084082524119</v>
+        <v>0.7983142170050405</v>
       </c>
       <c r="L63" t="n">
-        <v>0.7723127271879175</v>
+        <v>0.7723196406974149</v>
       </c>
       <c r="M63" t="n">
-        <v>0.7600427188647787</v>
+        <v>0.7600508790260301</v>
       </c>
       <c r="N63" t="n">
-        <v>0.7576977908145474</v>
+        <v>0.7577074487360942</v>
       </c>
       <c r="O63" t="n">
-        <v>0.7577381741551472</v>
+        <v>0.7577493388412452</v>
       </c>
       <c r="P63" t="n">
-        <v>0.771936661365203</v>
+        <v>0.7719497138729383</v>
       </c>
       <c r="Q63" t="n">
-        <v>0.7854813178722622</v>
+        <v>0.7854965948831217</v>
       </c>
       <c r="R63" t="n">
-        <v>0.7953883753762553</v>
+        <v>0.7954061654495846</v>
       </c>
       <c r="S63" t="n">
-        <v>0.8034332755427248</v>
+        <v>0.8034541078064712</v>
       </c>
       <c r="T63" t="n">
-        <v>0.8087249637117233</v>
+        <v>0.8087496478651242</v>
       </c>
       <c r="U63" t="n">
-        <v>0.8107161432884318</v>
+        <v>0.8107460303433163</v>
       </c>
       <c r="V63" t="n">
-        <v>0.810208145963487</v>
+        <v>0.8102452347653519</v>
       </c>
     </row>
     <row r="64">
@@ -5259,7 +5259,7 @@
         <v>0.3646606238390565</v>
       </c>
       <c r="L64" t="n">
-        <v>0.3462442290895479</v>
+        <v>0.3462338310526973</v>
       </c>
       <c r="M64" t="n">
         <v>0.3351278600269179</v>
@@ -5277,19 +5277,19 @@
         <v>0.3496774035577429</v>
       </c>
       <c r="R64" t="n">
-        <v>0.3558253232744865</v>
+        <v>0.3558125582404677</v>
       </c>
       <c r="S64" t="n">
         <v>0.3606301731376705</v>
       </c>
       <c r="T64" t="n">
-        <v>0.3644045381777685</v>
+        <v>0.3643906173870676</v>
       </c>
       <c r="U64" t="n">
-        <v>0.3674662014827736</v>
+        <v>0.3674516644861172</v>
       </c>
       <c r="V64" t="n">
-        <v>0.3702090195661744</v>
+        <v>0.3701938402222256</v>
       </c>
     </row>
     <row r="65">
@@ -5314,58 +5314,58 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0.3688267510290166</v>
+        <v>0.3688260706874851</v>
       </c>
       <c r="F65" t="n">
-        <v>0.3826811381927588</v>
+        <v>0.3826797615953552</v>
       </c>
       <c r="G65" t="n">
-        <v>0.3993433868691183</v>
+        <v>0.3993413155343206</v>
       </c>
       <c r="H65" t="n">
-        <v>0.4061051494315887</v>
+        <v>0.4061025240776108</v>
       </c>
       <c r="I65" t="n">
-        <v>0.4047120140726617</v>
+        <v>0.4047088916805688</v>
       </c>
       <c r="J65" t="n">
-        <v>0.3940331633213353</v>
+        <v>0.3940296268335293</v>
       </c>
       <c r="K65" t="n">
-        <v>0.3773515225247913</v>
+        <v>0.3773477088689487</v>
       </c>
       <c r="L65" t="n">
-        <v>0.3601487452112775</v>
+        <v>0.3601446337623264</v>
       </c>
       <c r="M65" t="n">
-        <v>0.3533980013402161</v>
+        <v>0.3533936271890097</v>
       </c>
       <c r="N65" t="n">
-        <v>0.3550911153803902</v>
+        <v>0.3550863914071766</v>
       </c>
       <c r="O65" t="n">
-        <v>0.3599325091893382</v>
+        <v>0.3599274497501507</v>
       </c>
       <c r="P65" t="n">
-        <v>0.3726694447039771</v>
+        <v>0.3726639384596219</v>
       </c>
       <c r="Q65" t="n">
-        <v>0.3857822901285801</v>
+        <v>0.3857762401901192</v>
       </c>
       <c r="R65" t="n">
-        <v>0.3967302854753539</v>
+        <v>0.3967236987930411</v>
       </c>
       <c r="S65" t="n">
-        <v>0.4063528771070699</v>
+        <v>0.4063456087614654</v>
       </c>
       <c r="T65" t="n">
-        <v>0.4145531601962999</v>
+        <v>0.4145450233897321</v>
       </c>
       <c r="U65" t="n">
-        <v>0.4213103256202749</v>
+        <v>0.4213010355395671</v>
       </c>
       <c r="V65" t="n">
-        <v>0.4275666007516649</v>
+        <v>0.4275555834760486</v>
       </c>
     </row>
     <row r="66">
@@ -5390,58 +5390,58 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.44234679760787</v>
+        <v>0.4423460798683762</v>
       </c>
       <c r="F66" t="n">
-        <v>0.4578206401720342</v>
+        <v>0.4578191159736427</v>
       </c>
       <c r="G66" t="n">
-        <v>0.4777098601082357</v>
+        <v>0.4777075640184766</v>
       </c>
       <c r="H66" t="n">
-        <v>0.4862183802298982</v>
+        <v>0.4862155196517108</v>
       </c>
       <c r="I66" t="n">
-        <v>0.4847199195382224</v>
+        <v>0.4847165640962547</v>
       </c>
       <c r="J66" t="n">
-        <v>0.4715644128458506</v>
+        <v>0.4715606199385872</v>
       </c>
       <c r="K66" t="n">
-        <v>0.4506263088512384</v>
+        <v>0.4506221250913771</v>
       </c>
       <c r="L66" t="n">
-        <v>0.4290072388086578</v>
+        <v>0.4290027730759535</v>
       </c>
       <c r="M66" t="n">
-        <v>0.4206672338231857</v>
+        <v>0.4206624351580372</v>
       </c>
       <c r="N66" t="n">
-        <v>0.4241698080045749</v>
+        <v>0.4241647582547015</v>
       </c>
       <c r="O66" t="n">
-        <v>0.4334610699165874</v>
+        <v>0.433455910113717</v>
       </c>
       <c r="P66" t="n">
-        <v>0.4540894309385946</v>
+        <v>0.4540841048584141</v>
       </c>
       <c r="Q66" t="n">
-        <v>0.4761369501734798</v>
+        <v>0.4761315845186862</v>
       </c>
       <c r="R66" t="n">
-        <v>0.4957117746086941</v>
+        <v>0.4957064838386675</v>
       </c>
       <c r="S66" t="n">
-        <v>0.5133509927149614</v>
+        <v>0.5133458275633153</v>
       </c>
       <c r="T66" t="n">
-        <v>0.529267543882706</v>
+        <v>0.5292625497442475</v>
       </c>
       <c r="U66" t="n">
-        <v>0.543542181275103</v>
+        <v>0.5435375014751543</v>
       </c>
       <c r="V66" t="n">
-        <v>0.5573753575847369</v>
+        <v>0.5573711217324833</v>
       </c>
     </row>
     <row r="67">
@@ -5466,58 +5466,58 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>0.1156310732633292</v>
+        <v>0.1156290017626588</v>
       </c>
       <c r="F67" t="n">
-        <v>0.1272476332267187</v>
+        <v>0.1272436262742109</v>
       </c>
       <c r="G67" t="n">
-        <v>0.144128249422969</v>
+        <v>0.1441221553662824</v>
       </c>
       <c r="H67" t="n">
-        <v>0.1584425019333974</v>
+        <v>0.1584345824790963</v>
       </c>
       <c r="I67" t="n">
-        <v>0.1692526703665081</v>
+        <v>0.1692432679411486</v>
       </c>
       <c r="J67" t="n">
-        <v>0.1755913624558113</v>
+        <v>0.1755807661784864</v>
       </c>
       <c r="K67" t="n">
-        <v>0.177382868647758</v>
+        <v>0.1773714805478844</v>
       </c>
       <c r="L67" t="n">
-        <v>0.1770195441246939</v>
+        <v>0.1770073686526452</v>
       </c>
       <c r="M67" t="n">
-        <v>0.1807093939578005</v>
+        <v>0.1806963379699545</v>
       </c>
       <c r="N67" t="n">
-        <v>0.1886962486171729</v>
+        <v>0.1886819387648396</v>
       </c>
       <c r="O67" t="n">
-        <v>0.1988510903833369</v>
+        <v>0.1988355241602736</v>
       </c>
       <c r="P67" t="n">
-        <v>0.2142113067717563</v>
+        <v>0.2141940234770357</v>
       </c>
       <c r="Q67" t="n">
-        <v>0.2307543448153657</v>
+        <v>0.2307352262288355</v>
       </c>
       <c r="R67" t="n">
-        <v>0.2467010080042545</v>
+        <v>0.2466799598038757</v>
       </c>
       <c r="S67" t="n">
-        <v>0.2625684277946251</v>
+        <v>0.2625450956812715</v>
       </c>
       <c r="T67" t="n">
-        <v>0.278377270413483</v>
+        <v>0.278351171101391</v>
       </c>
       <c r="U67" t="n">
-        <v>0.2938225727363981</v>
+        <v>0.2937928569044703</v>
       </c>
       <c r="V67" t="n">
-        <v>0.3092377439172432</v>
+        <v>0.3092029144861198</v>
       </c>
     </row>
     <row r="68">
@@ -5542,58 +5542,58 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.8947909256754688</v>
+        <v>0.8947916460314687</v>
       </c>
       <c r="F68" t="n">
-        <v>1.048636861271501</v>
+        <v>1.048639004430982</v>
       </c>
       <c r="G68" t="n">
-        <v>1.287108056763324</v>
+        <v>1.287113416243297</v>
       </c>
       <c r="H68" t="n">
-        <v>1.485570921613627</v>
+        <v>1.485580659902523</v>
       </c>
       <c r="I68" t="n">
-        <v>1.597053976004071</v>
+        <v>1.597068263220346</v>
       </c>
       <c r="J68" t="n">
-        <v>1.611397194671471</v>
+        <v>1.611415538960837</v>
       </c>
       <c r="K68" t="n">
-        <v>1.561673850256696</v>
+        <v>1.561695406800859</v>
       </c>
       <c r="L68" t="n">
-        <v>1.492030861236012</v>
+        <v>1.492055168324596</v>
       </c>
       <c r="M68" t="n">
-        <v>1.455259033200492</v>
+        <v>1.455286829578333</v>
       </c>
       <c r="N68" t="n">
-        <v>1.446576011880918</v>
+        <v>1.446607693172334</v>
       </c>
       <c r="O68" t="n">
-        <v>1.447016579604815</v>
+        <v>1.447053372700432</v>
       </c>
       <c r="P68" t="n">
-        <v>1.479527566544445</v>
+        <v>1.479570843617583</v>
       </c>
       <c r="Q68" t="n">
-        <v>1.514238009468097</v>
+        <v>1.514288816806669</v>
       </c>
       <c r="R68" t="n">
-        <v>1.540948603429572</v>
+        <v>1.54100814642144</v>
       </c>
       <c r="S68" t="n">
-        <v>1.563496397641933</v>
+        <v>1.563566650073189</v>
       </c>
       <c r="T68" t="n">
-        <v>1.583788491971291</v>
+        <v>1.58387287693782</v>
       </c>
       <c r="U68" t="n">
-        <v>1.602385169513485</v>
+        <v>1.602488209811997</v>
       </c>
       <c r="V68" t="n">
-        <v>1.621078872787964</v>
+        <v>1.621210180464379</v>
       </c>
     </row>
     <row r="69">
@@ -5624,19 +5624,19 @@
         <v>0.3606356192209221</v>
       </c>
       <c r="G69" t="n">
-        <v>0.373024322753527</v>
+        <v>0.3730191794349551</v>
       </c>
       <c r="H69" t="n">
-        <v>0.3751811036341883</v>
+        <v>0.3751760554492632</v>
       </c>
       <c r="I69" t="n">
         <v>0.3704019676809404</v>
       </c>
       <c r="J69" t="n">
-        <v>0.3621996436176285</v>
+        <v>0.3621946800748502</v>
       </c>
       <c r="K69" t="n">
-        <v>0.3511218076219269</v>
+        <v>0.3511168350704113</v>
       </c>
       <c r="L69" t="n">
         <v>0.338327379279894</v>
@@ -5645,31 +5645,31 @@
         <v>0.3308042333973676</v>
       </c>
       <c r="N69" t="n">
-        <v>0.327646081836026</v>
+        <v>0.3276408753195499</v>
       </c>
       <c r="O69" t="n">
-        <v>0.3260243466344043</v>
+        <v>0.3260189933726619</v>
       </c>
       <c r="P69" t="n">
-        <v>0.3310982159666006</v>
+        <v>0.3310926789293585</v>
       </c>
       <c r="Q69" t="n">
-        <v>0.3351919587569482</v>
+        <v>0.3351861985541891</v>
       </c>
       <c r="R69" t="n">
-        <v>0.336571879461032</v>
+        <v>0.3365658561266346</v>
       </c>
       <c r="S69" t="n">
-        <v>0.336456343231651</v>
+        <v>0.3364500170806078</v>
       </c>
       <c r="T69" t="n">
-        <v>0.3352621965040467</v>
+        <v>0.3352488633484887</v>
       </c>
       <c r="U69" t="n">
-        <v>0.3333802896264157</v>
+        <v>0.3333732461824534</v>
       </c>
       <c r="V69" t="n">
-        <v>0.3313594904800614</v>
+        <v>0.3313520326355276</v>
       </c>
     </row>
     <row r="70">
@@ -5694,58 +5694,58 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0.3168303817517583</v>
+        <v>0.3168290673210341</v>
       </c>
       <c r="F70" t="n">
-        <v>0.3336497276487628</v>
+        <v>0.3336470432185371</v>
       </c>
       <c r="G70" t="n">
-        <v>0.3569175558381779</v>
+        <v>0.3569137135414066</v>
       </c>
       <c r="H70" t="n">
-        <v>0.3714460687301878</v>
+        <v>0.3714410738257471</v>
       </c>
       <c r="I70" t="n">
-        <v>0.3780675362827519</v>
+        <v>0.378061526219502</v>
       </c>
       <c r="J70" t="n">
-        <v>0.3768176743028278</v>
+        <v>0.3768109101644257</v>
       </c>
       <c r="K70" t="n">
-        <v>0.3704487511203814</v>
+        <v>0.370441629169088</v>
       </c>
       <c r="L70" t="n">
-        <v>0.364340197899396</v>
+        <v>0.3643328126750144</v>
       </c>
       <c r="M70" t="n">
-        <v>0.3681758864472783</v>
+        <v>0.3681683459252197</v>
       </c>
       <c r="N70" t="n">
-        <v>0.3794917618651135</v>
+        <v>0.3794838613560628</v>
       </c>
       <c r="O70" t="n">
-        <v>0.3931754772387454</v>
+        <v>0.3931671899015149</v>
       </c>
       <c r="P70" t="n">
-        <v>0.4161451146060296</v>
+        <v>0.4161364087948494</v>
       </c>
       <c r="Q70" t="n">
-        <v>0.4408117652301984</v>
+        <v>0.4408027813952882</v>
       </c>
       <c r="R70" t="n">
-        <v>0.4646212915324501</v>
+        <v>0.464612182839879</v>
       </c>
       <c r="S70" t="n">
-        <v>0.4882820908068574</v>
+        <v>0.4882728389812267</v>
       </c>
       <c r="T70" t="n">
-        <v>0.5114563166955013</v>
+        <v>0.5114472966684922</v>
       </c>
       <c r="U70" t="n">
-        <v>0.5338946406572517</v>
+        <v>0.5338862781571497</v>
       </c>
       <c r="V70" t="n">
-        <v>0.5556904202724395</v>
+        <v>0.5556825620133455</v>
       </c>
     </row>
     <row r="71">
@@ -5770,58 +5770,58 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0.9929841256500834</v>
+        <v>0.992985189507599</v>
       </c>
       <c r="F71" t="n">
-        <v>1.126938515853549</v>
+        <v>1.12694127521745</v>
       </c>
       <c r="G71" t="n">
-        <v>1.188134181956898</v>
+        <v>1.18813895629996</v>
       </c>
       <c r="H71" t="n">
-        <v>1.179677233945159</v>
+        <v>1.179683658520076</v>
       </c>
       <c r="I71" t="n">
-        <v>1.132918413222905</v>
+        <v>1.132926416111059</v>
       </c>
       <c r="J71" t="n">
-        <v>1.071317391457296</v>
+        <v>1.071326294540933</v>
       </c>
       <c r="K71" t="n">
-        <v>1.01070769365004</v>
+        <v>1.010717744810447</v>
       </c>
       <c r="L71" t="n">
-        <v>0.9654426270429848</v>
+        <v>0.9654543015443031</v>
       </c>
       <c r="M71" t="n">
-        <v>0.9486427545520631</v>
+        <v>0.9486563302944174</v>
       </c>
       <c r="N71" t="n">
-        <v>0.9481190607687074</v>
+        <v>0.9481348464553988</v>
       </c>
       <c r="O71" t="n">
-        <v>0.9472674847709089</v>
+        <v>0.9472856178534876</v>
       </c>
       <c r="P71" t="n">
-        <v>0.9596324940677708</v>
+        <v>0.9596535903445856</v>
       </c>
       <c r="Q71" t="n">
-        <v>0.9671075071885954</v>
+        <v>0.967131581670994</v>
       </c>
       <c r="R71" t="n">
-        <v>0.9682630482768235</v>
+        <v>0.9682903765723324</v>
       </c>
       <c r="S71" t="n">
-        <v>0.9668161185698622</v>
+        <v>0.9668475073032715</v>
       </c>
       <c r="T71" t="n">
-        <v>0.9622411371405766</v>
+        <v>0.962277509854265</v>
       </c>
       <c r="U71" t="n">
-        <v>0.9541659792027639</v>
+        <v>0.9542086583497847</v>
       </c>
       <c r="V71" t="n">
-        <v>0.9439164180636622</v>
+        <v>0.9439685639487375</v>
       </c>
     </row>
     <row r="72">
@@ -5846,58 +5846,58 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>0.4062645990602465</v>
+        <v>0.406263962155096</v>
       </c>
       <c r="F72" t="n">
-        <v>0.4085769558078691</v>
+        <v>0.4085755321942315</v>
       </c>
       <c r="G72" t="n">
-        <v>0.4201203081575137</v>
+        <v>0.4201182416079409</v>
       </c>
       <c r="H72" t="n">
-        <v>0.4262017417585218</v>
+        <v>0.4261993221117644</v>
       </c>
       <c r="I72" t="n">
-        <v>0.4288987803162606</v>
+        <v>0.4288958189205219</v>
       </c>
       <c r="J72" t="n">
-        <v>0.4263354292349959</v>
+        <v>0.4263323946283417</v>
       </c>
       <c r="K72" t="n">
-        <v>0.4192317483537043</v>
+        <v>0.419228622640651</v>
       </c>
       <c r="L72" t="n">
-        <v>0.4113973851263779</v>
+        <v>0.4113945081612309</v>
       </c>
       <c r="M72" t="n">
-        <v>0.4127292117412052</v>
+        <v>0.4127265942083721</v>
       </c>
       <c r="N72" t="n">
-        <v>0.4198727816790936</v>
+        <v>0.4198702436382541</v>
       </c>
       <c r="O72" t="n">
-        <v>0.4271525642878826</v>
+        <v>0.4271503216458383</v>
       </c>
       <c r="P72" t="n">
-        <v>0.4442195141121419</v>
+        <v>0.444217171087847</v>
       </c>
       <c r="Q72" t="n">
-        <v>0.4634041445272645</v>
+        <v>0.4634021400376533</v>
       </c>
       <c r="R72" t="n">
-        <v>0.4812403438318473</v>
+        <v>0.4812387121317369</v>
       </c>
       <c r="S72" t="n">
-        <v>0.497517455713857</v>
+        <v>0.4975164788630238</v>
       </c>
       <c r="T72" t="n">
         <v>0.5118407352226405</v>
       </c>
       <c r="U72" t="n">
-        <v>0.5241616558446878</v>
+        <v>0.5241627301198005</v>
       </c>
       <c r="V72" t="n">
-        <v>0.5345952488178338</v>
+        <v>0.5345977820310741</v>
       </c>
     </row>
     <row r="73">
@@ -5922,58 +5922,58 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>9.502461409419469</v>
+        <v>9.50248278413819</v>
       </c>
       <c r="F73" t="n">
-        <v>7.962996783383881</v>
+        <v>7.963032809484422</v>
       </c>
       <c r="G73" t="n">
-        <v>6.228574792723783</v>
+        <v>6.228617743851325</v>
       </c>
       <c r="H73" t="n">
-        <v>5.070962241462603</v>
+        <v>5.071009648450845</v>
       </c>
       <c r="I73" t="n">
-        <v>4.49574675949075</v>
+        <v>4.495799838455325</v>
       </c>
       <c r="J73" t="n">
-        <v>4.220975600871403</v>
+        <v>4.221035785019057</v>
       </c>
       <c r="K73" t="n">
-        <v>4.053304049096289</v>
+        <v>4.053373890851306</v>
       </c>
       <c r="L73" t="n">
-        <v>3.898685958193095</v>
+        <v>3.89876505001268</v>
       </c>
       <c r="M73" t="n">
-        <v>3.819070771723205</v>
+        <v>3.819160474318328</v>
       </c>
       <c r="N73" t="n">
-        <v>3.799575460094402</v>
+        <v>3.799678279854246</v>
       </c>
       <c r="O73" t="n">
-        <v>3.809727919374414</v>
+        <v>3.809846727402149</v>
       </c>
       <c r="P73" t="n">
-        <v>3.915095850851861</v>
+        <v>3.915236291660449</v>
       </c>
       <c r="Q73" t="n">
-        <v>4.032843313862491</v>
+        <v>4.033009869295329</v>
       </c>
       <c r="R73" t="n">
-        <v>4.12827877799097</v>
+        <v>4.128474097223021</v>
       </c>
       <c r="S73" t="n">
-        <v>4.204871753062809</v>
+        <v>4.205103899226455</v>
       </c>
       <c r="T73" t="n">
-        <v>4.259025215413124</v>
+        <v>4.259301913403998</v>
       </c>
       <c r="U73" t="n">
-        <v>4.293191455627084</v>
+        <v>4.293529593538816</v>
       </c>
       <c r="V73" t="n">
-        <v>4.323399345942954</v>
+        <v>4.323824763131911</v>
       </c>
     </row>
     <row r="74">
@@ -6004,7 +6004,7 @@
         <v>0.3702894243518815</v>
       </c>
       <c r="G74" t="n">
-        <v>0.4091318824849611</v>
+        <v>0.4091226843760923</v>
       </c>
       <c r="H74" t="n">
         <v>0.4181460852070565</v>
@@ -6013,7 +6013,7 @@
         <v>0.4120557293147569</v>
       </c>
       <c r="J74" t="n">
-        <v>0.3988447709409496</v>
+        <v>0.3988350794219979</v>
       </c>
       <c r="K74" t="n">
         <v>0.3816145999362449</v>
@@ -6022,7 +6022,7 @@
         <v>0.3634642103638141</v>
       </c>
       <c r="M74" t="n">
-        <v>0.3535922806792831</v>
+        <v>0.3535816068397963</v>
       </c>
       <c r="N74" t="n">
         <v>0.3499527961348364</v>
@@ -6049,7 +6049,7 @@
         <v>0.3604455522667083</v>
       </c>
       <c r="V74" t="n">
-        <v>0.3593403524909249</v>
+        <v>0.3593239270051412</v>
       </c>
     </row>
     <row r="75">
@@ -6074,58 +6074,58 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>0.584952657547895</v>
+        <v>0.5849520054929113</v>
       </c>
       <c r="F75" t="n">
-        <v>0.6415542100714762</v>
+        <v>0.6415532140724045</v>
       </c>
       <c r="G75" t="n">
-        <v>0.7339759904763269</v>
+        <v>0.7339746276152452</v>
       </c>
       <c r="H75" t="n">
-        <v>0.7628333099185165</v>
+        <v>0.7628315538072492</v>
       </c>
       <c r="I75" t="n">
-        <v>0.77390819462507</v>
+        <v>0.7739060150102806</v>
       </c>
       <c r="J75" t="n">
-        <v>0.7763641452836967</v>
+        <v>0.7763615010971485</v>
       </c>
       <c r="K75" t="n">
-        <v>0.7712773171243789</v>
+        <v>0.7712745493818642</v>
       </c>
       <c r="L75" t="n">
-        <v>0.7608778219035689</v>
+        <v>0.7608744902582693</v>
       </c>
       <c r="M75" t="n">
-        <v>0.7572248683715062</v>
+        <v>0.7572209046527452</v>
       </c>
       <c r="N75" t="n">
-        <v>0.7633380140346322</v>
+        <v>0.7633338112100538</v>
       </c>
       <c r="O75" t="n">
-        <v>0.7609372204266193</v>
+        <v>0.7609327596435933</v>
       </c>
       <c r="P75" t="n">
-        <v>0.7735299687154999</v>
+        <v>0.7735252214468936</v>
       </c>
       <c r="Q75" t="n">
-        <v>0.7785486374174555</v>
+        <v>0.7785430020208532</v>
       </c>
       <c r="R75" t="n">
-        <v>0.7693243988525237</v>
+        <v>0.7693189622938412</v>
       </c>
       <c r="S75" t="n">
-        <v>0.7616695590840815</v>
+        <v>0.7616637245476451</v>
       </c>
       <c r="T75" t="n">
-        <v>0.7553839580662978</v>
+        <v>0.7553777055262034</v>
       </c>
       <c r="U75" t="n">
-        <v>0.7545360582848961</v>
+        <v>0.7545293755995853</v>
       </c>
       <c r="V75" t="n">
-        <v>0.7577198879640522</v>
+        <v>0.7577127630097706</v>
       </c>
     </row>
     <row r="76">
@@ -6150,58 +6150,58 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1.141537694570931</v>
+        <v>1.141537280510388</v>
       </c>
       <c r="F76" t="n">
-        <v>1.221144273640116</v>
+        <v>1.221143474970699</v>
       </c>
       <c r="G76" t="n">
-        <v>1.087647310843487</v>
+        <v>1.087646137051905</v>
       </c>
       <c r="H76" t="n">
-        <v>0.9202927413959532</v>
+        <v>0.9202910954759469</v>
       </c>
       <c r="I76" t="n">
-        <v>0.8241018311539843</v>
+        <v>0.8240998086307806</v>
       </c>
       <c r="J76" t="n">
-        <v>0.7846286251787772</v>
+        <v>0.7846262157817434</v>
       </c>
       <c r="K76" t="n">
-        <v>0.7696514437104642</v>
+        <v>0.7696486232036288</v>
       </c>
       <c r="L76" t="n">
-        <v>0.764184224826266</v>
+        <v>0.7641809584988355</v>
       </c>
       <c r="M76" t="n">
-        <v>0.7609031985027331</v>
+        <v>0.7608994470215318</v>
       </c>
       <c r="N76" t="n">
-        <v>0.7631855309705153</v>
+        <v>0.7631812534767679</v>
       </c>
       <c r="O76" t="n">
-        <v>0.7445830896491595</v>
+        <v>0.7445783418541867</v>
       </c>
       <c r="P76" t="n">
-        <v>0.7317784217269855</v>
+        <v>0.7317731434547908</v>
       </c>
       <c r="Q76" t="n">
-        <v>0.7043370301644764</v>
+        <v>0.7043311483609648</v>
       </c>
       <c r="R76" t="n">
-        <v>0.6612647184153206</v>
+        <v>0.6612585265975107</v>
       </c>
       <c r="S76" t="n">
-        <v>0.624457871554094</v>
+        <v>0.6244512066429562</v>
       </c>
       <c r="T76" t="n">
-        <v>0.5973328615014137</v>
+        <v>0.5973258226671992</v>
       </c>
       <c r="U76" t="n">
-        <v>0.5830762052255203</v>
+        <v>0.5830686158049975</v>
       </c>
       <c r="V76" t="n">
-        <v>0.5776530621410967</v>
+        <v>0.5776448537686187</v>
       </c>
     </row>
     <row r="77">
@@ -6226,58 +6226,58 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>0.8015631541034798</v>
+        <v>0.8015626826775484</v>
       </c>
       <c r="F77" t="n">
-        <v>1.015475448132199</v>
+        <v>1.015474715670625</v>
       </c>
       <c r="G77" t="n">
-        <v>1.239326270937236</v>
+        <v>1.239325507141364</v>
       </c>
       <c r="H77" t="n">
-        <v>1.273219108865656</v>
+        <v>1.27321804202858</v>
       </c>
       <c r="I77" t="n">
-        <v>1.21718047588436</v>
+        <v>1.217179075960963</v>
       </c>
       <c r="J77" t="n">
-        <v>1.140570462421861</v>
+        <v>1.140568691990717</v>
       </c>
       <c r="K77" t="n">
-        <v>1.078255328954012</v>
+        <v>1.078252827794881</v>
       </c>
       <c r="L77" t="n">
-        <v>1.042487084588247</v>
+        <v>1.042484420758559</v>
       </c>
       <c r="M77" t="n">
-        <v>1.039494867019242</v>
+        <v>1.039491665021196</v>
       </c>
       <c r="N77" t="n">
-        <v>1.058802742889173</v>
+        <v>1.058799315800857</v>
       </c>
       <c r="O77" t="n">
-        <v>1.06284504833733</v>
+        <v>1.062841380861645</v>
       </c>
       <c r="P77" t="n">
-        <v>1.082190029955414</v>
+        <v>1.082185667728287</v>
       </c>
       <c r="Q77" t="n">
-        <v>1.08869612687955</v>
+        <v>1.088691920369836</v>
       </c>
       <c r="R77" t="n">
-        <v>1.076583341225424</v>
+        <v>1.076578831459526</v>
       </c>
       <c r="S77" t="n">
-        <v>1.068975697631601</v>
+        <v>1.068970329789484</v>
       </c>
       <c r="T77" t="n">
-        <v>1.064989642890537</v>
+        <v>1.064984480110965</v>
       </c>
       <c r="U77" t="n">
-        <v>1.068866756919466</v>
+        <v>1.068861256184507</v>
       </c>
       <c r="V77" t="n">
-        <v>1.077350658397492</v>
+        <v>1.077344810018663</v>
       </c>
     </row>
     <row r="78">
@@ -6302,58 +6302,58 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>3.914028954450463</v>
+        <v>3.914030147611976</v>
       </c>
       <c r="F78" t="n">
-        <v>3.535592369015253</v>
+        <v>3.535593693838993</v>
       </c>
       <c r="G78" t="n">
-        <v>3.264203395473265</v>
+        <v>3.264204463974905</v>
       </c>
       <c r="H78" t="n">
-        <v>2.932854917359813</v>
+        <v>2.932855692959878</v>
       </c>
       <c r="I78" t="n">
-        <v>2.742326705006203</v>
+        <v>2.742327252922586</v>
       </c>
       <c r="J78" t="n">
-        <v>2.64502948314328</v>
+        <v>2.645029972760938</v>
       </c>
       <c r="K78" t="n">
-        <v>2.591961656847702</v>
+        <v>2.591962146029447</v>
       </c>
       <c r="L78" t="n">
-        <v>2.552655336385281</v>
+        <v>2.552655828752495</v>
       </c>
       <c r="M78" t="n">
-        <v>2.549255641130176</v>
+        <v>2.549256250443137</v>
       </c>
       <c r="N78" t="n">
-        <v>2.579850603257126</v>
+        <v>2.579851279617541</v>
       </c>
       <c r="O78" t="n">
-        <v>2.577160133451747</v>
+        <v>2.577160940294232</v>
       </c>
       <c r="P78" t="n">
-        <v>2.615336179485205</v>
+        <v>2.61533706767407</v>
       </c>
       <c r="Q78" t="n">
-        <v>2.621914712753336</v>
+        <v>2.621915630083538</v>
       </c>
       <c r="R78" t="n">
-        <v>2.581105064987015</v>
+        <v>2.581106017410298</v>
       </c>
       <c r="S78" t="n">
-        <v>2.550694935592305</v>
+        <v>2.550696061369422</v>
       </c>
       <c r="T78" t="n">
-        <v>2.531270188477791</v>
+        <v>2.531271436445511</v>
       </c>
       <c r="U78" t="n">
-        <v>2.534063678693699</v>
+        <v>2.53406506298145</v>
       </c>
       <c r="V78" t="n">
-        <v>2.550434218993996</v>
+        <v>2.550435833619737</v>
       </c>
     </row>
     <row r="79">
@@ -6378,58 +6378,58 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>0.5915795294094415</v>
+        <v>0.5915788113068838</v>
       </c>
       <c r="F79" t="n">
-        <v>0.807958067813567</v>
+        <v>0.807957197851193</v>
       </c>
       <c r="G79" t="n">
-        <v>1.156106718962466</v>
+        <v>1.156105864828114</v>
       </c>
       <c r="H79" t="n">
-        <v>1.421037141739681</v>
+        <v>1.421036295543746</v>
       </c>
       <c r="I79" t="n">
-        <v>1.60319208347919</v>
+        <v>1.603191240377682</v>
       </c>
       <c r="J79" t="n">
-        <v>1.702173271768047</v>
+        <v>1.702172256323301</v>
       </c>
       <c r="K79" t="n">
-        <v>1.737485083504124</v>
+        <v>1.737483884876244</v>
       </c>
       <c r="L79" t="n">
-        <v>1.733826072760257</v>
+        <v>1.733824850515045</v>
       </c>
       <c r="M79" t="n">
-        <v>1.733012676656723</v>
+        <v>1.733011423438862</v>
       </c>
       <c r="N79" t="n">
-        <v>1.750209777155697</v>
+        <v>1.750208301475551</v>
       </c>
       <c r="O79" t="n">
-        <v>1.747000818387546</v>
+        <v>1.746999102690384</v>
       </c>
       <c r="P79" t="n">
-        <v>1.779410202958418</v>
+        <v>1.779408225326621</v>
       </c>
       <c r="Q79" t="n">
-        <v>1.795575861533321</v>
+        <v>1.795573801360621</v>
       </c>
       <c r="R79" t="n">
-        <v>1.779233265724451</v>
+        <v>1.779231111431861</v>
       </c>
       <c r="S79" t="n">
-        <v>1.766867611569384</v>
+        <v>1.766865578095236</v>
       </c>
       <c r="T79" t="n">
-        <v>1.758524359996162</v>
+        <v>1.758522222612757</v>
       </c>
       <c r="U79" t="n">
-        <v>1.762645956229258</v>
+        <v>1.762643706036866</v>
       </c>
       <c r="V79" t="n">
-        <v>1.774243145361707</v>
+        <v>1.774240772260024</v>
       </c>
     </row>
     <row r="80">
@@ -6454,58 +6454,58 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1.954322083520736</v>
+        <v>1.95432242296693</v>
       </c>
       <c r="F80" t="n">
-        <v>1.700482630356346</v>
+        <v>1.700482308752857</v>
       </c>
       <c r="G80" t="n">
-        <v>1.578902558822009</v>
+        <v>1.578902249228415</v>
       </c>
       <c r="H80" t="n">
-        <v>1.473125336930482</v>
+        <v>1.473124732570873</v>
       </c>
       <c r="I80" t="n">
-        <v>1.443769552096258</v>
+        <v>1.443768661171044</v>
       </c>
       <c r="J80" t="n">
-        <v>1.456305107737257</v>
+        <v>1.456304228416936</v>
       </c>
       <c r="K80" t="n">
-        <v>1.487161923570354</v>
+        <v>1.487161050241723</v>
       </c>
       <c r="L80" t="n">
-        <v>1.521506681166252</v>
+        <v>1.521505514354123</v>
       </c>
       <c r="M80" t="n">
-        <v>1.574576156731701</v>
+        <v>1.574574977198142</v>
       </c>
       <c r="N80" t="n">
-        <v>1.648819565603987</v>
+        <v>1.648818364021744</v>
       </c>
       <c r="O80" t="n">
-        <v>1.703320922234441</v>
+        <v>1.703319999704791</v>
       </c>
       <c r="P80" t="n">
-        <v>1.789741018803004</v>
+        <v>1.789739755202716</v>
       </c>
       <c r="Q80" t="n">
-        <v>1.855661642097258</v>
+        <v>1.855660665441289</v>
       </c>
       <c r="R80" t="n">
-        <v>1.881495324460338</v>
+        <v>1.881494651260718</v>
       </c>
       <c r="S80" t="n">
-        <v>1.903665471606559</v>
+        <v>1.903664773421491</v>
       </c>
       <c r="T80" t="n">
-        <v>1.923359360475925</v>
+        <v>1.92335863427217</v>
       </c>
       <c r="U80" t="n">
-        <v>1.951506479504143</v>
+        <v>1.951506100663312</v>
       </c>
       <c r="V80" t="n">
-        <v>1.983080745775244</v>
+        <v>1.983080349103164</v>
       </c>
     </row>
     <row r="81">
@@ -6530,58 +6530,58 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>0.2240846347818048</v>
+        <v>0.2240838081518663</v>
       </c>
       <c r="F81" t="n">
-        <v>0.3113240595877831</v>
+        <v>0.3113227514611774</v>
       </c>
       <c r="G81" t="n">
-        <v>0.4437495294158553</v>
+        <v>0.4437479034772823</v>
       </c>
       <c r="H81" t="n">
-        <v>0.5443484237631658</v>
+        <v>0.5443464950991442</v>
       </c>
       <c r="I81" t="n">
-        <v>0.6189241135607734</v>
+        <v>0.6189218850667088</v>
       </c>
       <c r="J81" t="n">
-        <v>0.663357340132767</v>
+        <v>0.6633548154769207</v>
       </c>
       <c r="K81" t="n">
-        <v>0.6816826151080072</v>
+        <v>0.6816796859289107</v>
       </c>
       <c r="L81" t="n">
-        <v>0.6845235296413864</v>
+        <v>0.6845202027371108</v>
       </c>
       <c r="M81" t="n">
-        <v>0.6898294639515773</v>
+        <v>0.6898256273453995</v>
       </c>
       <c r="N81" t="n">
-        <v>0.7028796672078805</v>
+        <v>0.7028753131137911</v>
       </c>
       <c r="O81" t="n">
-        <v>0.7124581876797528</v>
+        <v>0.7124534378131269</v>
       </c>
       <c r="P81" t="n">
-        <v>0.7377128078129227</v>
+        <v>0.737707571899773</v>
       </c>
       <c r="Q81" t="n">
-        <v>0.7551775887838397</v>
+        <v>0.7551718905448488</v>
       </c>
       <c r="R81" t="n">
-        <v>0.755811173751081</v>
+        <v>0.7558052492849066</v>
       </c>
       <c r="S81" t="n">
-        <v>0.7560373819244116</v>
+        <v>0.7560312498530857</v>
       </c>
       <c r="T81" t="n">
-        <v>0.7558369658263525</v>
+        <v>0.7558304435442803</v>
       </c>
       <c r="U81" t="n">
-        <v>0.758898521012173</v>
+        <v>0.7588916346780048</v>
       </c>
       <c r="V81" t="n">
-        <v>0.7630543038934049</v>
+        <v>0.7630469849200258</v>
       </c>
     </row>
     <row r="82">
@@ -6606,58 +6606,58 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>3.95187922005916</v>
+        <v>3.951880541519238</v>
       </c>
       <c r="F82" t="n">
-        <v>4.118107420367566</v>
+        <v>4.118109415168028</v>
       </c>
       <c r="G82" t="n">
-        <v>4.343597152371256</v>
+        <v>4.34359926684238</v>
       </c>
       <c r="H82" t="n">
-        <v>4.33762953618091</v>
+        <v>4.33763196158711</v>
       </c>
       <c r="I82" t="n">
-        <v>4.35050099426442</v>
+        <v>4.350503740614135</v>
       </c>
       <c r="J82" t="n">
-        <v>4.377876612620192</v>
+        <v>4.377879867021727</v>
       </c>
       <c r="K82" t="n">
-        <v>4.381591125069275</v>
+        <v>4.381594913888744</v>
       </c>
       <c r="L82" t="n">
-        <v>4.362933625579602</v>
+        <v>4.36293798972227</v>
       </c>
       <c r="M82" t="n">
-        <v>4.380067250310502</v>
+        <v>4.380072239734705</v>
       </c>
       <c r="N82" t="n">
-        <v>4.447945595344405</v>
+        <v>4.447951272721412</v>
       </c>
       <c r="O82" t="n">
-        <v>4.455846362426553</v>
+        <v>4.455852607610192</v>
       </c>
       <c r="P82" t="n">
-        <v>4.544835850205783</v>
+        <v>4.544842925500877</v>
       </c>
       <c r="Q82" t="n">
-        <v>4.584744961600034</v>
+        <v>4.584752753759358</v>
       </c>
       <c r="R82" t="n">
-        <v>4.538417051663929</v>
+        <v>4.538425430120983</v>
       </c>
       <c r="S82" t="n">
-        <v>4.500721154009004</v>
+        <v>4.500729960962613</v>
       </c>
       <c r="T82" t="n">
-        <v>4.473152297298262</v>
+        <v>4.473161816325607</v>
       </c>
       <c r="U82" t="n">
-        <v>4.478760662268932</v>
+        <v>4.478770966709869</v>
       </c>
       <c r="V82" t="n">
-        <v>4.504621230397107</v>
+        <v>4.504632401462558</v>
       </c>
     </row>
     <row r="83">
@@ -6682,58 +6682,58 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1.194165025285576</v>
+        <v>1.194164746445397</v>
       </c>
       <c r="F83" t="n">
-        <v>1.663302695822867</v>
+        <v>1.663302561280627</v>
       </c>
       <c r="G83" t="n">
-        <v>2.335765602514014</v>
+        <v>2.335765865183983</v>
       </c>
       <c r="H83" t="n">
-        <v>2.805280153825202</v>
+        <v>2.805280834754639</v>
       </c>
       <c r="I83" t="n">
-        <v>3.096890596199026</v>
+        <v>3.09689166129546</v>
       </c>
       <c r="J83" t="n">
-        <v>3.226636272270325</v>
+        <v>3.226637662750901</v>
       </c>
       <c r="K83" t="n">
-        <v>3.243541718581413</v>
+        <v>3.243543382027735</v>
       </c>
       <c r="L83" t="n">
-        <v>3.205394291548031</v>
+        <v>3.20539614773959</v>
       </c>
       <c r="M83" t="n">
-        <v>3.188285248953001</v>
+        <v>3.188287351768468</v>
       </c>
       <c r="N83" t="n">
-        <v>3.213119061111465</v>
+        <v>3.213121401904357</v>
       </c>
       <c r="O83" t="n">
-        <v>3.201110144594291</v>
+        <v>3.201112711527991</v>
       </c>
       <c r="P83" t="n">
-        <v>3.252685779386474</v>
+        <v>3.252688672634272</v>
       </c>
       <c r="Q83" t="n">
-        <v>3.274063167884299</v>
+        <v>3.274066383532743</v>
       </c>
       <c r="R83" t="n">
-        <v>3.237721094752898</v>
+        <v>3.237724546469141</v>
       </c>
       <c r="S83" t="n">
-        <v>3.209563620608549</v>
+        <v>3.209567335541847</v>
       </c>
       <c r="T83" t="n">
-        <v>3.188591827855991</v>
+        <v>3.188595832559697</v>
       </c>
       <c r="U83" t="n">
-        <v>3.190330481469285</v>
+        <v>3.190334849996304</v>
       </c>
       <c r="V83" t="n">
-        <v>3.205779362107399</v>
+        <v>3.205784075899143</v>
       </c>
     </row>
     <row r="84">
@@ -6910,10 +6910,10 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1.875253870674894</v>
+        <v>1.875254008516987</v>
       </c>
       <c r="F86" t="n">
-        <v>2.068512359029223</v>
+        <v>2.068512501183434</v>
       </c>
       <c r="G86" t="n">
         <v>2.178902178736219</v>
@@ -6922,46 +6922,46 @@
         <v>2.175784327400673</v>
       </c>
       <c r="I86" t="n">
-        <v>2.148317216150005</v>
+        <v>2.148317061283807</v>
       </c>
       <c r="J86" t="n">
-        <v>2.082016891857494</v>
+        <v>2.08201657367151</v>
       </c>
       <c r="K86" t="n">
-        <v>2.002101347942611</v>
+        <v>2.002100857508208</v>
       </c>
       <c r="L86" t="n">
-        <v>1.906065864764742</v>
+        <v>1.906065023820584</v>
       </c>
       <c r="M86" t="n">
-        <v>1.840810646647448</v>
+        <v>1.840809606868089</v>
       </c>
       <c r="N86" t="n">
-        <v>1.808681876812489</v>
+        <v>1.808680624506905</v>
       </c>
       <c r="O86" t="n">
-        <v>1.790761317422349</v>
+        <v>1.79075964703629</v>
       </c>
       <c r="P86" t="n">
-        <v>1.7941370197226</v>
+        <v>1.794135085868906</v>
       </c>
       <c r="Q86" t="n">
-        <v>1.776097717052713</v>
+        <v>1.776095492312714</v>
       </c>
       <c r="R86" t="n">
-        <v>1.735878468582625</v>
+        <v>1.735875710709268</v>
       </c>
       <c r="S86" t="n">
-        <v>1.69659009269129</v>
+        <v>1.696586970045124</v>
       </c>
       <c r="T86" t="n">
-        <v>1.65939983930352</v>
+        <v>1.659396314227185</v>
       </c>
       <c r="U86" t="n">
-        <v>1.626514372652423</v>
+        <v>1.62651040028323</v>
       </c>
       <c r="V86" t="n">
-        <v>1.596678578405021</v>
+        <v>1.596674102947115</v>
       </c>
     </row>
     <row r="87">
@@ -6986,16 +6986,16 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1.594013787461761</v>
+        <v>1.594012935331862</v>
       </c>
       <c r="F87" t="n">
-        <v>1.816440049942576</v>
+        <v>1.816439242855056</v>
       </c>
       <c r="G87" t="n">
-        <v>2.038707321807667</v>
+        <v>2.038706551512705</v>
       </c>
       <c r="H87" t="n">
-        <v>2.141562667386785</v>
+        <v>2.141561925506296</v>
       </c>
       <c r="I87" t="n">
         <v>2.18912418552547</v>
@@ -7013,31 +7013,31 @@
         <v>1.976652924872647</v>
       </c>
       <c r="N87" t="n">
-        <v>1.950899949077603</v>
+        <v>1.950899286887781</v>
       </c>
       <c r="O87" t="n">
-        <v>1.938828796466299</v>
+        <v>1.938828131236529</v>
       </c>
       <c r="P87" t="n">
-        <v>1.950984597992356</v>
+        <v>1.95098392347157</v>
       </c>
       <c r="Q87" t="n">
-        <v>1.942817461713758</v>
+        <v>1.942816081842901</v>
       </c>
       <c r="R87" t="n">
-        <v>1.914124917487993</v>
+        <v>1.914123494867184</v>
       </c>
       <c r="S87" t="n">
-        <v>1.889220440684998</v>
+        <v>1.889218964204956</v>
       </c>
       <c r="T87" t="n">
-        <v>1.867378688470313</v>
+        <v>1.867377148519761</v>
       </c>
       <c r="U87" t="n">
-        <v>1.851738994058078</v>
+        <v>1.851737381377246</v>
       </c>
       <c r="V87" t="n">
-        <v>1.84150799747011</v>
+        <v>1.841505454015183</v>
       </c>
     </row>
     <row r="88">
@@ -7062,58 +7062,58 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>2.752938107495987</v>
+        <v>2.75293894598369</v>
       </c>
       <c r="F88" t="n">
-        <v>2.64103865161821</v>
+        <v>2.641039660391789</v>
       </c>
       <c r="G88" t="n">
-        <v>2.520798196391877</v>
+        <v>2.520799012914669</v>
       </c>
       <c r="H88" t="n">
-        <v>2.414341539169966</v>
+        <v>2.414342171198462</v>
       </c>
       <c r="I88" t="n">
-        <v>2.373253422062151</v>
+        <v>2.373254053605391</v>
       </c>
       <c r="J88" t="n">
-        <v>2.338045870350545</v>
+        <v>2.338046592490824</v>
       </c>
       <c r="K88" t="n">
-        <v>2.304973207019914</v>
+        <v>2.304974110204815</v>
       </c>
       <c r="L88" t="n">
-        <v>2.25536644048895</v>
+        <v>2.255367436201952</v>
       </c>
       <c r="M88" t="n">
-        <v>2.23844067228849</v>
+        <v>2.238441946665501</v>
       </c>
       <c r="N88" t="n">
-        <v>2.260435160160943</v>
+        <v>2.260436723963153</v>
       </c>
       <c r="O88" t="n">
-        <v>2.299016819848377</v>
+        <v>2.29901869382179</v>
       </c>
       <c r="P88" t="n">
-        <v>2.364532645896227</v>
+        <v>2.364534855790017</v>
       </c>
       <c r="Q88" t="n">
-        <v>2.40099651033288</v>
+        <v>2.400999084271748</v>
       </c>
       <c r="R88" t="n">
-        <v>2.404310866282896</v>
+        <v>2.404313627862249</v>
       </c>
       <c r="S88" t="n">
-        <v>2.403673740716983</v>
+        <v>2.403676915800284</v>
       </c>
       <c r="T88" t="n">
-        <v>2.405696017866075</v>
+        <v>2.405699418211813</v>
       </c>
       <c r="U88" t="n">
-        <v>2.417327535866019</v>
+        <v>2.417331295227684</v>
       </c>
       <c r="V88" t="n">
-        <v>2.439033589653846</v>
+        <v>2.439037743572434</v>
       </c>
     </row>
     <row r="89">
@@ -7138,58 +7138,58 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>4.096400985809095</v>
+        <v>4.096402487651104</v>
       </c>
       <c r="F89" t="n">
-        <v>4.286228249685823</v>
+        <v>4.286232046380421</v>
       </c>
       <c r="G89" t="n">
-        <v>4.518972416089175</v>
+        <v>4.518977040124294</v>
       </c>
       <c r="H89" t="n">
-        <v>4.560883543280196</v>
+        <v>4.56089060911414</v>
       </c>
       <c r="I89" t="n">
-        <v>4.562738116944809</v>
+        <v>4.562746114155383</v>
       </c>
       <c r="J89" t="n">
-        <v>4.479025494718556</v>
+        <v>4.479035254085108</v>
       </c>
       <c r="K89" t="n">
-        <v>4.366516461892084</v>
+        <v>4.366526383675359</v>
       </c>
       <c r="L89" t="n">
-        <v>4.222298483128467</v>
+        <v>4.222310273158145</v>
       </c>
       <c r="M89" t="n">
-        <v>4.148135789420272</v>
+        <v>4.148147829624234</v>
       </c>
       <c r="N89" t="n">
-        <v>4.15422462491648</v>
+        <v>4.154238710080664</v>
       </c>
       <c r="O89" t="n">
-        <v>4.195430586636106</v>
+        <v>4.195445951173308</v>
       </c>
       <c r="P89" t="n">
-        <v>4.294228291006599</v>
+        <v>4.294245027065926</v>
       </c>
       <c r="Q89" t="n">
-        <v>4.350859842549868</v>
+        <v>4.350877092107848</v>
       </c>
       <c r="R89" t="n">
-        <v>4.357983484322971</v>
+        <v>4.358002285872614</v>
       </c>
       <c r="S89" t="n">
-        <v>4.369046498108634</v>
+        <v>4.369066967429217</v>
       </c>
       <c r="T89" t="n">
-        <v>4.387217818036545</v>
+        <v>4.38724007150782</v>
       </c>
       <c r="U89" t="n">
-        <v>4.420456816998618</v>
+        <v>4.420480980236668</v>
       </c>
       <c r="V89" t="n">
-        <v>4.471025178686904</v>
+        <v>4.471051410049806</v>
       </c>
     </row>
     <row r="90">
@@ -7214,58 +7214,58 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1.319073443409129</v>
+        <v>1.319072934960234</v>
       </c>
       <c r="F90" t="n">
-        <v>1.402595865722623</v>
+        <v>1.402594833092972</v>
       </c>
       <c r="G90" t="n">
-        <v>1.512088500377828</v>
+        <v>1.512087030230019</v>
       </c>
       <c r="H90" t="n">
-        <v>1.571821908302238</v>
+        <v>1.571820194349397</v>
       </c>
       <c r="I90" t="n">
-        <v>1.615920220924648</v>
+        <v>1.615918249556579</v>
       </c>
       <c r="J90" t="n">
-        <v>1.62181058095894</v>
+        <v>1.621808337614383</v>
       </c>
       <c r="K90" t="n">
-        <v>1.6071098928214</v>
+        <v>1.607107591073268</v>
       </c>
       <c r="L90" t="n">
-        <v>1.574130250316946</v>
+        <v>1.574127764700674</v>
       </c>
       <c r="M90" t="n">
-        <v>1.56445316814174</v>
+        <v>1.564450605379385</v>
       </c>
       <c r="N90" t="n">
-        <v>1.580249064075324</v>
+        <v>1.58024616090697</v>
       </c>
       <c r="O90" t="n">
-        <v>1.603385989612242</v>
+        <v>1.603383102155211</v>
       </c>
       <c r="P90" t="n">
-        <v>1.641862349565879</v>
+        <v>1.641859196062234</v>
       </c>
       <c r="Q90" t="n">
-        <v>1.659122418439314</v>
+        <v>1.659119113696793</v>
       </c>
       <c r="R90" t="n">
-        <v>1.654881273175373</v>
+        <v>1.654877804739422</v>
       </c>
       <c r="S90" t="n">
-        <v>1.651913645752297</v>
+        <v>1.65191000232704</v>
       </c>
       <c r="T90" t="n">
-        <v>1.652723796644945</v>
+        <v>1.652720132829947</v>
       </c>
       <c r="U90" t="n">
-        <v>1.659361245157463</v>
+        <v>1.659357389529692</v>
       </c>
       <c r="V90" t="n">
-        <v>1.67033162294652</v>
+        <v>1.670327744099535</v>
       </c>
     </row>
     <row r="91">
@@ -7290,58 +7290,58 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1.147976454861036</v>
+        <v>1.147975838818677</v>
       </c>
       <c r="F91" t="n">
-        <v>1.260026198826864</v>
+        <v>1.260025251424735</v>
       </c>
       <c r="G91" t="n">
-        <v>1.341374225815479</v>
+        <v>1.341372602616986</v>
       </c>
       <c r="H91" t="n">
-        <v>1.339091056707637</v>
+        <v>1.339088708259693</v>
       </c>
       <c r="I91" t="n">
-        <v>1.309616056107673</v>
+        <v>1.309612922923317</v>
       </c>
       <c r="J91" t="n">
-        <v>1.251490500572002</v>
+        <v>1.25148687801623</v>
       </c>
       <c r="K91" t="n">
-        <v>1.187654196933117</v>
+        <v>1.187650041572494</v>
       </c>
       <c r="L91" t="n">
-        <v>1.121333038781631</v>
+        <v>1.121328296446529</v>
       </c>
       <c r="M91" t="n">
-        <v>1.078260068403012</v>
+        <v>1.078254673189065</v>
       </c>
       <c r="N91" t="n">
-        <v>1.057959288337953</v>
+        <v>1.057953162072113</v>
       </c>
       <c r="O91" t="n">
-        <v>1.045355879887415</v>
+        <v>1.045349403119581</v>
       </c>
       <c r="P91" t="n">
-        <v>1.044476396723813</v>
+        <v>1.044469045739296</v>
       </c>
       <c r="Q91" t="n">
-        <v>1.030149254972221</v>
+        <v>1.030140941089909</v>
       </c>
       <c r="R91" t="n">
-        <v>1.006620709725532</v>
+        <v>1.006611890931358</v>
       </c>
       <c r="S91" t="n">
-        <v>0.9900538242318316</v>
+        <v>0.9900438903273572</v>
       </c>
       <c r="T91" t="n">
-        <v>0.9814727313883113</v>
+        <v>0.9814622175329053</v>
       </c>
       <c r="U91" t="n">
-        <v>0.9808709574838338</v>
+        <v>0.9808598568276544</v>
       </c>
       <c r="V91" t="n">
-        <v>0.9864341338602451</v>
+        <v>0.9864231259558818</v>
       </c>
     </row>
     <row r="92">
@@ -7366,58 +7366,58 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>0.957407913000585</v>
+        <v>0.9574074541429112</v>
       </c>
       <c r="F92" t="n">
-        <v>1.06656371519115</v>
+        <v>1.066562294953137</v>
       </c>
       <c r="G92" t="n">
-        <v>1.176068520459804</v>
+        <v>1.176066567419678</v>
       </c>
       <c r="H92" t="n">
-        <v>1.207211671906778</v>
+        <v>1.207208643912975</v>
       </c>
       <c r="I92" t="n">
-        <v>1.204798077178972</v>
+        <v>1.204794946228535</v>
       </c>
       <c r="J92" t="n">
-        <v>1.168597383070314</v>
+        <v>1.16859306862025</v>
       </c>
       <c r="K92" t="n">
-        <v>1.121462279953366</v>
+        <v>1.121457813135126</v>
       </c>
       <c r="L92" t="n">
-        <v>1.06466886209454</v>
+        <v>1.064664223049905</v>
       </c>
       <c r="M92" t="n">
-        <v>1.027054652391363</v>
+        <v>1.027049215484552</v>
       </c>
       <c r="N92" t="n">
-        <v>1.008022934572467</v>
+        <v>1.008016622768067</v>
       </c>
       <c r="O92" t="n">
-        <v>0.9955373821251521</v>
+        <v>0.995530758081995</v>
       </c>
       <c r="P92" t="n">
-        <v>0.9941653864114021</v>
+        <v>0.9941577083698331</v>
       </c>
       <c r="Q92" t="n">
-        <v>0.9829037109889843</v>
+        <v>0.9828948505126894</v>
       </c>
       <c r="R92" t="n">
-        <v>0.9639530792983677</v>
+        <v>0.963944460506738</v>
       </c>
       <c r="S92" t="n">
-        <v>0.9508172284600529</v>
+        <v>0.9508072353469734</v>
       </c>
       <c r="T92" t="n">
-        <v>0.943222289092647</v>
+        <v>0.9432116684957695</v>
       </c>
       <c r="U92" t="n">
-        <v>0.9411294083138412</v>
+        <v>0.9411181266405434</v>
       </c>
       <c r="V92" t="n">
-        <v>0.9440743942475378</v>
+        <v>0.9440634010083798</v>
       </c>
     </row>
     <row r="93">
@@ -7442,58 +7442,58 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1.076085136489594</v>
+        <v>1.076082778138082</v>
       </c>
       <c r="F93" t="n">
         <v>1.202823209129785</v>
       </c>
       <c r="G93" t="n">
-        <v>1.35688621376207</v>
+        <v>1.356883912027713</v>
       </c>
       <c r="H93" t="n">
-        <v>1.472256759707204</v>
+        <v>1.472254461464211</v>
       </c>
       <c r="I93" t="n">
-        <v>1.567812498556935</v>
+        <v>1.567810189653341</v>
       </c>
       <c r="J93" t="n">
-        <v>1.611538291108981</v>
+        <v>1.61153595891609</v>
       </c>
       <c r="K93" t="n">
-        <v>1.615167914772432</v>
+        <v>1.615165549442492</v>
       </c>
       <c r="L93" t="n">
-        <v>1.58031701425313</v>
+        <v>1.580314608255459</v>
       </c>
       <c r="M93" t="n">
-        <v>1.549909865718315</v>
+        <v>1.5499074130848</v>
       </c>
       <c r="N93" t="n">
-        <v>1.533623250159788</v>
+        <v>1.533620743674257</v>
       </c>
       <c r="O93" t="n">
-        <v>1.523048435322992</v>
+        <v>1.523045859934946</v>
       </c>
       <c r="P93" t="n">
-        <v>1.531847015024739</v>
+        <v>1.531841688991622</v>
       </c>
       <c r="Q93" t="n">
-        <v>1.527567831337995</v>
+        <v>1.527565058751116</v>
       </c>
       <c r="R93" t="n">
-        <v>1.508445577944769</v>
+        <v>1.508442673188812</v>
       </c>
       <c r="S93" t="n">
-        <v>1.49125472727773</v>
+        <v>1.49125167002455</v>
       </c>
       <c r="T93" t="n">
-        <v>1.475402111894251</v>
+        <v>1.47539565744972</v>
       </c>
       <c r="U93" t="n">
-        <v>1.462774957698816</v>
+        <v>1.462768134927133</v>
       </c>
       <c r="V93" t="n">
-        <v>1.454366268365763</v>
+        <v>1.454359048409805</v>
       </c>
     </row>
     <row r="94">
@@ -7518,58 +7518,58 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>2.176892577991995</v>
+        <v>2.176892891089734</v>
       </c>
       <c r="F94" t="n">
-        <v>2.508610615121665</v>
+        <v>2.508611426027352</v>
       </c>
       <c r="G94" t="n">
-        <v>2.741120952496259</v>
+        <v>2.741122271363205</v>
       </c>
       <c r="H94" t="n">
-        <v>2.812856061610759</v>
+        <v>2.812857856671128</v>
       </c>
       <c r="I94" t="n">
-        <v>2.832643433279889</v>
+        <v>2.832645623989364</v>
       </c>
       <c r="J94" t="n">
-        <v>2.793184007592034</v>
+        <v>2.793186537520384</v>
       </c>
       <c r="K94" t="n">
-        <v>2.733701034104174</v>
+        <v>2.733703898177842</v>
       </c>
       <c r="L94" t="n">
-        <v>2.650337794598807</v>
+        <v>2.650340927160774</v>
       </c>
       <c r="M94" t="n">
-        <v>2.602825981577233</v>
+        <v>2.602829373556867</v>
       </c>
       <c r="N94" t="n">
-        <v>2.596475006788983</v>
+        <v>2.596478717139806</v>
       </c>
       <c r="O94" t="n">
-        <v>2.604896009383876</v>
+        <v>2.604899979382695</v>
       </c>
       <c r="P94" t="n">
-        <v>2.645165683445306</v>
+        <v>2.645169953501884</v>
       </c>
       <c r="Q94" t="n">
-        <v>2.656138006234781</v>
+        <v>2.65614254343819</v>
       </c>
       <c r="R94" t="n">
-        <v>2.631833994300281</v>
+        <v>2.631838747963133</v>
       </c>
       <c r="S94" t="n">
-        <v>2.602776037700903</v>
+        <v>2.602780894367501</v>
       </c>
       <c r="T94" t="n">
-        <v>2.571766191780989</v>
+        <v>2.571771184788607</v>
       </c>
       <c r="U94" t="n">
-        <v>2.548136823494655</v>
+        <v>2.548141945503653</v>
       </c>
       <c r="V94" t="n">
-        <v>2.536032371509682</v>
+        <v>2.536037619746467</v>
       </c>
     </row>
     <row r="95">
@@ -7594,58 +7594,58 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1.038066096109129</v>
+        <v>1.038065385439033</v>
       </c>
       <c r="F95" t="n">
-        <v>1.219493441947082</v>
+        <v>1.219492185291034</v>
       </c>
       <c r="G95" t="n">
-        <v>1.375738396624473</v>
+        <v>1.375736712822646</v>
       </c>
       <c r="H95" t="n">
-        <v>1.445399652834758</v>
+        <v>1.445397563319943</v>
       </c>
       <c r="I95" t="n">
-        <v>1.480691288695692</v>
+        <v>1.480688869064276</v>
       </c>
       <c r="J95" t="n">
-        <v>1.469058763342118</v>
+        <v>1.469055984727426</v>
       </c>
       <c r="K95" t="n">
-        <v>1.433282376002726</v>
+        <v>1.433279200620107</v>
       </c>
       <c r="L95" t="n">
-        <v>1.3754341709921</v>
+        <v>1.375430608928787</v>
       </c>
       <c r="M95" t="n">
-        <v>1.334601854672874</v>
+        <v>1.334597850791611</v>
       </c>
       <c r="N95" t="n">
-        <v>1.315116612578543</v>
+        <v>1.315112164250848</v>
       </c>
       <c r="O95" t="n">
-        <v>1.304422436578615</v>
+        <v>1.304417470976053</v>
       </c>
       <c r="P95" t="n">
-        <v>1.310465131338865</v>
+        <v>1.310459493660278</v>
       </c>
       <c r="Q95" t="n">
-        <v>1.30230447460359</v>
+        <v>1.302298319489798</v>
       </c>
       <c r="R95" t="n">
-        <v>1.281389657420982</v>
+        <v>1.281383110028923</v>
       </c>
       <c r="S95" t="n">
-        <v>1.265644103367625</v>
+        <v>1.265637145857994</v>
       </c>
       <c r="T95" t="n">
-        <v>1.256480906105357</v>
+        <v>1.256473527931308</v>
       </c>
       <c r="U95" t="n">
-        <v>1.254564172285999</v>
+        <v>1.254556359890015</v>
       </c>
       <c r="V95" t="n">
-        <v>1.259395039799889</v>
+        <v>1.25938665142424</v>
       </c>
     </row>
     <row r="96">
@@ -7670,58 +7670,58 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>1.70414016697902</v>
+        <v>1.704139986026876</v>
       </c>
       <c r="F96" t="n">
-        <v>1.721181382096713</v>
+        <v>1.72118084390125</v>
       </c>
       <c r="G96" t="n">
-        <v>1.66672257943607</v>
+        <v>1.666721506483139</v>
       </c>
       <c r="H96" t="n">
-        <v>1.596876669423909</v>
+        <v>1.596875053852384</v>
       </c>
       <c r="I96" t="n">
-        <v>1.562991704896029</v>
+        <v>1.562989529511449</v>
       </c>
       <c r="J96" t="n">
-        <v>1.533711201228438</v>
+        <v>1.533708628198024</v>
       </c>
       <c r="K96" t="n">
-        <v>1.508897615410679</v>
+        <v>1.508894813659248</v>
       </c>
       <c r="L96" t="n">
-        <v>1.476548353787075</v>
+        <v>1.476545498669991</v>
       </c>
       <c r="M96" t="n">
-        <v>1.465218089282778</v>
+        <v>1.465214975875962</v>
       </c>
       <c r="N96" t="n">
-        <v>1.478078699961815</v>
+        <v>1.478075103308861</v>
       </c>
       <c r="O96" t="n">
-        <v>1.500590148029744</v>
+        <v>1.500586429260434</v>
       </c>
       <c r="P96" t="n">
-        <v>1.541630185918005</v>
+        <v>1.541626316611984</v>
       </c>
       <c r="Q96" t="n">
-        <v>1.565874640251807</v>
+        <v>1.565870596244015</v>
       </c>
       <c r="R96" t="n">
-        <v>1.570358007730721</v>
+        <v>1.570354006566146</v>
       </c>
       <c r="S96" t="n">
-        <v>1.573551955666814</v>
+        <v>1.573547513661634</v>
       </c>
       <c r="T96" t="n">
-        <v>1.57687846522047</v>
+        <v>1.576874065762069</v>
       </c>
       <c r="U96" t="n">
-        <v>1.584666394053781</v>
+        <v>1.584661778098541</v>
       </c>
       <c r="V96" t="n">
-        <v>1.598324565807792</v>
+        <v>1.598319716091928</v>
       </c>
     </row>
     <row r="97">
@@ -7749,55 +7749,55 @@
         <v>1.89345638113114</v>
       </c>
       <c r="F97" t="n">
-        <v>1.767717534067839</v>
+        <v>1.767717053663992</v>
       </c>
       <c r="G97" t="n">
-        <v>1.659467486863488</v>
+        <v>1.659466531220151</v>
       </c>
       <c r="H97" t="n">
-        <v>1.574580739673276</v>
+        <v>1.574578830962158</v>
       </c>
       <c r="I97" t="n">
-        <v>1.540973819590925</v>
+        <v>1.54097143348</v>
       </c>
       <c r="J97" t="n">
-        <v>1.513819037269677</v>
+        <v>1.513816171290049</v>
       </c>
       <c r="K97" t="n">
-        <v>1.490187973634071</v>
+        <v>1.490185099858898</v>
       </c>
       <c r="L97" t="n">
-        <v>1.458203162254096</v>
+        <v>1.458199790570267</v>
       </c>
       <c r="M97" t="n">
-        <v>1.446771877950507</v>
+        <v>1.446768478189073</v>
       </c>
       <c r="N97" t="n">
-        <v>1.45851742277078</v>
+        <v>1.458513496401974</v>
       </c>
       <c r="O97" t="n">
-        <v>1.478922688062355</v>
+        <v>1.478918705246215</v>
       </c>
       <c r="P97" t="n">
-        <v>1.516382513971235</v>
+        <v>1.516378461401298</v>
       </c>
       <c r="Q97" t="n">
-        <v>1.53686968940329</v>
+        <v>1.536865552870831</v>
       </c>
       <c r="R97" t="n">
-        <v>1.539056042605533</v>
+        <v>1.53905180662095</v>
       </c>
       <c r="S97" t="n">
-        <v>1.542087390049747</v>
+        <v>1.542083037738888</v>
       </c>
       <c r="T97" t="n">
-        <v>1.54694187673303</v>
+        <v>1.546937390831378</v>
       </c>
       <c r="U97" t="n">
-        <v>1.556139443695342</v>
+        <v>1.556134806084082</v>
       </c>
       <c r="V97" t="n">
-        <v>1.569960514722024</v>
+        <v>1.569955101660306</v>
       </c>
     </row>
     <row r="98">
@@ -7822,58 +7822,58 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>2.254847806702494</v>
+        <v>2.254847572418388</v>
       </c>
       <c r="F98" t="n">
-        <v>2.185426221903988</v>
+        <v>2.185425990553979</v>
       </c>
       <c r="G98" t="n">
         <v>1.976319493125171</v>
       </c>
       <c r="H98" t="n">
-        <v>1.768724856175445</v>
+        <v>1.768725311550614</v>
       </c>
       <c r="I98" t="n">
-        <v>1.616908875617138</v>
+        <v>1.61690955665955</v>
       </c>
       <c r="J98" t="n">
-        <v>1.490331600658296</v>
+        <v>1.490332508590457</v>
       </c>
       <c r="K98" t="n">
-        <v>1.394328529126094</v>
+        <v>1.394329666988606</v>
       </c>
       <c r="L98" t="n">
-        <v>1.303623947390004</v>
+        <v>1.303625092838609</v>
       </c>
       <c r="M98" t="n">
-        <v>1.253692393655171</v>
+        <v>1.253693783601964</v>
       </c>
       <c r="N98" t="n">
-        <v>1.238437542129092</v>
+        <v>1.238439071422471</v>
       </c>
       <c r="O98" t="n">
-        <v>1.236899190310444</v>
+        <v>1.236900992397116</v>
       </c>
       <c r="P98" t="n">
-        <v>1.255424938084477</v>
+        <v>1.255426909131764</v>
       </c>
       <c r="Q98" t="n">
-        <v>1.275137269577776</v>
+        <v>1.275139678260799</v>
       </c>
       <c r="R98" t="n">
-        <v>1.289112331865354</v>
+        <v>1.289114952009441</v>
       </c>
       <c r="S98" t="n">
-        <v>1.304319269294227</v>
+        <v>1.304322396942954</v>
       </c>
       <c r="T98" t="n">
-        <v>1.318242821307238</v>
+        <v>1.318246507140948</v>
       </c>
       <c r="U98" t="n">
-        <v>1.338828874388376</v>
+        <v>1.33883347851174</v>
       </c>
       <c r="V98" t="n">
-        <v>1.365270513922907</v>
+        <v>1.365276306914577</v>
       </c>
     </row>
     <row r="99">
@@ -7898,58 +7898,58 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>2.66591949502802</v>
+        <v>2.665919130479955</v>
       </c>
       <c r="F99" t="n">
-        <v>2.973128864877053</v>
+        <v>2.973127880622442</v>
       </c>
       <c r="G99" t="n">
-        <v>3.132743053933438</v>
+        <v>3.132741467318824</v>
       </c>
       <c r="H99" t="n">
-        <v>3.145347358475271</v>
+        <v>3.145345266558178</v>
       </c>
       <c r="I99" t="n">
-        <v>3.104245711230482</v>
+        <v>3.104243119959438</v>
       </c>
       <c r="J99" t="n">
-        <v>2.995395864206482</v>
+        <v>2.995392946720703</v>
       </c>
       <c r="K99" t="n">
-        <v>2.874941025981082</v>
+        <v>2.87493786016505</v>
       </c>
       <c r="L99" t="n">
-        <v>2.721025082554626</v>
+        <v>2.721021655273814</v>
       </c>
       <c r="M99" t="n">
-        <v>2.629140372741421</v>
+        <v>2.62913666927058</v>
       </c>
       <c r="N99" t="n">
-        <v>2.600385110117696</v>
+        <v>2.600380941131307</v>
       </c>
       <c r="O99" t="n">
-        <v>2.596824069285999</v>
+        <v>2.596819496184978</v>
       </c>
       <c r="P99" t="n">
-        <v>2.634650866512882</v>
+        <v>2.634645595427199</v>
       </c>
       <c r="Q99" t="n">
-        <v>2.674024679081787</v>
+        <v>2.674018669121645</v>
       </c>
       <c r="R99" t="n">
-        <v>2.698663501430599</v>
+        <v>2.698656513811728</v>
       </c>
       <c r="S99" t="n">
-        <v>2.724551546436157</v>
+        <v>2.724543506289022</v>
       </c>
       <c r="T99" t="n">
-        <v>2.750022858937153</v>
+        <v>2.750013379637081</v>
       </c>
       <c r="U99" t="n">
-        <v>2.791277041829225</v>
+        <v>2.791265480463748</v>
       </c>
       <c r="V99" t="n">
-        <v>2.84699462359623</v>
+        <v>2.846979893137997</v>
       </c>
     </row>
     <row r="100">
@@ -7974,58 +7974,58 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1.719173322874818</v>
+        <v>1.719173499459386</v>
       </c>
       <c r="F100" t="n">
-        <v>1.646711897453737</v>
+        <v>1.646712244635093</v>
       </c>
       <c r="G100" t="n">
-        <v>1.499911116003529</v>
+        <v>1.499911970657341</v>
       </c>
       <c r="H100" t="n">
-        <v>1.352713155376177</v>
+        <v>1.352714337965423</v>
       </c>
       <c r="I100" t="n">
-        <v>1.242673934414812</v>
+        <v>1.242675441181198</v>
       </c>
       <c r="J100" t="n">
-        <v>1.146858692494333</v>
+        <v>1.146860522811914</v>
       </c>
       <c r="K100" t="n">
-        <v>1.07244131435938</v>
+        <v>1.072443304054418</v>
       </c>
       <c r="L100" t="n">
-        <v>1.000371720732376</v>
+        <v>1.00037403984568</v>
       </c>
       <c r="M100" t="n">
-        <v>0.9590246367874227</v>
+        <v>0.9590271240621109</v>
       </c>
       <c r="N100" t="n">
-        <v>0.9442488760779688</v>
+        <v>0.9442517039732594</v>
       </c>
       <c r="O100" t="n">
-        <v>0.9400118815202522</v>
+        <v>0.9400150619779133</v>
       </c>
       <c r="P100" t="n">
-        <v>0.9517594961877737</v>
+        <v>0.9517632127134911</v>
       </c>
       <c r="Q100" t="n">
-        <v>0.9650056168659547</v>
+        <v>0.9650097211370131</v>
       </c>
       <c r="R100" t="n">
-        <v>0.9739049138432397</v>
+        <v>0.9739097777274405</v>
       </c>
       <c r="S100" t="n">
-        <v>0.9841560705425476</v>
+        <v>0.9841617382608713</v>
       </c>
       <c r="T100" t="n">
-        <v>0.9947291513982695</v>
+        <v>0.99473567719356</v>
       </c>
       <c r="U100" t="n">
-        <v>1.010197259220105</v>
+        <v>1.010205451434783</v>
       </c>
       <c r="V100" t="n">
-        <v>1.028389916688732</v>
+        <v>1.028400469705168</v>
       </c>
     </row>
     <row r="101">
@@ -8050,58 +8050,58 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>2.398120083787964</v>
+        <v>2.398119901211559</v>
       </c>
       <c r="F101" t="n">
-        <v>2.462145155708597</v>
+        <v>2.462144796717964</v>
       </c>
       <c r="G101" t="n">
-        <v>2.390273844770802</v>
+        <v>2.39027331325012</v>
       </c>
       <c r="H101" t="n">
-        <v>2.258387139438128</v>
+        <v>2.258386611812345</v>
       </c>
       <c r="I101" t="n">
-        <v>2.1372632006933</v>
+        <v>2.137262850187827</v>
       </c>
       <c r="J101" t="n">
-        <v>2.007307104203048</v>
+        <v>2.007306753860036</v>
       </c>
       <c r="K101" t="n">
-        <v>1.894456783528399</v>
+        <v>1.894456608035739</v>
       </c>
       <c r="L101" t="n">
-        <v>1.77460554874611</v>
+        <v>1.774605372614451</v>
       </c>
       <c r="M101" t="n">
-        <v>1.703511544403526</v>
+        <v>1.703511190470713</v>
       </c>
       <c r="N101" t="n">
-        <v>1.678394411305867</v>
+        <v>1.67839423325847</v>
       </c>
       <c r="O101" t="n">
-        <v>1.672657140635754</v>
+        <v>1.67265696107775</v>
       </c>
       <c r="P101" t="n">
-        <v>1.69650023780738</v>
+        <v>1.696500056275029</v>
       </c>
       <c r="Q101" t="n">
-        <v>1.72352136277662</v>
+        <v>1.723520994649642</v>
       </c>
       <c r="R101" t="n">
-        <v>1.742469193987868</v>
+        <v>1.742468819344201</v>
       </c>
       <c r="S101" t="n">
-        <v>1.76145403005224</v>
+        <v>1.761453647396641</v>
       </c>
       <c r="T101" t="n">
-        <v>1.77884476425279</v>
+        <v>1.778844372074472</v>
       </c>
       <c r="U101" t="n">
-        <v>1.805816153817759</v>
+        <v>1.805815548674403</v>
       </c>
       <c r="V101" t="n">
-        <v>1.840979974318133</v>
+        <v>1.840979348541648</v>
       </c>
     </row>
     <row r="102">
@@ -8126,58 +8126,58 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1.474233451480413</v>
+        <v>1.47423371490181</v>
       </c>
       <c r="F102" t="n">
-        <v>1.588607393039346</v>
+        <v>1.588607831472387</v>
       </c>
       <c r="G102" t="n">
-        <v>1.634547379804043</v>
+        <v>1.634547882911024</v>
       </c>
       <c r="H102" t="n">
-        <v>1.625256060880563</v>
+        <v>1.62525658432917</v>
       </c>
       <c r="I102" t="n">
-        <v>1.602917130305455</v>
+        <v>1.602917660042001</v>
       </c>
       <c r="J102" t="n">
-        <v>1.552148425377805</v>
+        <v>1.552148962620227</v>
       </c>
       <c r="K102" t="n">
-        <v>1.496755378208166</v>
+        <v>1.496755938901778</v>
       </c>
       <c r="L102" t="n">
-        <v>1.422756161227432</v>
+        <v>1.422756747409529</v>
       </c>
       <c r="M102" t="n">
-        <v>1.378549333221826</v>
+        <v>1.378549960449792</v>
       </c>
       <c r="N102" t="n">
-        <v>1.365184964837336</v>
+        <v>1.365185662467723</v>
       </c>
       <c r="O102" t="n">
-        <v>1.363461930288862</v>
+        <v>1.363462714482103</v>
       </c>
       <c r="P102" t="n">
-        <v>1.383388558834843</v>
+        <v>1.383389460284049</v>
       </c>
       <c r="Q102" t="n">
-        <v>1.404642308304612</v>
+        <v>1.404643345015982</v>
       </c>
       <c r="R102" t="n">
-        <v>1.418868589005201</v>
+        <v>1.418869781107109</v>
       </c>
       <c r="S102" t="n">
-        <v>1.434820319146626</v>
+        <v>1.43482170381289</v>
       </c>
       <c r="T102" t="n">
-        <v>1.452652881054852</v>
+        <v>1.452654487284167</v>
       </c>
       <c r="U102" t="n">
-        <v>1.478660155096479</v>
+        <v>1.478662106494175</v>
       </c>
       <c r="V102" t="n">
-        <v>1.510078059530846</v>
+        <v>1.510080538557574</v>
       </c>
     </row>
     <row r="103">
@@ -8202,58 +8202,58 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>2.737814972364542</v>
+        <v>2.7378145697465</v>
       </c>
       <c r="F103" t="n">
-        <v>2.604803631921294</v>
+        <v>2.604803128783123</v>
       </c>
       <c r="G103" t="n">
-        <v>2.332006017794871</v>
+        <v>2.332005720937441</v>
       </c>
       <c r="H103" t="n">
-        <v>2.078635072102474</v>
+        <v>2.078635059595324</v>
       </c>
       <c r="I103" t="n">
-        <v>1.901630452340083</v>
+        <v>1.901630718387459</v>
       </c>
       <c r="J103" t="n">
-        <v>1.757675224035338</v>
+        <v>1.757675686878424</v>
       </c>
       <c r="K103" t="n">
-        <v>1.653077956118816</v>
+        <v>1.653078557929875</v>
       </c>
       <c r="L103" t="n">
-        <v>1.554946425510086</v>
+        <v>1.554947106974872</v>
       </c>
       <c r="M103" t="n">
-        <v>1.504631857832138</v>
+        <v>1.504632597353936</v>
       </c>
       <c r="N103" t="n">
-        <v>1.493904481824476</v>
+        <v>1.493905297709361</v>
       </c>
       <c r="O103" t="n">
-        <v>1.498303508415302</v>
+        <v>1.498304392231057</v>
       </c>
       <c r="P103" t="n">
-        <v>1.526804170088559</v>
+        <v>1.526805141544929</v>
       </c>
       <c r="Q103" t="n">
-        <v>1.557646662828538</v>
+        <v>1.557647728689311</v>
       </c>
       <c r="R103" t="n">
-        <v>1.582709316401314</v>
+        <v>1.582710485592205</v>
       </c>
       <c r="S103" t="n">
-        <v>1.609595734303107</v>
+        <v>1.609597001196547</v>
       </c>
       <c r="T103" t="n">
-        <v>1.634939025568508</v>
+        <v>1.634940453072293</v>
       </c>
       <c r="U103" t="n">
-        <v>1.666770077378419</v>
+        <v>1.666771773233858</v>
       </c>
       <c r="V103" t="n">
-        <v>1.707900481138017</v>
+        <v>1.707902537694078</v>
       </c>
     </row>
     <row r="104">
@@ -8278,22 +8278,22 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1.736525416979892</v>
+        <v>1.736525592006868</v>
       </c>
       <c r="F104" t="n">
-        <v>1.85201415633518</v>
+        <v>1.852014420117823</v>
       </c>
       <c r="G104" t="n">
-        <v>1.870072520875209</v>
+        <v>1.870072786519441</v>
       </c>
       <c r="H104" t="n">
-        <v>1.851943887310259</v>
+        <v>1.85194406591071</v>
       </c>
       <c r="I104" t="n">
-        <v>1.834854820342706</v>
+        <v>1.834855000382585</v>
       </c>
       <c r="J104" t="n">
-        <v>1.791550871788071</v>
+        <v>1.79155096261352</v>
       </c>
       <c r="K104" t="n">
         <v>1.740409040536492</v>
@@ -8302,22 +8302,22 @@
         <v>1.660937905658439</v>
       </c>
       <c r="M104" t="n">
-        <v>1.612459058897993</v>
+        <v>1.612458963575288</v>
       </c>
       <c r="N104" t="n">
-        <v>1.598472456567929</v>
+        <v>1.598472358923885</v>
       </c>
       <c r="O104" t="n">
-        <v>1.598477411344036</v>
+        <v>1.598477310852421</v>
       </c>
       <c r="P104" t="n">
-        <v>1.622872968247978</v>
+        <v>1.622872864457422</v>
       </c>
       <c r="Q104" t="n">
-        <v>1.6461727222235</v>
+        <v>1.64617261470996</v>
       </c>
       <c r="R104" t="n">
-        <v>1.658239817645805</v>
+        <v>1.658239706018604</v>
       </c>
       <c r="S104" t="n">
         <v>1.669912717606572</v>
@@ -8354,37 +8354,37 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>2.263469276094276</v>
+        <v>2.263469065656566</v>
       </c>
       <c r="F105" t="n">
-        <v>2.324493830445019</v>
+        <v>2.32449342977253</v>
       </c>
       <c r="G105" t="n">
-        <v>2.301827382842189</v>
+        <v>2.301826998008485</v>
       </c>
       <c r="H105" t="n">
-        <v>2.209354335041775</v>
+        <v>2.209353962710667</v>
       </c>
       <c r="I105" t="n">
-        <v>2.110047640242172</v>
+        <v>2.110047278824714</v>
       </c>
       <c r="J105" t="n">
-        <v>1.983995536633283</v>
+        <v>1.98399518474376</v>
       </c>
       <c r="K105" t="n">
-        <v>1.866376142622396</v>
+        <v>1.866375798562656</v>
       </c>
       <c r="L105" t="n">
-        <v>1.73961356343188</v>
+        <v>1.739613394243431</v>
       </c>
       <c r="M105" t="n">
-        <v>1.663027803764873</v>
+        <v>1.663027636376175</v>
       </c>
       <c r="N105" t="n">
-        <v>1.633098401779258</v>
+        <v>1.633098235232005</v>
       </c>
       <c r="O105" t="n">
-        <v>1.622591522439107</v>
+        <v>1.622591355700437</v>
       </c>
       <c r="P105" t="n">
         <v>1.638678976881945</v>
@@ -8393,19 +8393,19 @@
         <v>1.654558679404745</v>
       </c>
       <c r="R105" t="n">
-        <v>1.6595407887192</v>
+        <v>1.659540960552699</v>
       </c>
       <c r="S105" t="n">
-        <v>1.664430197731985</v>
+        <v>1.664430547335029</v>
       </c>
       <c r="T105" t="n">
-        <v>1.670114277486998</v>
+        <v>1.670114634308652</v>
       </c>
       <c r="U105" t="n">
-        <v>1.687553453712922</v>
+        <v>1.687554001956132</v>
       </c>
       <c r="V105" t="n">
-        <v>1.713551264443204</v>
+        <v>1.713552016595488</v>
       </c>
     </row>
     <row r="106">
@@ -8430,58 +8430,58 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1.648448483896369</v>
+        <v>1.648448663158773</v>
       </c>
       <c r="F106" t="n">
-        <v>1.833580981312581</v>
+        <v>1.833581209279423</v>
       </c>
       <c r="G106" t="n">
-        <v>1.964049503557628</v>
+        <v>1.964049568838192</v>
       </c>
       <c r="H106" t="n">
-        <v>2.011785775245154</v>
+        <v>2.011785660470416</v>
       </c>
       <c r="I106" t="n">
-        <v>2.025351380193699</v>
+        <v>2.025351066903053</v>
       </c>
       <c r="J106" t="n">
-        <v>1.987173393084843</v>
+        <v>1.987172911467832</v>
       </c>
       <c r="K106" t="n">
-        <v>1.93126265600116</v>
+        <v>1.931262051735853</v>
       </c>
       <c r="L106" t="n">
-        <v>1.842705828738001</v>
+        <v>1.842705147022232</v>
       </c>
       <c r="M106" t="n">
-        <v>1.791594516487897</v>
+        <v>1.791593716767035</v>
       </c>
       <c r="N106" t="n">
-        <v>1.780899981462517</v>
+        <v>1.780899073286097</v>
       </c>
       <c r="O106" t="n">
-        <v>1.785621241328468</v>
+        <v>1.785620197062204</v>
       </c>
       <c r="P106" t="n">
-        <v>1.816270241260519</v>
+        <v>1.816269031839888</v>
       </c>
       <c r="Q106" t="n">
-        <v>1.84513183519225</v>
+        <v>1.845130429928679</v>
       </c>
       <c r="R106" t="n">
-        <v>1.861800487796119</v>
+        <v>1.861798873779677</v>
       </c>
       <c r="S106" t="n">
-        <v>1.880131091376731</v>
+        <v>1.880129233493911</v>
       </c>
       <c r="T106" t="n">
-        <v>1.903433446822397</v>
+        <v>1.903431215032126</v>
       </c>
       <c r="U106" t="n">
-        <v>1.942595601384945</v>
+        <v>1.942592776718967</v>
       </c>
       <c r="V106" t="n">
-        <v>1.990717826850527</v>
+        <v>1.990714134045508</v>
       </c>
     </row>
     <row r="107">
@@ -8506,58 +8506,58 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>4.82057630024594</v>
+        <v>4.82057448786703</v>
       </c>
       <c r="F107" t="n">
-        <v>5.29088299707709</v>
+        <v>5.290879604262053</v>
       </c>
       <c r="G107" t="n">
-        <v>5.206794555166274</v>
+        <v>5.206789768920031</v>
       </c>
       <c r="H107" t="n">
-        <v>4.925778979517584</v>
+        <v>4.92577294062409</v>
       </c>
       <c r="I107" t="n">
-        <v>4.674573794517067</v>
+        <v>4.674568052925986</v>
       </c>
       <c r="J107" t="n">
-        <v>4.415557625126357</v>
+        <v>4.415550767196602</v>
       </c>
       <c r="K107" t="n">
-        <v>4.194663119819459</v>
+        <v>4.194655210596251</v>
       </c>
       <c r="L107" t="n">
-        <v>3.950177078472918</v>
+        <v>3.950169429294822</v>
       </c>
       <c r="M107" t="n">
-        <v>3.80259372964927</v>
+        <v>3.802586287096474</v>
       </c>
       <c r="N107" t="n">
-        <v>3.743040472042299</v>
+        <v>3.743031973338351</v>
       </c>
       <c r="O107" t="n">
-        <v>3.71689169039067</v>
+        <v>3.716880911289192</v>
       </c>
       <c r="P107" t="n">
-        <v>3.74738395444457</v>
+        <v>3.747372053862037</v>
       </c>
       <c r="Q107" t="n">
-        <v>3.777541580623417</v>
+        <v>3.777528480613176</v>
       </c>
       <c r="R107" t="n">
-        <v>3.784942958477612</v>
+        <v>3.784928555568225</v>
       </c>
       <c r="S107" t="n">
-        <v>3.791808246071704</v>
+        <v>3.791791195648732</v>
       </c>
       <c r="T107" t="n">
-        <v>3.795245497960402</v>
+        <v>3.795225599442841</v>
       </c>
       <c r="U107" t="n">
-        <v>3.818418718544477</v>
+        <v>3.818394435966843</v>
       </c>
       <c r="V107" t="n">
-        <v>3.857949077083364</v>
+        <v>3.857919952553493</v>
       </c>
     </row>
     <row r="108">
@@ -8582,58 +8582,58 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>2.864520135894281</v>
+        <v>2.864519603300425</v>
       </c>
       <c r="F108" t="n">
-        <v>2.988202988799291</v>
+        <v>2.988201939279446</v>
       </c>
       <c r="G108" t="n">
-        <v>2.900332578781543</v>
+        <v>2.90033131159533</v>
       </c>
       <c r="H108" t="n">
-        <v>2.734877429353864</v>
+        <v>2.734876057806164</v>
       </c>
       <c r="I108" t="n">
-        <v>2.58721140325269</v>
+        <v>2.587209923670638</v>
       </c>
       <c r="J108" t="n">
-        <v>2.433325881480268</v>
+        <v>2.43332440248653</v>
       </c>
       <c r="K108" t="n">
-        <v>2.301042503789885</v>
+        <v>2.301040962722142</v>
       </c>
       <c r="L108" t="n">
-        <v>2.160730978477887</v>
+        <v>2.160729369734597</v>
       </c>
       <c r="M108" t="n">
-        <v>2.079040266768355</v>
+        <v>2.079038586136993</v>
       </c>
       <c r="N108" t="n">
-        <v>2.051289496556992</v>
+        <v>2.05128762360736</v>
       </c>
       <c r="O108" t="n">
-        <v>2.044668498834272</v>
+        <v>2.044666426692969</v>
       </c>
       <c r="P108" t="n">
-        <v>2.072605197311103</v>
+        <v>2.072602798865775</v>
       </c>
       <c r="Q108" t="n">
-        <v>2.103982698357962</v>
+        <v>2.103979961526228</v>
       </c>
       <c r="R108" t="n">
-        <v>2.127038679957626</v>
+        <v>2.127035526044826</v>
       </c>
       <c r="S108" t="n">
-        <v>2.154397776701283</v>
+        <v>2.154394055224197</v>
       </c>
       <c r="T108" t="n">
-        <v>2.182785742410648</v>
+        <v>2.182781288527701</v>
       </c>
       <c r="U108" t="n">
-        <v>2.221403931910495</v>
+        <v>2.221398432271616</v>
       </c>
       <c r="V108" t="n">
-        <v>2.268700747418503</v>
+        <v>2.268693771786029</v>
       </c>
     </row>
     <row r="109">
@@ -8658,58 +8658,58 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>1.37491053556223</v>
+        <v>1.374910906591521</v>
       </c>
       <c r="F109" t="n">
-        <v>1.450611307554005</v>
+        <v>1.450612044790823</v>
       </c>
       <c r="G109" t="n">
-        <v>1.517445778396949</v>
+        <v>1.517446696745648</v>
       </c>
       <c r="H109" t="n">
-        <v>1.578368320733222</v>
+        <v>1.578369146268306</v>
       </c>
       <c r="I109" t="n">
-        <v>1.65003937300213</v>
+        <v>1.650040014704143</v>
       </c>
       <c r="J109" t="n">
-        <v>1.683589875369395</v>
+        <v>1.683590334244966</v>
       </c>
       <c r="K109" t="n">
-        <v>1.68955732718894</v>
+        <v>1.689557603686636</v>
       </c>
       <c r="L109" t="n">
-        <v>1.650074942039557</v>
+        <v>1.650075034962111</v>
       </c>
       <c r="M109" t="n">
         <v>1.627612578975979</v>
       </c>
       <c r="N109" t="n">
-        <v>1.630897070239581</v>
+        <v>1.630896974754771</v>
       </c>
       <c r="O109" t="n">
-        <v>1.642506412391252</v>
+        <v>1.642506217633735</v>
       </c>
       <c r="P109" t="n">
-        <v>1.675892407618801</v>
+        <v>1.675892208225952</v>
       </c>
       <c r="Q109" t="n">
-        <v>1.706902210153575</v>
+        <v>1.706901902860591</v>
       </c>
       <c r="R109" t="n">
-        <v>1.725131482357788</v>
+        <v>1.725131165761694</v>
       </c>
       <c r="S109" t="n">
-        <v>1.742243249026144</v>
+        <v>1.742242813247497</v>
       </c>
       <c r="T109" t="n">
-        <v>1.759710179744358</v>
+        <v>1.759709729020022</v>
       </c>
       <c r="U109" t="n">
-        <v>1.788891806747231</v>
+        <v>1.78889122265637</v>
       </c>
       <c r="V109" t="n">
-        <v>1.82768284906897</v>
+        <v>1.827682119092498</v>
       </c>
     </row>
     <row r="110">
@@ -8734,58 +8734,58 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>1.257656846066869</v>
+        <v>1.257657256484079</v>
       </c>
       <c r="F110" t="n">
-        <v>1.369756585660647</v>
+        <v>1.369757180079058</v>
       </c>
       <c r="G110" t="n">
-        <v>1.42053613512333</v>
+        <v>1.420536807092151</v>
       </c>
       <c r="H110" t="n">
-        <v>1.409709103443625</v>
+        <v>1.409709852790756</v>
       </c>
       <c r="I110" t="n">
-        <v>1.375549905539106</v>
+        <v>1.375550823080572</v>
       </c>
       <c r="J110" t="n">
-        <v>1.313740330208635</v>
+        <v>1.313741320366467</v>
       </c>
       <c r="K110" t="n">
-        <v>1.249310932183988</v>
+        <v>1.249311992900272</v>
       </c>
       <c r="L110" t="n">
-        <v>1.173466849543345</v>
+        <v>1.173468067174999</v>
       </c>
       <c r="M110" t="n">
-        <v>1.127316974383793</v>
+        <v>1.127318261544112</v>
       </c>
       <c r="N110" t="n">
-        <v>1.110914095653171</v>
+        <v>1.110915624880529</v>
       </c>
       <c r="O110" t="n">
-        <v>1.10734064023769</v>
+        <v>1.107342415810376</v>
       </c>
       <c r="P110" t="n">
-        <v>1.122549167058156</v>
+        <v>1.122551194914137</v>
       </c>
       <c r="Q110" t="n">
-        <v>1.138799843362751</v>
+        <v>1.138802131893988</v>
       </c>
       <c r="R110" t="n">
-        <v>1.148701076884976</v>
+        <v>1.148703724262791</v>
       </c>
       <c r="S110" t="n">
-        <v>1.158827176399988</v>
+        <v>1.158830375780173</v>
       </c>
       <c r="T110" t="n">
-        <v>1.168224228339521</v>
+        <v>1.168227924178974</v>
       </c>
       <c r="U110" t="n">
-        <v>1.183144529457185</v>
+        <v>1.183149209057547</v>
       </c>
       <c r="V110" t="n">
-        <v>1.203161757351007</v>
+        <v>1.203167684835642</v>
       </c>
     </row>
     <row r="111">
@@ -8810,58 +8810,58 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>1.64761078531562</v>
+        <v>1.647610973980033</v>
       </c>
       <c r="F111" t="n">
-        <v>1.769880023661371</v>
+        <v>1.769880312214667</v>
       </c>
       <c r="G111" t="n">
-        <v>1.788364654830676</v>
+        <v>1.788365021505477</v>
       </c>
       <c r="H111" t="n">
-        <v>1.743560163147314</v>
+        <v>1.74356054691879</v>
       </c>
       <c r="I111" t="n">
-        <v>1.695977506216847</v>
+        <v>1.695977946737454</v>
       </c>
       <c r="J111" t="n">
-        <v>1.627497125107002</v>
+        <v>1.627497601773198</v>
       </c>
       <c r="K111" t="n">
-        <v>1.55760454300994</v>
+        <v>1.557605076672484</v>
       </c>
       <c r="L111" t="n">
-        <v>1.468079357847983</v>
+        <v>1.468079951304883</v>
       </c>
       <c r="M111" t="n">
-        <v>1.412951373254842</v>
+        <v>1.412952050338372</v>
       </c>
       <c r="N111" t="n">
-        <v>1.393183494365422</v>
+        <v>1.393184280248226</v>
       </c>
       <c r="O111" t="n">
-        <v>1.388462835225784</v>
+        <v>1.388463717088573</v>
       </c>
       <c r="P111" t="n">
-        <v>1.405115481741499</v>
+        <v>1.405116529575103</v>
       </c>
       <c r="Q111" t="n">
-        <v>1.419639689065501</v>
+        <v>1.41964095644988</v>
       </c>
       <c r="R111" t="n">
-        <v>1.422388565128888</v>
+        <v>1.422390088330225</v>
       </c>
       <c r="S111" t="n">
-        <v>1.422744107740282</v>
+        <v>1.422746016514075</v>
       </c>
       <c r="T111" t="n">
-        <v>1.425222331500108</v>
+        <v>1.425224700534159</v>
       </c>
       <c r="U111" t="n">
-        <v>1.441019511117172</v>
+        <v>1.441022501270815</v>
       </c>
       <c r="V111" t="n">
-        <v>1.466039546724198</v>
+        <v>1.466043419188999</v>
       </c>
     </row>
     <row r="112">
@@ -8886,58 +8886,58 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>1.856489932673037</v>
+        <v>1.85648997954614</v>
       </c>
       <c r="F112" t="n">
         <v>2.005702907009407</v>
       </c>
       <c r="G112" t="n">
-        <v>2.075525078988647</v>
+        <v>2.075524944920222</v>
       </c>
       <c r="H112" t="n">
-        <v>2.070151151013141</v>
+        <v>2.07015087263143</v>
       </c>
       <c r="I112" t="n">
-        <v>2.043914474040757</v>
+        <v>2.043914069383908</v>
       </c>
       <c r="J112" t="n">
-        <v>1.978100768160476</v>
+        <v>1.978100268074604</v>
       </c>
       <c r="K112" t="n">
-        <v>1.90418725280003</v>
+        <v>1.904186672277441</v>
       </c>
       <c r="L112" t="n">
-        <v>1.805054907187343</v>
+        <v>1.805054273740327</v>
       </c>
       <c r="M112" t="n">
-        <v>1.743727047756112</v>
+        <v>1.743726373799954</v>
       </c>
       <c r="N112" t="n">
-        <v>1.722800588931412</v>
+        <v>1.722799858177536</v>
       </c>
       <c r="O112" t="n">
-        <v>1.718106569769658</v>
+        <v>1.718105765117924</v>
       </c>
       <c r="P112" t="n">
-        <v>1.741609039893096</v>
+        <v>1.741608129977964</v>
       </c>
       <c r="Q112" t="n">
-        <v>1.767280225943451</v>
+        <v>1.767279192507937</v>
       </c>
       <c r="R112" t="n">
-        <v>1.784381991998472</v>
+        <v>1.784380800170228</v>
       </c>
       <c r="S112" t="n">
-        <v>1.802811034842495</v>
+        <v>1.802809646618797</v>
       </c>
       <c r="T112" t="n">
-        <v>1.82028378914039</v>
+        <v>1.820282178293095</v>
       </c>
       <c r="U112" t="n">
-        <v>1.846648375865499</v>
+        <v>1.846646436802553</v>
       </c>
       <c r="V112" t="n">
-        <v>1.880679227532779</v>
+        <v>1.88067682827213</v>
       </c>
     </row>
     <row r="113">
@@ -8962,58 +8962,58 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>1.667505774447999</v>
+        <v>1.667505880771843</v>
       </c>
       <c r="F113" t="n">
-        <v>1.835182016448948</v>
+        <v>1.835181907744446</v>
       </c>
       <c r="G113" t="n">
-        <v>1.606598192126755</v>
+        <v>1.606597523146979</v>
       </c>
       <c r="H113" t="n">
-        <v>1.481111721882322</v>
+        <v>1.481110345352883</v>
       </c>
       <c r="I113" t="n">
-        <v>1.425699722823103</v>
+        <v>1.425697596508686</v>
       </c>
       <c r="J113" t="n">
-        <v>1.421319265147984</v>
+        <v>1.421316463270678</v>
       </c>
       <c r="K113" t="n">
-        <v>1.435714097605778</v>
+        <v>1.435710569446214</v>
       </c>
       <c r="L113" t="n">
-        <v>1.455303217889811</v>
+        <v>1.455298899031372</v>
       </c>
       <c r="M113" t="n">
-        <v>1.488037554402652</v>
+        <v>1.48803250764788</v>
       </c>
       <c r="N113" t="n">
-        <v>1.523093713720061</v>
+        <v>1.52308758390716</v>
       </c>
       <c r="O113" t="n">
-        <v>1.525279040752929</v>
+        <v>1.525271863625</v>
       </c>
       <c r="P113" t="n">
-        <v>1.549072765915528</v>
+        <v>1.549064425639833</v>
       </c>
       <c r="Q113" t="n">
-        <v>1.554210759132088</v>
+        <v>1.554200954959632</v>
       </c>
       <c r="R113" t="n">
-        <v>1.515534490077059</v>
+        <v>1.51552322720659</v>
       </c>
       <c r="S113" t="n">
-        <v>1.505896168722744</v>
+        <v>1.505882910932672</v>
       </c>
       <c r="T113" t="n">
-        <v>1.494940008881699</v>
+        <v>1.494924346957225</v>
       </c>
       <c r="U113" t="n">
-        <v>1.488615844258289</v>
+        <v>1.488596681671744</v>
       </c>
       <c r="V113" t="n">
-        <v>1.484975468323854</v>
+        <v>1.484951277116551</v>
       </c>
     </row>
     <row r="114">
@@ -9038,58 +9038,58 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>0.6530752490443303</v>
+        <v>0.6530746550917181</v>
       </c>
       <c r="F114" t="n">
-        <v>1.052444864320014</v>
+        <v>1.052444234926255</v>
       </c>
       <c r="G114" t="n">
-        <v>1.426681656336145</v>
+        <v>1.426680986356877</v>
       </c>
       <c r="H114" t="n">
-        <v>1.788090806045521</v>
+        <v>1.788090447796698</v>
       </c>
       <c r="I114" t="n">
         <v>2.057969085923288</v>
       </c>
       <c r="J114" t="n">
-        <v>2.235336732645841</v>
+        <v>2.235337147331003</v>
       </c>
       <c r="K114" t="n">
-        <v>2.335283900007099</v>
+        <v>2.335284798609683</v>
       </c>
       <c r="L114" t="n">
-        <v>2.384771416723392</v>
+        <v>2.384771905734338</v>
       </c>
       <c r="M114" t="n">
-        <v>2.435368033502826</v>
+        <v>2.435369101287963</v>
       </c>
       <c r="N114" t="n">
-        <v>2.485334997082202</v>
+        <v>2.48533616654017</v>
       </c>
       <c r="O114" t="n">
-        <v>2.483119365803061</v>
+        <v>2.483120647941463</v>
       </c>
       <c r="P114" t="n">
-        <v>2.522876590290469</v>
+        <v>2.522877998795728</v>
       </c>
       <c r="Q114" t="n">
-        <v>2.537357467692159</v>
+        <v>2.537359019275317</v>
       </c>
       <c r="R114" t="n">
-        <v>2.480615113408325</v>
+        <v>2.480616824909184</v>
       </c>
       <c r="S114" t="n">
-        <v>2.468949673546419</v>
+        <v>2.468952501616714</v>
       </c>
       <c r="T114" t="n">
-        <v>2.452910522391379</v>
+        <v>2.452912590735679</v>
       </c>
       <c r="U114" t="n">
-        <v>2.442554420613545</v>
+        <v>2.442557805506318</v>
       </c>
       <c r="V114" t="n">
-        <v>2.436672437473734</v>
+        <v>2.436676113147025</v>
       </c>
     </row>
     <row r="115">
@@ -9114,58 +9114,58 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>1.361070384012957</v>
+        <v>1.361070406729569</v>
       </c>
       <c r="F115" t="n">
-        <v>1.738110356089548</v>
+        <v>1.738110426416185</v>
       </c>
       <c r="G115" t="n">
-        <v>1.912164931427069</v>
+        <v>1.912165124593656</v>
       </c>
       <c r="H115" t="n">
-        <v>2.086318300754959</v>
+        <v>2.086318623854488</v>
       </c>
       <c r="I115" t="n">
-        <v>2.219159569650485</v>
+        <v>2.219160029141971</v>
       </c>
       <c r="J115" t="n">
-        <v>2.316453854844263</v>
+        <v>2.316454430848703</v>
       </c>
       <c r="K115" t="n">
-        <v>2.374943739622459</v>
+        <v>2.37494443817538</v>
       </c>
       <c r="L115" t="n">
-        <v>2.407393221085905</v>
+        <v>2.407394077051238</v>
       </c>
       <c r="M115" t="n">
-        <v>2.451696024903031</v>
+        <v>2.451697018797961</v>
       </c>
       <c r="N115" t="n">
-        <v>2.500727976937513</v>
+        <v>2.500729145486712</v>
       </c>
       <c r="O115" t="n">
-        <v>2.503145689068778</v>
+        <v>2.50314704708952</v>
       </c>
       <c r="P115" t="n">
-        <v>2.546068855394783</v>
+        <v>2.546070451544494</v>
       </c>
       <c r="Q115" t="n">
-        <v>2.559790248647909</v>
+        <v>2.559792106296614</v>
       </c>
       <c r="R115" t="n">
-        <v>2.501077356837318</v>
+        <v>2.501079469034508</v>
       </c>
       <c r="S115" t="n">
-        <v>2.488974767171171</v>
+        <v>2.488977196565123</v>
       </c>
       <c r="T115" t="n">
-        <v>2.474223602134439</v>
+        <v>2.474226457470706</v>
       </c>
       <c r="U115" t="n">
-        <v>2.466350217283177</v>
+        <v>2.466353704911016</v>
       </c>
       <c r="V115" t="n">
-        <v>2.460697169621632</v>
+        <v>2.46070157719914</v>
       </c>
     </row>
     <row r="116">
@@ -9190,58 +9190,58 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>0.4679027670860572</v>
+        <v>0.4679024576793507</v>
       </c>
       <c r="F116" t="n">
-        <v>0.5260636077387322</v>
+        <v>0.526062684174167</v>
       </c>
       <c r="G116" t="n">
-        <v>0.5451635762044211</v>
+        <v>0.5451620363883183</v>
       </c>
       <c r="H116" t="n">
-        <v>0.5556644903479536</v>
+        <v>0.555662940042559</v>
       </c>
       <c r="I116" t="n">
-        <v>0.5584013505297613</v>
+        <v>0.5583991556680579</v>
       </c>
       <c r="J116" t="n">
-        <v>0.5532946486137975</v>
+        <v>0.5532921014717704</v>
       </c>
       <c r="K116" t="n">
-        <v>0.544405893179544</v>
+        <v>0.544402970168726</v>
       </c>
       <c r="L116" t="n">
-        <v>0.5306524135800661</v>
+        <v>0.5306490848714187</v>
       </c>
       <c r="M116" t="n">
-        <v>0.5242608751955748</v>
+        <v>0.5242574493166913</v>
       </c>
       <c r="N116" t="n">
-        <v>0.5260529801465191</v>
+        <v>0.5260487313677775</v>
       </c>
       <c r="O116" t="n">
-        <v>0.5306528407354355</v>
+        <v>0.5306484219363914</v>
       </c>
       <c r="P116" t="n">
-        <v>0.5399439071201246</v>
+        <v>0.5399388940069775</v>
       </c>
       <c r="Q116" t="n">
-        <v>0.5463135404640385</v>
+        <v>0.5463082519512579</v>
       </c>
       <c r="R116" t="n">
-        <v>0.542243715839438</v>
+        <v>0.5422380980367076</v>
       </c>
       <c r="S116" t="n">
-        <v>0.5434335366332246</v>
+        <v>0.5434275345925307</v>
       </c>
       <c r="T116" t="n">
-        <v>0.5419568177012064</v>
+        <v>0.5419503795301818</v>
       </c>
       <c r="U116" t="n">
-        <v>0.5417355765876181</v>
+        <v>0.541728652305706</v>
       </c>
       <c r="V116" t="n">
-        <v>0.5428903257199649</v>
+        <v>0.5428822923193805</v>
       </c>
     </row>
     <row r="117">
@@ -9266,58 +9266,58 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>1.73249009044683</v>
+        <v>1.732490358001421</v>
       </c>
       <c r="F117" t="n">
-        <v>2.443223661104513</v>
+        <v>2.443224742586911</v>
       </c>
       <c r="G117" t="n">
-        <v>2.834498332681637</v>
+        <v>2.834500254820725</v>
       </c>
       <c r="H117" t="n">
-        <v>3.079952962248391</v>
+        <v>3.079956046507259</v>
       </c>
       <c r="I117" t="n">
-        <v>3.210435568399419</v>
+        <v>3.210439594889119</v>
       </c>
       <c r="J117" t="n">
-        <v>3.25033109322013</v>
+        <v>3.250336135625274</v>
       </c>
       <c r="K117" t="n">
-        <v>3.241059572092337</v>
+        <v>3.241065108960961</v>
       </c>
       <c r="L117" t="n">
-        <v>3.188925882880921</v>
+        <v>3.188932298642136</v>
       </c>
       <c r="M117" t="n">
-        <v>3.165654752021533</v>
+        <v>3.165661810327848</v>
       </c>
       <c r="N117" t="n">
-        <v>3.180380708084079</v>
+        <v>3.180388487595745</v>
       </c>
       <c r="O117" t="n">
-        <v>3.213756800199905</v>
+        <v>3.21376577797878</v>
       </c>
       <c r="P117" t="n">
-        <v>3.284924593925978</v>
+        <v>3.284934142523965</v>
       </c>
       <c r="Q117" t="n">
-        <v>3.354023650492325</v>
+        <v>3.354034284323988</v>
       </c>
       <c r="R117" t="n">
-        <v>3.370813272597095</v>
+        <v>3.370825144656477</v>
       </c>
       <c r="S117" t="n">
-        <v>3.426797357678932</v>
+        <v>3.42681013390964</v>
       </c>
       <c r="T117" t="n">
-        <v>3.465291119455778</v>
+        <v>3.465305405449736</v>
       </c>
       <c r="U117" t="n">
-        <v>3.509071568042601</v>
+        <v>3.509087521558613</v>
       </c>
       <c r="V117" t="n">
-        <v>3.565413818097902</v>
+        <v>3.565431003107418</v>
       </c>
     </row>
     <row r="118">
@@ -9345,55 +9345,55 @@
         <v>1.284449441344303</v>
       </c>
       <c r="F118" t="n">
-        <v>1.4346874253386</v>
+        <v>1.434687193380854</v>
       </c>
       <c r="G118" t="n">
         <v>1.464477317354579</v>
       </c>
       <c r="H118" t="n">
-        <v>1.472473612144343</v>
+        <v>1.472473372554234</v>
       </c>
       <c r="I118" t="n">
-        <v>1.46491748788892</v>
+        <v>1.464917243701616</v>
       </c>
       <c r="J118" t="n">
-        <v>1.439770531608755</v>
+        <v>1.439770282262478</v>
       </c>
       <c r="K118" t="n">
-        <v>1.406720262915746</v>
+        <v>1.406720007598249</v>
       </c>
       <c r="L118" t="n">
-        <v>1.361803239441163</v>
+        <v>1.361802977218918</v>
       </c>
       <c r="M118" t="n">
-        <v>1.335538738073293</v>
+        <v>1.335538198128443</v>
       </c>
       <c r="N118" t="n">
-        <v>1.33171575674501</v>
+        <v>1.331715199536402</v>
       </c>
       <c r="O118" t="n">
-        <v>1.340535748280523</v>
+        <v>1.340535170523532</v>
       </c>
       <c r="P118" t="n">
-        <v>1.366321953733139</v>
+        <v>1.366321050765446</v>
       </c>
       <c r="Q118" t="n">
-        <v>1.391158054363538</v>
+        <v>1.391157108943578</v>
       </c>
       <c r="R118" t="n">
-        <v>1.394641079752064</v>
+        <v>1.39464041685573</v>
       </c>
       <c r="S118" t="n">
-        <v>1.415207524342752</v>
+        <v>1.415206824612183</v>
       </c>
       <c r="T118" t="n">
-        <v>1.430141027355373</v>
+        <v>1.4301402865293</v>
       </c>
       <c r="U118" t="n">
-        <v>1.448349925586576</v>
+        <v>1.448349138975329</v>
       </c>
       <c r="V118" t="n">
-        <v>1.470600332736329</v>
+        <v>1.470599913883951</v>
       </c>
     </row>
     <row r="119">
@@ -9421,55 +9421,55 @@
         <v>1.182253090411605</v>
       </c>
       <c r="F119" t="n">
-        <v>1.556924966256569</v>
+        <v>1.556925439682464</v>
       </c>
       <c r="G119" t="n">
-        <v>1.843142538979677</v>
+        <v>1.843143476329115</v>
       </c>
       <c r="H119" t="n">
-        <v>2.066343052608371</v>
+        <v>2.066343982890256</v>
       </c>
       <c r="I119" t="n">
-        <v>2.205451883023117</v>
+        <v>2.205453731933831</v>
       </c>
       <c r="J119" t="n">
-        <v>2.263523976995191</v>
+        <v>2.263526278028309</v>
       </c>
       <c r="K119" t="n">
-        <v>2.268175571018306</v>
+        <v>2.268177867769597</v>
       </c>
       <c r="L119" t="n">
-        <v>2.23055281033699</v>
+        <v>2.230556030984469</v>
       </c>
       <c r="M119" t="n">
-        <v>2.211127526985971</v>
+        <v>2.211130764932484</v>
       </c>
       <c r="N119" t="n">
-        <v>2.22196821671787</v>
+        <v>2.221971953619446</v>
       </c>
       <c r="O119" t="n">
-        <v>2.250804002399155</v>
+        <v>2.250807810581033</v>
       </c>
       <c r="P119" t="n">
-        <v>2.303775069586085</v>
+        <v>2.303779473768688</v>
       </c>
       <c r="Q119" t="n">
-        <v>2.349756279856541</v>
+        <v>2.349760843429393</v>
       </c>
       <c r="R119" t="n">
-        <v>2.356585180512751</v>
+        <v>2.356590472279608</v>
       </c>
       <c r="S119" t="n">
-        <v>2.391518077912553</v>
+        <v>2.39152419000839</v>
       </c>
       <c r="T119" t="n">
-        <v>2.417345515258107</v>
+        <v>2.417352555024575</v>
       </c>
       <c r="U119" t="n">
-        <v>2.448887469113662</v>
+        <v>2.448894318906425</v>
       </c>
       <c r="V119" t="n">
-        <v>2.487777378910561</v>
+        <v>2.487785356254903</v>
       </c>
     </row>
     <row r="120">
@@ -9494,58 +9494,58 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>9.381303062995451e-06</v>
+        <v>7.817752552496209e-06</v>
       </c>
       <c r="F120" t="n">
-        <v>1.854590807720662e-05</v>
+        <v>1.700041573743939e-05</v>
       </c>
       <c r="G120" t="n">
-        <v>2.758688335652675e-05</v>
+        <v>2.452167409469044e-05</v>
       </c>
       <c r="H120" t="n">
-        <v>3.50985888841243e-05</v>
+        <v>3.204653767680914e-05</v>
       </c>
       <c r="I120" t="n">
-        <v>4.417687812665663e-05</v>
+        <v>3.960685625148526e-05</v>
       </c>
       <c r="J120" t="n">
-        <v>5.183306095567968e-05</v>
+        <v>4.725955557723736e-05</v>
       </c>
       <c r="K120" t="n">
-        <v>5.816044630489849e-05</v>
+        <v>5.356883212293281e-05</v>
       </c>
       <c r="L120" t="n">
-        <v>6.474836780156167e-05</v>
+        <v>5.858185658236532e-05</v>
       </c>
       <c r="M120" t="n">
-        <v>7.162319968859479e-05</v>
+        <v>6.539509536784741e-05</v>
       </c>
       <c r="N120" t="n">
-        <v>7.887716774176247e-05</v>
+        <v>7.256699432242146e-05</v>
       </c>
       <c r="O120" t="n">
-        <v>8.696590453398354e-05</v>
+        <v>8.05239856796144e-05</v>
       </c>
       <c r="P120" t="n">
-        <v>9.609617570357312e-05</v>
+        <v>8.781202262567888e-05</v>
       </c>
       <c r="Q120" t="n">
-        <v>0.0001064774345120843</v>
+        <v>9.789054463207754e-05</v>
       </c>
       <c r="R120" t="n">
-        <v>0.0001147052076164258</v>
+        <v>0.0001039515944023859</v>
       </c>
       <c r="S120" t="n">
-        <v>0.0001241586371144028</v>
+        <v>0.0001128714882858207</v>
       </c>
       <c r="T120" t="n">
-        <v>0.0001329620978640731</v>
+        <v>0.0001210550443240068</v>
       </c>
       <c r="U120" t="n">
-        <v>0.0001430530895259894</v>
+        <v>0.0001304307580972256</v>
       </c>
       <c r="V120" t="n">
-        <v>0.000152440733060584</v>
+        <v>0.0001389900801434736</v>
       </c>
     </row>
     <row r="121">
@@ -9570,58 +9570,58 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>8.914101565633863e-06</v>
+        <v>8.196875002881714e-06</v>
       </c>
       <c r="F121" t="n">
-        <v>1.880021374396857e-05</v>
+        <v>1.725074557825687e-05</v>
       </c>
       <c r="G121" t="n">
-        <v>2.766109337230844e-05</v>
+        <v>2.526934469725921e-05</v>
       </c>
       <c r="H121" t="n">
-        <v>3.624102628720846e-05</v>
+        <v>3.320348362151758e-05</v>
       </c>
       <c r="I121" t="n">
-        <v>4.447098384499084e-05</v>
+        <v>4.077387117379208e-05</v>
       </c>
       <c r="J121" t="n">
-        <v>5.206271295169871e-05</v>
+        <v>4.768859157665846e-05</v>
       </c>
       <c r="K121" t="n">
-        <v>5.908257399984381e-05</v>
+        <v>5.411402115890631e-05</v>
       </c>
       <c r="L121" t="n">
-        <v>6.52211396730985e-05</v>
+        <v>5.974037163334232e-05</v>
       </c>
       <c r="M121" t="n">
-        <v>7.211911715053913e-05</v>
+        <v>6.598843485798943e-05</v>
       </c>
       <c r="N121" t="n">
-        <v>8.005590267294604e-05</v>
+        <v>7.334667219325313e-05</v>
       </c>
       <c r="O121" t="n">
-        <v>8.861352450473749e-05</v>
+        <v>8.113164380776757e-05</v>
       </c>
       <c r="P121" t="n">
-        <v>9.834657842927676e-05</v>
+        <v>9.011065806820432e-05</v>
       </c>
       <c r="Q121" t="n">
-        <v>0.0001081684217709167</v>
+        <v>9.907014330420409e-05</v>
       </c>
       <c r="R121" t="n">
-        <v>0.0001161916514972011</v>
+        <v>0.0001063763750008621</v>
       </c>
       <c r="S121" t="n">
-        <v>0.0001257830836443515</v>
+        <v>0.0001151495860281438</v>
       </c>
       <c r="T121" t="n">
-        <v>0.0001350460713155919</v>
+        <v>0.0001237798787579794</v>
       </c>
       <c r="U121" t="n">
-        <v>0.0001450402545890484</v>
+        <v>0.0001328878067072674</v>
       </c>
       <c r="V121" t="n">
-        <v>0.0001557225416148225</v>
+        <v>0.0001427175137359274</v>
       </c>
     </row>
     <row r="122">
@@ -9646,58 +9646,58 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>1.484949507120837</v>
+        <v>1.484949623981462</v>
       </c>
       <c r="F122" t="n">
-        <v>1.613018849579072</v>
+        <v>1.613019034898488</v>
       </c>
       <c r="G122" t="n">
-        <v>1.629070465246019</v>
+        <v>1.629070702491157</v>
       </c>
       <c r="H122" t="n">
-        <v>1.634312730829433</v>
+        <v>1.634313006867246</v>
       </c>
       <c r="I122" t="n">
-        <v>1.630590955631917</v>
+        <v>1.630591258860595</v>
       </c>
       <c r="J122" t="n">
-        <v>1.613387463013231</v>
+        <v>1.613387816306493</v>
       </c>
       <c r="K122" t="n">
-        <v>1.590429950828827</v>
+        <v>1.590430333262784</v>
       </c>
       <c r="L122" t="n">
-        <v>1.555209350169859</v>
+        <v>1.555209774872665</v>
       </c>
       <c r="M122" t="n">
-        <v>1.54177514279795</v>
+        <v>1.541775612411291</v>
       </c>
       <c r="N122" t="n">
-        <v>1.55161261000402</v>
+        <v>1.551613127851466</v>
       </c>
       <c r="O122" t="n">
-        <v>1.567982819035308</v>
+        <v>1.567983388962719</v>
       </c>
       <c r="P122" t="n">
-        <v>1.597047633300396</v>
+        <v>1.597048259706678</v>
       </c>
       <c r="Q122" t="n">
-        <v>1.616063051749728</v>
+        <v>1.6160637278404</v>
       </c>
       <c r="R122" t="n">
-        <v>1.603074977566576</v>
+        <v>1.603075684036814</v>
       </c>
       <c r="S122" t="n">
-        <v>1.604833454891903</v>
+        <v>1.604834182639808</v>
       </c>
       <c r="T122" t="n">
-        <v>1.598614226728835</v>
+        <v>1.598614978170616</v>
       </c>
       <c r="U122" t="n">
-        <v>1.596518462395902</v>
+        <v>1.596519226772474</v>
       </c>
       <c r="V122" t="n">
-        <v>1.598806080990679</v>
+        <v>1.598806873647615</v>
       </c>
     </row>
     <row r="123">
@@ -9725,16 +9725,16 @@
         <v>2.647248682330274</v>
       </c>
       <c r="F123" t="n">
-        <v>2.763052131765944</v>
+        <v>2.763049390297395</v>
       </c>
       <c r="G123" t="n">
-        <v>2.782656370053002</v>
+        <v>2.782648556433864</v>
       </c>
       <c r="H123" t="n">
-        <v>2.673324845216696</v>
+        <v>2.673309866187338</v>
       </c>
       <c r="I123" t="n">
-        <v>2.523807805293511</v>
+        <v>2.523776528302069</v>
       </c>
       <c r="J123" t="n">
         <v>1.491198248963815</v>
@@ -9798,19 +9798,19 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>2.33915521636424</v>
+        <v>2.339154243043923</v>
       </c>
       <c r="F124" t="n">
-        <v>2.483738136534112</v>
+        <v>2.483735720113006</v>
       </c>
       <c r="G124" t="n">
-        <v>2.492491074742955</v>
+        <v>2.492486269998857</v>
       </c>
       <c r="H124" t="n">
-        <v>2.388135272419579</v>
+        <v>2.388126365480816</v>
       </c>
       <c r="I124" t="n">
-        <v>2.240725789422692</v>
+        <v>2.240706081285301</v>
       </c>
       <c r="J124" t="n">
         <v>1.564594995317781</v>
@@ -9874,19 +9874,19 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>1.27897338611903</v>
+        <v>1.278974147280415</v>
       </c>
       <c r="F125" t="n">
-        <v>1.287233554074242</v>
+        <v>1.287235415575103</v>
       </c>
       <c r="G125" t="n">
-        <v>1.209457676050456</v>
+        <v>1.209461323372416</v>
       </c>
       <c r="H125" t="n">
-        <v>1.107587909848334</v>
+        <v>1.107594721160992</v>
       </c>
       <c r="I125" t="n">
-        <v>1.015590671689373</v>
+        <v>1.015606214085438</v>
       </c>
       <c r="J125" t="n">
         <v>1.458286782580707</v>
@@ -10254,58 +10254,58 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6.032885511604383</v>
+        <v>6.032881912963477</v>
       </c>
       <c r="F130" t="n">
-        <v>5.982368009496361</v>
+        <v>5.98236081804163</v>
       </c>
       <c r="G130" t="n">
-        <v>6.051535054248511</v>
+        <v>6.051523751615988</v>
       </c>
       <c r="H130" t="n">
-        <v>6.07672717088796</v>
+        <v>6.076711417619156</v>
       </c>
       <c r="I130" t="n">
-        <v>6.094635087285375</v>
+        <v>6.09461468918844</v>
       </c>
       <c r="J130" t="n">
-        <v>6.098898483190203</v>
+        <v>6.098873303744687</v>
       </c>
       <c r="K130" t="n">
-        <v>6.022798075417553</v>
+        <v>6.022768236432566</v>
       </c>
       <c r="L130" t="n">
-        <v>5.882849531377279</v>
+        <v>5.882815160954704</v>
       </c>
       <c r="M130" t="n">
-        <v>5.864021302554089</v>
+        <v>5.863981179955913</v>
       </c>
       <c r="N130" t="n">
-        <v>5.923662990182168</v>
+        <v>5.923615732191176</v>
       </c>
       <c r="O130" t="n">
-        <v>6.102304127679647</v>
+        <v>6.102247596376034</v>
       </c>
       <c r="P130" t="n">
-        <v>6.376104370854863</v>
+        <v>6.37603563289229</v>
       </c>
       <c r="Q130" t="n">
-        <v>6.60118481575752</v>
+        <v>6.601101407483863</v>
       </c>
       <c r="R130" t="n">
-        <v>6.762564133415236</v>
+        <v>6.762463001779461</v>
       </c>
       <c r="S130" t="n">
-        <v>6.868862647077154</v>
+        <v>6.868739901002765</v>
       </c>
       <c r="T130" t="n">
-        <v>6.935840222381057</v>
+        <v>6.935689959369538</v>
       </c>
       <c r="U130" t="n">
-        <v>6.949099083617241</v>
+        <v>6.948912556262521</v>
       </c>
       <c r="V130" t="n">
-        <v>6.914351998488141</v>
+        <v>6.914113653973353</v>
       </c>
     </row>
     <row r="131">
@@ -10330,58 +10330,58 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>5.833812514766664</v>
+        <v>5.83380883268948</v>
       </c>
       <c r="F131" t="n">
-        <v>6.456564265447996</v>
+        <v>6.4565562460003</v>
       </c>
       <c r="G131" t="n">
-        <v>6.619200850208069</v>
+        <v>6.619187971158562</v>
       </c>
       <c r="H131" t="n">
-        <v>6.567265673684498</v>
+        <v>6.567247893848307</v>
       </c>
       <c r="I131" t="n">
-        <v>6.467173035633159</v>
+        <v>6.467150699345187</v>
       </c>
       <c r="J131" t="n">
-        <v>6.374703061037679</v>
+        <v>6.374676378222969</v>
       </c>
       <c r="K131" t="n">
-        <v>6.203556541859604</v>
+        <v>6.203525565167999</v>
       </c>
       <c r="L131" t="n">
-        <v>5.965532913872475</v>
+        <v>5.965498181163825</v>
       </c>
       <c r="M131" t="n">
-        <v>5.828952266273598</v>
+        <v>5.828912849226297</v>
       </c>
       <c r="N131" t="n">
-        <v>5.736671100789504</v>
+        <v>5.736626677295399</v>
       </c>
       <c r="O131" t="n">
-        <v>5.741985032249941</v>
+        <v>5.741934185361726</v>
       </c>
       <c r="P131" t="n">
-        <v>5.836842114731125</v>
+        <v>5.836783050394172</v>
       </c>
       <c r="Q131" t="n">
-        <v>5.898213160574663</v>
+        <v>5.898143950844912</v>
       </c>
       <c r="R131" t="n">
-        <v>5.911953264108831</v>
+        <v>5.911872410341317</v>
       </c>
       <c r="S131" t="n">
-        <v>5.877707637386578</v>
+        <v>5.877612236941682</v>
       </c>
       <c r="T131" t="n">
-        <v>5.805189161283244</v>
+        <v>5.805076619095511</v>
       </c>
       <c r="U131" t="n">
-        <v>5.688226466532063</v>
+        <v>5.688091756446726</v>
       </c>
       <c r="V131" t="n">
-        <v>5.539034961108713</v>
+        <v>5.538868444957639</v>
       </c>
     </row>
     <row r="132">
@@ -10406,58 +10406,58 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>2.287225448972132</v>
+        <v>2.287225628141218</v>
       </c>
       <c r="F132" t="n">
-        <v>2.250690661523839</v>
+        <v>2.25069096748911</v>
       </c>
       <c r="G132" t="n">
-        <v>2.179798007830017</v>
+        <v>2.179798565236279</v>
       </c>
       <c r="H132" t="n">
-        <v>2.078191140450025</v>
+        <v>2.078192081677132</v>
       </c>
       <c r="I132" t="n">
-        <v>1.994123449290172</v>
+        <v>1.994124869529801</v>
       </c>
       <c r="J132" t="n">
-        <v>1.940452254578709</v>
+        <v>1.940454149373356</v>
       </c>
       <c r="K132" t="n">
-        <v>1.903445949324501</v>
+        <v>1.903448144009336</v>
       </c>
       <c r="L132" t="n">
-        <v>1.870559473595065</v>
+        <v>1.870561782747853</v>
       </c>
       <c r="M132" t="n">
-        <v>1.881115884236002</v>
+        <v>1.881118272849861</v>
       </c>
       <c r="N132" t="n">
-        <v>1.921451125036874</v>
+        <v>1.921453463229791</v>
       </c>
       <c r="O132" t="n">
-        <v>2.00783526598289</v>
+        <v>2.007837361612309</v>
       </c>
       <c r="P132" t="n">
-        <v>2.125732057241653</v>
+        <v>2.125733729907107</v>
       </c>
       <c r="Q132" t="n">
-        <v>2.212731053177875</v>
+        <v>2.212732341501348</v>
       </c>
       <c r="R132" t="n">
-        <v>2.259683379555824</v>
+        <v>2.259684486150132</v>
       </c>
       <c r="S132" t="n">
-        <v>2.276954135123105</v>
+        <v>2.276955261237884</v>
       </c>
       <c r="T132" t="n">
-        <v>2.280905567084487</v>
+        <v>2.280906773600551</v>
       </c>
       <c r="U132" t="n">
-        <v>2.27411197383417</v>
+        <v>2.27411298270579</v>
       </c>
       <c r="V132" t="n">
-        <v>2.25691883262619</v>
+        <v>2.256919303648135</v>
       </c>
     </row>
     <row r="133">
@@ -10482,58 +10482,58 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>1.070363979941118</v>
+        <v>1.070365401161246</v>
       </c>
       <c r="F133" t="n">
-        <v>1.360033439191737</v>
+        <v>1.360035547201416</v>
       </c>
       <c r="G133" t="n">
-        <v>1.648074064785823</v>
+        <v>1.648076233829521</v>
       </c>
       <c r="H133" t="n">
-        <v>1.800520670045633</v>
+        <v>1.800522738356498</v>
       </c>
       <c r="I133" t="n">
-        <v>1.846906218042937</v>
+        <v>1.846908376705263</v>
       </c>
       <c r="J133" t="n">
-        <v>1.828891621245174</v>
+        <v>1.828894191251496</v>
       </c>
       <c r="K133" t="n">
-        <v>1.767985229681196</v>
+        <v>1.767988437218648</v>
       </c>
       <c r="L133" t="n">
-        <v>1.689891887081352</v>
+        <v>1.689895809497152</v>
       </c>
       <c r="M133" t="n">
-        <v>1.657493247562756</v>
+        <v>1.657497965754389</v>
       </c>
       <c r="N133" t="n">
-        <v>1.657322870206065</v>
+        <v>1.65732842549518</v>
       </c>
       <c r="O133" t="n">
-        <v>1.696776271964235</v>
+        <v>1.696782766864536</v>
       </c>
       <c r="P133" t="n">
-        <v>1.768565619366802</v>
+        <v>1.768573156828243</v>
       </c>
       <c r="Q133" t="n">
-        <v>1.8325449296596</v>
+        <v>1.832553492279986</v>
       </c>
       <c r="R133" t="n">
-        <v>1.883708818564226</v>
+        <v>1.883718369518832</v>
       </c>
       <c r="S133" t="n">
-        <v>1.920574021697894</v>
+        <v>1.920584652646838</v>
       </c>
       <c r="T133" t="n">
-        <v>1.945082466550242</v>
+        <v>1.945094427322116</v>
       </c>
       <c r="U133" t="n">
-        <v>1.952356196759435</v>
+        <v>1.952369922398322</v>
       </c>
       <c r="V133" t="n">
-        <v>1.945916864978271</v>
+        <v>1.945933037614267</v>
       </c>
     </row>
     <row r="134">
@@ -10558,58 +10558,58 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>2.335157786555039</v>
+        <v>2.335157907350423</v>
       </c>
       <c r="F134" t="n">
-        <v>2.06461739353294</v>
+        <v>2.064617942094698</v>
       </c>
       <c r="G134" t="n">
-        <v>1.878760619649796</v>
+        <v>1.878761931979527</v>
       </c>
       <c r="H134" t="n">
-        <v>1.74534167329389</v>
+        <v>1.745343741363459</v>
       </c>
       <c r="I134" t="n">
-        <v>1.663507583807817</v>
+        <v>1.663510491506875</v>
       </c>
       <c r="J134" t="n">
-        <v>1.617014693866015</v>
+        <v>1.61701835133111</v>
       </c>
       <c r="K134" t="n">
-        <v>1.570885072989155</v>
+        <v>1.570889496813662</v>
       </c>
       <c r="L134" t="n">
-        <v>1.521599469728842</v>
+        <v>1.521604539387464</v>
       </c>
       <c r="M134" t="n">
-        <v>1.506476469125413</v>
+        <v>1.506482303256685</v>
       </c>
       <c r="N134" t="n">
-        <v>1.511405379629466</v>
+        <v>1.511412161565497</v>
       </c>
       <c r="O134" t="n">
-        <v>1.545501028875012</v>
+        <v>1.545509051425923</v>
       </c>
       <c r="P134" t="n">
-        <v>1.609443899354541</v>
+        <v>1.609453304100803</v>
       </c>
       <c r="Q134" t="n">
-        <v>1.669995205290965</v>
+        <v>1.670005939714178</v>
       </c>
       <c r="R134" t="n">
-        <v>1.721799143658945</v>
+        <v>1.721811300723123</v>
       </c>
       <c r="S134" t="n">
-        <v>1.765555139206355</v>
+        <v>1.765568691372828</v>
       </c>
       <c r="T134" t="n">
-        <v>1.80306582551071</v>
+        <v>1.803080812516852</v>
       </c>
       <c r="U134" t="n">
-        <v>1.829137614345759</v>
+        <v>1.829154317980312</v>
       </c>
       <c r="V134" t="n">
-        <v>1.846106051298861</v>
+        <v>1.846124892262585</v>
       </c>
     </row>
     <row r="135">
@@ -10634,58 +10634,58 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>1.026249880694536</v>
+        <v>1.02625143148934</v>
       </c>
       <c r="F135" t="n">
-        <v>1.186445390791143</v>
+        <v>1.186447858019869</v>
       </c>
       <c r="G135" t="n">
-        <v>1.354848074676064</v>
+        <v>1.35485112374539</v>
       </c>
       <c r="H135" t="n">
-        <v>1.447011373821276</v>
+        <v>1.447015063782929</v>
       </c>
       <c r="I135" t="n">
-        <v>1.495798612511243</v>
+        <v>1.495802732549883</v>
       </c>
       <c r="J135" t="n">
-        <v>1.52597030645294</v>
+        <v>1.525974861413332</v>
       </c>
       <c r="K135" t="n">
-        <v>1.530415961761701</v>
+        <v>1.530421095009823</v>
       </c>
       <c r="L135" t="n">
-        <v>1.517296085683568</v>
+        <v>1.517301630232668</v>
       </c>
       <c r="M135" t="n">
-        <v>1.537613386864061</v>
+        <v>1.537619471802271</v>
       </c>
       <c r="N135" t="n">
-        <v>1.577550852946262</v>
+        <v>1.577557476064461</v>
       </c>
       <c r="O135" t="n">
-        <v>1.649206387800426</v>
+        <v>1.649213626821291</v>
       </c>
       <c r="P135" t="n">
-        <v>1.746627908869298</v>
+        <v>1.746635889342341</v>
       </c>
       <c r="Q135" t="n">
-        <v>1.831981969550157</v>
+        <v>1.831990600401134</v>
       </c>
       <c r="R135" t="n">
-        <v>1.899846492971488</v>
+        <v>1.899855743865862</v>
       </c>
       <c r="S135" t="n">
-        <v>1.951214092027576</v>
+        <v>1.951223990464041</v>
       </c>
       <c r="T135" t="n">
-        <v>1.98854687096764</v>
+        <v>1.988557545109509</v>
       </c>
       <c r="U135" t="n">
-        <v>2.007121673307402</v>
+        <v>2.007133299347275</v>
       </c>
       <c r="V135" t="n">
-        <v>2.008167923259232</v>
+        <v>2.008181066155153</v>
       </c>
     </row>
     <row r="136">
@@ -10710,58 +10710,58 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>8.488036721795027</v>
+        <v>8.488030723977602</v>
       </c>
       <c r="F136" t="n">
-        <v>7.381405686984353</v>
+        <v>7.381395829589871</v>
       </c>
       <c r="G136" t="n">
-        <v>6.165119708170416</v>
+        <v>6.165108222434297</v>
       </c>
       <c r="H136" t="n">
-        <v>5.099163125829006</v>
+        <v>5.099151650892141</v>
       </c>
       <c r="I136" t="n">
-        <v>4.407113203867869</v>
+        <v>4.407101924498941</v>
       </c>
       <c r="J136" t="n">
-        <v>4.150301018917648</v>
+        <v>4.150288626291626</v>
       </c>
       <c r="K136" t="n">
-        <v>4.026874720149326</v>
+        <v>4.026860462696725</v>
       </c>
       <c r="L136" t="n">
-        <v>3.951210709473383</v>
+        <v>3.951194060553232</v>
       </c>
       <c r="M136" t="n">
-        <v>4.018455850293992</v>
+        <v>4.018435566970061</v>
       </c>
       <c r="N136" t="n">
-        <v>4.123369828595254</v>
+        <v>4.123344868360248</v>
       </c>
       <c r="O136" t="n">
-        <v>4.28826361640683</v>
+        <v>4.288233160681275</v>
       </c>
       <c r="P136" t="n">
-        <v>4.51246813075174</v>
+        <v>4.512430530000004</v>
       </c>
       <c r="Q136" t="n">
-        <v>4.70451347772891</v>
+        <v>4.704466906447258</v>
       </c>
       <c r="R136" t="n">
-        <v>4.858246922189737</v>
+        <v>4.858189344562758</v>
       </c>
       <c r="S136" t="n">
-        <v>4.976654798977934</v>
+        <v>4.976583369399166</v>
       </c>
       <c r="T136" t="n">
-        <v>5.062464353457382</v>
+        <v>5.062375431793969</v>
       </c>
       <c r="U136" t="n">
-        <v>5.10117404688935</v>
+        <v>5.101062316907393</v>
       </c>
       <c r="V136" t="n">
-        <v>5.098266634928323</v>
+        <v>5.098122170738614</v>
       </c>
     </row>
     <row r="137">
@@ -10786,58 +10786,58 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>1.746682529953423</v>
+        <v>1.74668321581805</v>
       </c>
       <c r="F137" t="n">
-        <v>1.811205833274484</v>
+        <v>1.811206943646827</v>
       </c>
       <c r="G137" t="n">
-        <v>1.766504284065119</v>
+        <v>1.766506021009647</v>
       </c>
       <c r="H137" t="n">
-        <v>1.68373043448671</v>
+        <v>1.683732788651045</v>
       </c>
       <c r="I137" t="n">
-        <v>1.63911103578188</v>
+        <v>1.639114009304151</v>
       </c>
       <c r="J137" t="n">
-        <v>1.634148946085316</v>
+        <v>1.634152555273119</v>
       </c>
       <c r="K137" t="n">
-        <v>1.630789078114016</v>
+        <v>1.630792925263354</v>
       </c>
       <c r="L137" t="n">
-        <v>1.614555720875257</v>
+        <v>1.614560053657171</v>
       </c>
       <c r="M137" t="n">
-        <v>1.623715557221321</v>
+        <v>1.623720197988382</v>
       </c>
       <c r="N137" t="n">
-        <v>1.641153144422751</v>
+        <v>1.641158361819183</v>
       </c>
       <c r="O137" t="n">
-        <v>1.681134006478228</v>
+        <v>1.681140336994482</v>
       </c>
       <c r="P137" t="n">
-        <v>1.744895017150362</v>
+        <v>1.744902334898193</v>
       </c>
       <c r="Q137" t="n">
-        <v>1.798282050320061</v>
+        <v>1.798290727864795</v>
       </c>
       <c r="R137" t="n">
-        <v>1.837025143261863</v>
+        <v>1.837035069645655</v>
       </c>
       <c r="S137" t="n">
-        <v>1.860282022182786</v>
+        <v>1.860293345419001</v>
       </c>
       <c r="T137" t="n">
-        <v>1.869015111394413</v>
+        <v>1.86902829132928</v>
       </c>
       <c r="U137" t="n">
-        <v>1.862596132829774</v>
+        <v>1.862612017302639</v>
       </c>
       <c r="V137" t="n">
-        <v>1.848223086961408</v>
+        <v>1.848242322552516</v>
       </c>
     </row>
     <row r="138">
@@ -10862,58 +10862,58 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>7.418033785603873</v>
+        <v>7.418029175302748</v>
       </c>
       <c r="F138" t="n">
-        <v>7.140898473990884</v>
+        <v>7.140889309504856</v>
       </c>
       <c r="G138" t="n">
-        <v>6.706383325976565</v>
+        <v>6.706370200778439</v>
       </c>
       <c r="H138" t="n">
-        <v>6.125042787215166</v>
+        <v>6.125027142402057</v>
       </c>
       <c r="I138" t="n">
-        <v>5.58268436880297</v>
+        <v>5.582667127130826</v>
       </c>
       <c r="J138" t="n">
-        <v>5.159322022151752</v>
+        <v>5.159303458401854</v>
       </c>
       <c r="K138" t="n">
-        <v>4.805822595285013</v>
+        <v>4.805802654396533</v>
       </c>
       <c r="L138" t="n">
-        <v>4.51061363171746</v>
+        <v>4.510592459267146</v>
       </c>
       <c r="M138" t="n">
-        <v>4.367861322237578</v>
+        <v>4.36783764377989</v>
       </c>
       <c r="N138" t="n">
-        <v>4.322751065107917</v>
+        <v>4.322724294614815</v>
       </c>
       <c r="O138" t="n">
-        <v>4.381629464760444</v>
+        <v>4.381598256400487</v>
       </c>
       <c r="P138" t="n">
-        <v>4.508379505260802</v>
+        <v>4.508342660995448</v>
       </c>
       <c r="Q138" t="n">
-        <v>4.59283844766304</v>
+        <v>4.592794908362787</v>
       </c>
       <c r="R138" t="n">
-        <v>4.638316232215058</v>
+        <v>4.638264621365686</v>
       </c>
       <c r="S138" t="n">
-        <v>4.642674250535859</v>
+        <v>4.642613122105026</v>
       </c>
       <c r="T138" t="n">
-        <v>4.612533534870712</v>
+        <v>4.612460836016628</v>
       </c>
       <c r="U138" t="n">
-        <v>4.542946075719049</v>
+        <v>4.542858001396755</v>
       </c>
       <c r="V138" t="n">
-        <v>4.443192246569824</v>
+        <v>4.443083263253597</v>
       </c>
     </row>
     <row r="139">
@@ -10938,58 +10938,58 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>14.08359724508733</v>
+        <v>14.08358594234646</v>
       </c>
       <c r="F139" t="n">
-        <v>13.96561981885804</v>
+        <v>13.96559741391984</v>
       </c>
       <c r="G139" t="n">
-        <v>14.12704192489186</v>
+        <v>14.12700694390601</v>
       </c>
       <c r="H139" t="n">
-        <v>14.18580688462417</v>
+        <v>14.18575865702204</v>
       </c>
       <c r="I139" t="n">
-        <v>14.22756613126708</v>
+        <v>14.22750456340375</v>
       </c>
       <c r="J139" t="n">
-        <v>14.23747049372541</v>
+        <v>14.23739475250512</v>
       </c>
       <c r="K139" t="n">
-        <v>14.0597683334389</v>
+        <v>14.05967891566041</v>
       </c>
       <c r="L139" t="n">
-        <v>13.73301440956582</v>
+        <v>13.73291152193667</v>
       </c>
       <c r="M139" t="n">
-        <v>13.68900135017511</v>
+        <v>13.68888154783527</v>
       </c>
       <c r="N139" t="n">
-        <v>13.82816255144425</v>
+        <v>13.82802194918248</v>
       </c>
       <c r="O139" t="n">
-        <v>14.24510623187354</v>
+        <v>14.24493822891058</v>
       </c>
       <c r="P139" t="n">
-        <v>14.88416970256371</v>
+        <v>14.88396634103921</v>
       </c>
       <c r="Q139" t="n">
-        <v>15.40947841325618</v>
+        <v>15.40923219712721</v>
       </c>
       <c r="R139" t="n">
-        <v>15.78605287526324</v>
+        <v>15.7857558396958</v>
       </c>
       <c r="S139" t="n">
-        <v>16.03400846515819</v>
+        <v>16.03364879042607</v>
       </c>
       <c r="T139" t="n">
-        <v>16.19011868181649</v>
+        <v>16.18967999142343</v>
       </c>
       <c r="U139" t="n">
-        <v>16.22074648262986</v>
+        <v>16.22020370740815</v>
       </c>
       <c r="V139" t="n">
-        <v>16.13916831699868</v>
+        <v>16.13847679391909</v>
       </c>
     </row>
     <row r="140">
@@ -11014,58 +11014,58 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>5.555396808790081</v>
+        <v>5.55539376929877</v>
       </c>
       <c r="F140" t="n">
-        <v>4.915862234643542</v>
+        <v>4.915857282841553</v>
       </c>
       <c r="G140" t="n">
-        <v>4.484786491005886</v>
+        <v>4.484780124654177</v>
       </c>
       <c r="H140" t="n">
-        <v>4.205029686093676</v>
+        <v>4.205021905097326</v>
       </c>
       <c r="I140" t="n">
-        <v>4.100749270128953</v>
+        <v>4.100739668876817</v>
       </c>
       <c r="J140" t="n">
-        <v>4.116523306091441</v>
+        <v>4.116511242141123</v>
       </c>
       <c r="K140" t="n">
-        <v>4.129981100007226</v>
+        <v>4.129966261386848</v>
       </c>
       <c r="L140" t="n">
-        <v>4.101293717231953</v>
+        <v>4.101275933731148</v>
       </c>
       <c r="M140" t="n">
-        <v>4.134871408858625</v>
+        <v>4.134850079614052</v>
       </c>
       <c r="N140" t="n">
-        <v>4.188133965282844</v>
+        <v>4.188108649124998</v>
       </c>
       <c r="O140" t="n">
-        <v>4.296721978625947</v>
+        <v>4.296691790721618</v>
       </c>
       <c r="P140" t="n">
-        <v>4.458367972055611</v>
+        <v>4.458331578738545</v>
       </c>
       <c r="Q140" t="n">
-        <v>4.590424807825894</v>
+        <v>4.590380884040119</v>
       </c>
       <c r="R140" t="n">
-        <v>4.689224950363051</v>
+        <v>4.689171712685963</v>
       </c>
       <c r="S140" t="n">
-        <v>4.766498103554126</v>
+        <v>4.766433029974421</v>
       </c>
       <c r="T140" t="n">
-        <v>4.830177894090258</v>
+        <v>4.830097309962902</v>
       </c>
       <c r="U140" t="n">
-        <v>4.86783324024018</v>
+        <v>4.867731668960748</v>
       </c>
       <c r="V140" t="n">
-        <v>4.879741024357474</v>
+        <v>4.879608900757612</v>
       </c>
     </row>
     <row r="141">
@@ -11090,58 +11090,58 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>0.3245982818252817</v>
+        <v>0.3246004239651902</v>
       </c>
       <c r="F141" t="n">
-        <v>0.3318933000318284</v>
+        <v>0.331897476235173</v>
       </c>
       <c r="G141" t="n">
-        <v>0.3388237333648086</v>
+        <v>0.338830003836053</v>
       </c>
       <c r="H141" t="n">
-        <v>0.3377471498409794</v>
+        <v>0.3377554145937318</v>
       </c>
       <c r="I141" t="n">
-        <v>0.336220921454392</v>
+        <v>0.3362312470442609</v>
       </c>
       <c r="J141" t="n">
-        <v>0.3351151822181934</v>
+        <v>0.3351276491502387</v>
       </c>
       <c r="K141" t="n">
-        <v>0.3291398932657156</v>
+        <v>0.3291544484383012</v>
       </c>
       <c r="L141" t="n">
-        <v>0.3190575047565313</v>
+        <v>0.3190741477854595</v>
       </c>
       <c r="M141" t="n">
-        <v>0.3158963014926005</v>
+        <v>0.3159155550438585</v>
       </c>
       <c r="N141" t="n">
-        <v>0.3186043040225117</v>
+        <v>0.3186266945705116</v>
       </c>
       <c r="O141" t="n">
-        <v>0.3301015686756879</v>
+        <v>0.3301279109292357</v>
       </c>
       <c r="P141" t="n">
-        <v>0.3496323267043475</v>
+        <v>0.3496637016048494</v>
       </c>
       <c r="Q141" t="n">
-        <v>0.3693261093381989</v>
+        <v>0.3693632861015461</v>
       </c>
       <c r="R141" t="n">
-        <v>0.3873104570699331</v>
+        <v>0.3873543796827322</v>
       </c>
       <c r="S141" t="n">
-        <v>0.4020025904248057</v>
+        <v>0.4020546352324781</v>
       </c>
       <c r="T141" t="n">
-        <v>0.4134104173103237</v>
+        <v>0.4134727145753003</v>
       </c>
       <c r="U141" t="n">
-        <v>0.4207875555685867</v>
+        <v>0.4208632642774967</v>
       </c>
       <c r="V141" t="n">
-        <v>0.425268361767755</v>
+        <v>0.4253631263053739</v>
       </c>
     </row>
     <row r="142">
@@ -11166,58 +11166,58 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>0.1442470812434167</v>
+        <v>0.1442494687014936</v>
       </c>
       <c r="F142" t="n">
-        <v>0.2194020968862541</v>
+        <v>0.21940648686649</v>
       </c>
       <c r="G142" t="n">
-        <v>0.3421768184072945</v>
+        <v>0.3421829106858829</v>
       </c>
       <c r="H142" t="n">
-        <v>0.4543090494947334</v>
+        <v>0.4543165544169785</v>
       </c>
       <c r="I142" t="n">
-        <v>0.5288639466560181</v>
+        <v>0.5288728383974496</v>
       </c>
       <c r="J142" t="n">
-        <v>0.5616368607089287</v>
+        <v>0.561647311366088</v>
       </c>
       <c r="K142" t="n">
-        <v>0.5600829937694252</v>
+        <v>0.5600951423429346</v>
       </c>
       <c r="L142" t="n">
-        <v>0.54206580181468</v>
+        <v>0.5420797011696831</v>
       </c>
       <c r="M142" t="n">
-        <v>0.5343578447961292</v>
+        <v>0.5343739639907523</v>
       </c>
       <c r="N142" t="n">
-        <v>0.5364096401215844</v>
+        <v>0.5364283986344778</v>
       </c>
       <c r="O142" t="n">
-        <v>0.5512883620853217</v>
+        <v>0.5513104523581931</v>
       </c>
       <c r="P142" t="n">
-        <v>0.5751834837036409</v>
+        <v>0.575209829865685</v>
       </c>
       <c r="Q142" t="n">
-        <v>0.5946733576696304</v>
+        <v>0.5947046669104897</v>
       </c>
       <c r="R142" t="n">
-        <v>0.6081362020465457</v>
+        <v>0.6081733563221162</v>
       </c>
       <c r="S142" t="n">
-        <v>0.6159887206647027</v>
+        <v>0.6160329372013018</v>
       </c>
       <c r="T142" t="n">
-        <v>0.6198748380881549</v>
+        <v>0.6199279892649431</v>
       </c>
       <c r="U142" t="n">
-        <v>0.6185283732400625</v>
+        <v>0.6185932481242145</v>
       </c>
       <c r="V142" t="n">
-        <v>0.6124674944039654</v>
+        <v>0.612549081096185</v>
       </c>
     </row>
     <row r="143">
@@ -11470,58 +11470,58 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>0.738411853853646</v>
+        <v>0.7384105394460297</v>
       </c>
       <c r="F146" t="n">
-        <v>0.7870617876487168</v>
+        <v>0.7870604862533609</v>
       </c>
       <c r="G146" t="n">
-        <v>0.7893930195887773</v>
+        <v>0.7893891197724586</v>
       </c>
       <c r="H146" t="n">
-        <v>0.7696758407535507</v>
+        <v>0.7696705844012489</v>
       </c>
       <c r="I146" t="n">
-        <v>0.7924916889211074</v>
+        <v>0.7924849891396543</v>
       </c>
       <c r="J146" t="n">
-        <v>0.8125660670159002</v>
+        <v>0.8125591760624816</v>
       </c>
       <c r="K146" t="n">
-        <v>0.8390716169770602</v>
+        <v>0.8390644804001051</v>
       </c>
       <c r="L146" t="n">
-        <v>0.8642326760270256</v>
+        <v>0.8642252432380201</v>
       </c>
       <c r="M146" t="n">
-        <v>0.8906483594609268</v>
+        <v>0.8906390253995368</v>
       </c>
       <c r="N146" t="n">
-        <v>0.9450633060517901</v>
+        <v>0.9450534886232366</v>
       </c>
       <c r="O146" t="n">
-        <v>1.018904776832003</v>
+        <v>1.018894442588108</v>
       </c>
       <c r="P146" t="n">
-        <v>1.117472371180402</v>
+        <v>1.117459672445196</v>
       </c>
       <c r="Q146" t="n">
-        <v>1.228872869020682</v>
+        <v>1.22885948016824</v>
       </c>
       <c r="R146" t="n">
-        <v>1.344016092808324</v>
+        <v>1.343997915690488</v>
       </c>
       <c r="S146" t="n">
-        <v>1.454999070824531</v>
+        <v>1.454979846504485</v>
       </c>
       <c r="T146" t="n">
-        <v>1.560489162405539</v>
+        <v>1.56046879949319</v>
       </c>
       <c r="U146" t="n">
-        <v>1.666674654735687</v>
+        <v>1.666653086949332</v>
       </c>
       <c r="V146" t="n">
-        <v>1.769759754815668</v>
+        <v>1.769734425855802</v>
       </c>
     </row>
     <row r="147">
@@ -11552,52 +11552,52 @@
         <v>1.620959705086031</v>
       </c>
       <c r="G147" t="n">
-        <v>1.784150909800645</v>
+        <v>1.784149197718136</v>
       </c>
       <c r="H147" t="n">
-        <v>1.781316106192317</v>
+        <v>1.78131442996557</v>
       </c>
       <c r="I147" t="n">
-        <v>1.793952186997268</v>
+        <v>1.793948883625517</v>
       </c>
       <c r="J147" t="n">
-        <v>1.757300406397483</v>
+        <v>1.757297128998427</v>
       </c>
       <c r="K147" t="n">
-        <v>1.733881882019484</v>
+        <v>1.733878609055963</v>
       </c>
       <c r="L147" t="n">
-        <v>1.697835953430244</v>
+        <v>1.69783266460567</v>
       </c>
       <c r="M147" t="n">
-        <v>1.657465914527189</v>
+        <v>1.657462592356349</v>
       </c>
       <c r="N147" t="n">
-        <v>1.663097384081225</v>
+        <v>1.663092325255513</v>
       </c>
       <c r="O147" t="n">
-        <v>1.694534005340982</v>
+        <v>1.694528846633341</v>
       </c>
       <c r="P147" t="n">
-        <v>1.751613914354241</v>
+        <v>1.751608631492197</v>
       </c>
       <c r="Q147" t="n">
-        <v>1.812314857064222</v>
+        <v>1.812307614308788</v>
       </c>
       <c r="R147" t="n">
-        <v>1.86528785046729</v>
+        <v>1.865278504672897</v>
       </c>
       <c r="S147" t="n">
-        <v>1.902366388416102</v>
+        <v>1.902354770438443</v>
       </c>
       <c r="T147" t="n">
-        <v>1.925937632750356</v>
+        <v>1.925923539821583</v>
       </c>
       <c r="U147" t="n">
-        <v>1.950885551571221</v>
+        <v>1.950868745943016</v>
       </c>
       <c r="V147" t="n">
-        <v>1.976108742168378</v>
+        <v>1.976084551829999</v>
       </c>
     </row>
     <row r="148">
@@ -11622,58 +11622,58 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>1.531960136693671</v>
+        <v>1.531960168850835</v>
       </c>
       <c r="F148" t="n">
-        <v>1.854092987369177</v>
+        <v>1.854093017614677</v>
       </c>
       <c r="G148" t="n">
-        <v>2.124611816002496</v>
+        <v>2.124611902286379</v>
       </c>
       <c r="H148" t="n">
-        <v>2.195421005653902</v>
+        <v>2.19542114395199</v>
       </c>
       <c r="I148" t="n">
-        <v>2.242076056784644</v>
+        <v>2.242076190920756</v>
       </c>
       <c r="J148" t="n">
-        <v>2.192814877940374</v>
+        <v>2.192815061603103</v>
       </c>
       <c r="K148" t="n">
-        <v>2.133344723396077</v>
+        <v>2.133344904464448</v>
       </c>
       <c r="L148" t="n">
-        <v>2.053818373298602</v>
+        <v>2.053818553191139</v>
       </c>
       <c r="M148" t="n">
-        <v>1.972827156752444</v>
+        <v>1.972827362385716</v>
       </c>
       <c r="N148" t="n">
-        <v>1.956495450690326</v>
+        <v>1.956495683550402</v>
       </c>
       <c r="O148" t="n">
-        <v>1.984265706402095</v>
+        <v>1.984265968540273</v>
       </c>
       <c r="P148" t="n">
-        <v>2.051959520448663</v>
+        <v>2.051959814468277</v>
       </c>
       <c r="Q148" t="n">
-        <v>2.125672767876607</v>
+        <v>2.125673096935556</v>
       </c>
       <c r="R148" t="n">
-        <v>2.190125811252001</v>
+        <v>2.190126179038437</v>
       </c>
       <c r="S148" t="n">
-        <v>2.236198633955135</v>
+        <v>2.236199074046908</v>
       </c>
       <c r="T148" t="n">
-        <v>2.269143491899301</v>
+        <v>2.269143980979664</v>
       </c>
       <c r="U148" t="n">
-        <v>2.305757082052404</v>
+        <v>2.305757657751014</v>
       </c>
       <c r="V148" t="n">
-        <v>2.342429580126449</v>
+        <v>2.342430319239896</v>
       </c>
     </row>
     <row r="149">
@@ -11698,7 +11698,7 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>0.5357698063613627</v>
+        <v>0.5357697133508256</v>
       </c>
       <c r="F149" t="n">
         <v>0.5536840301135901</v>
@@ -11713,19 +11713,19 @@
         <v>0.622356717600515</v>
       </c>
       <c r="J149" t="n">
-        <v>0.6491148844865695</v>
+        <v>0.6491148197804132</v>
       </c>
       <c r="K149" t="n">
-        <v>0.6738386029899752</v>
+        <v>0.6738385418227705</v>
       </c>
       <c r="L149" t="n">
-        <v>0.6975094619795186</v>
+        <v>0.6975094039750465</v>
       </c>
       <c r="M149" t="n">
-        <v>0.7392201290827692</v>
+        <v>0.7392200737915976</v>
       </c>
       <c r="N149" t="n">
-        <v>0.7986631911864026</v>
+        <v>0.798663138174196</v>
       </c>
       <c r="O149" t="n">
         <v>0.862587824995773</v>
@@ -11737,19 +11737,19 @@
         <v>1.005312805282369</v>
       </c>
       <c r="R149" t="n">
-        <v>1.063878758644775</v>
+        <v>1.063878804236572</v>
       </c>
       <c r="S149" t="n">
-        <v>1.10736524030601</v>
+        <v>1.107365284328581</v>
       </c>
       <c r="T149" t="n">
-        <v>1.147545651085348</v>
+        <v>1.147545736100638</v>
       </c>
       <c r="U149" t="n">
-        <v>1.186747616528035</v>
+        <v>1.186747739768571</v>
       </c>
       <c r="V149" t="n">
-        <v>1.22484902157402</v>
+        <v>1.224849140712648</v>
       </c>
     </row>
     <row r="150">
@@ -11774,58 +11774,58 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>1.367148217951738</v>
+        <v>1.367148274043909</v>
       </c>
       <c r="F150" t="n">
-        <v>1.463023281149981</v>
+        <v>1.463023335351434</v>
       </c>
       <c r="G150" t="n">
-        <v>1.544178270244926</v>
+        <v>1.544178375844001</v>
       </c>
       <c r="H150" t="n">
-        <v>1.610569262237013</v>
+        <v>1.610569417939055</v>
       </c>
       <c r="I150" t="n">
-        <v>1.661220608886301</v>
+        <v>1.661220814414074</v>
       </c>
       <c r="J150" t="n">
-        <v>1.695704551590308</v>
+        <v>1.695704756503827</v>
       </c>
       <c r="K150" t="n">
-        <v>1.714949571928331</v>
+        <v>1.714949880466983</v>
       </c>
       <c r="L150" t="n">
-        <v>1.721904779226448</v>
+        <v>1.7219050910168</v>
       </c>
       <c r="M150" t="n">
-        <v>1.757803069758892</v>
+        <v>1.757803439507537</v>
       </c>
       <c r="N150" t="n">
-        <v>1.818190405403728</v>
+        <v>1.818190837218315</v>
       </c>
       <c r="O150" t="n">
-        <v>1.875814673210369</v>
+        <v>1.875815172193552</v>
       </c>
       <c r="P150" t="n">
-        <v>1.941678545452881</v>
+        <v>1.941679117694689</v>
       </c>
       <c r="Q150" t="n">
-        <v>1.998514746320096</v>
+        <v>1.9985153397095</v>
       </c>
       <c r="R150" t="n">
-        <v>2.03011346455539</v>
+        <v>2.030114144761455</v>
       </c>
       <c r="S150" t="n">
-        <v>2.033640639235994</v>
+        <v>2.033641351541591</v>
       </c>
       <c r="T150" t="n">
-        <v>2.029822227852377</v>
+        <v>2.029822977026243</v>
       </c>
       <c r="U150" t="n">
-        <v>2.018210843559682</v>
+        <v>2.018211634210453</v>
       </c>
       <c r="V150" t="n">
-        <v>2.000747473885645</v>
+        <v>2.000748311860853</v>
       </c>
     </row>
     <row r="151">
@@ -11856,52 +11856,52 @@
         <v>0.8629770912779552</v>
       </c>
       <c r="G151" t="n">
-        <v>0.9306501152678337</v>
+        <v>0.9306501738388874</v>
       </c>
       <c r="H151" t="n">
-        <v>0.9906376829783302</v>
+        <v>0.9906377395120126</v>
       </c>
       <c r="I151" t="n">
-        <v>1.021278371189071</v>
+        <v>1.021278426160011</v>
       </c>
       <c r="J151" t="n">
-        <v>1.026979183325553</v>
+        <v>1.026979237172456</v>
       </c>
       <c r="K151" t="n">
-        <v>1.021071855813264</v>
+        <v>1.021071908957517</v>
       </c>
       <c r="L151" t="n">
-        <v>1.0109442745074</v>
+        <v>1.010944327355824</v>
       </c>
       <c r="M151" t="n">
-        <v>1.024694796750633</v>
+        <v>1.024694902517408</v>
       </c>
       <c r="N151" t="n">
-        <v>1.061904683319368</v>
+        <v>1.061904789789902</v>
       </c>
       <c r="O151" t="n">
-        <v>1.104205510591056</v>
+        <v>1.104205618297622</v>
       </c>
       <c r="P151" t="n">
-        <v>1.154920922399544</v>
+        <v>1.154921031898766</v>
       </c>
       <c r="Q151" t="n">
-        <v>1.202465480532133</v>
+        <v>1.202465592385891</v>
       </c>
       <c r="R151" t="n">
-        <v>1.23690747569657</v>
+        <v>1.236907590450415</v>
       </c>
       <c r="S151" t="n">
-        <v>1.255267662206713</v>
+        <v>1.255267839517337</v>
       </c>
       <c r="T151" t="n">
-        <v>1.271640115820467</v>
+        <v>1.271640238019736</v>
       </c>
       <c r="U151" t="n">
-        <v>1.288255437438324</v>
+        <v>1.288255627575166</v>
       </c>
       <c r="V151" t="n">
-        <v>1.303726018364353</v>
+        <v>1.303726216185028</v>
       </c>
     </row>
     <row r="152">
@@ -11929,55 +11929,55 @@
         <v>0.5240811827576841</v>
       </c>
       <c r="F152" t="n">
-        <v>0.6136281602908087</v>
+        <v>0.61362812824649</v>
       </c>
       <c r="G152" t="n">
-        <v>0.6664549660103067</v>
+        <v>0.6664549032407902</v>
       </c>
       <c r="H152" t="n">
-        <v>0.6955192725582441</v>
+        <v>0.6955192104983072</v>
       </c>
       <c r="I152" t="n">
-        <v>0.6997328266679025</v>
+        <v>0.6997327648794354</v>
       </c>
       <c r="J152" t="n">
-        <v>0.692531037703594</v>
+        <v>0.6925309447948823</v>
       </c>
       <c r="K152" t="n">
-        <v>0.6876912910895684</v>
+        <v>0.6876911659988385</v>
       </c>
       <c r="L152" t="n">
-        <v>0.6897009309592859</v>
+        <v>0.6897008037486432</v>
       </c>
       <c r="M152" t="n">
-        <v>0.7108431198842043</v>
+        <v>0.7108429897475055</v>
       </c>
       <c r="N152" t="n">
-        <v>0.7452002026928427</v>
+        <v>0.7452000353440624</v>
       </c>
       <c r="O152" t="n">
-        <v>0.7785974454741518</v>
+        <v>0.7785972382664311</v>
       </c>
       <c r="P152" t="n">
-        <v>0.8152167147762788</v>
+        <v>0.8152165003999904</v>
       </c>
       <c r="Q152" t="n">
-        <v>0.8479265816911544</v>
+        <v>0.8479263222729775</v>
       </c>
       <c r="R152" t="n">
-        <v>0.869612638329006</v>
+        <v>0.8696123686348816</v>
       </c>
       <c r="S152" t="n">
-        <v>0.8791290649949578</v>
+        <v>0.8791287438418899</v>
       </c>
       <c r="T152" t="n">
-        <v>0.8862245002717428</v>
+        <v>0.8862241650453583</v>
       </c>
       <c r="U152" t="n">
-        <v>0.891440139847214</v>
+        <v>0.8914397894407645</v>
       </c>
       <c r="V152" t="n">
-        <v>0.8941512265419695</v>
+        <v>0.8941508141434368</v>
       </c>
     </row>
     <row r="153">
@@ -12008,52 +12008,52 @@
         <v>0.2837003931988779</v>
       </c>
       <c r="G153" t="n">
-        <v>0.300197061661429</v>
+        <v>0.3001969404598412</v>
       </c>
       <c r="H153" t="n">
-        <v>0.3232719622878588</v>
+        <v>0.323271849434021</v>
       </c>
       <c r="I153" t="n">
-        <v>0.3441104881682715</v>
+        <v>0.3441103822075912</v>
       </c>
       <c r="J153" t="n">
-        <v>0.3605565050918152</v>
+        <v>0.3605563049202081</v>
       </c>
       <c r="K153" t="n">
-        <v>0.3728842427458869</v>
+        <v>0.3728840528662801</v>
       </c>
       <c r="L153" t="n">
-        <v>0.3834576206817041</v>
+        <v>0.3834574398343439</v>
       </c>
       <c r="M153" t="n">
-        <v>0.4029821945746972</v>
+        <v>0.4029819349825511</v>
       </c>
       <c r="N153" t="n">
-        <v>0.4323277820022396</v>
+        <v>0.4323275324169671</v>
       </c>
       <c r="O153" t="n">
-        <v>0.4648883473285476</v>
+        <v>0.4648880262453413</v>
       </c>
       <c r="P153" t="n">
-        <v>0.5020403060226069</v>
+        <v>0.5020399954028273</v>
       </c>
       <c r="Q153" t="n">
-        <v>0.5382251157498855</v>
+        <v>0.538224739511025</v>
       </c>
       <c r="R153" t="n">
-        <v>0.5683204158520974</v>
+        <v>0.5683200507108205</v>
       </c>
       <c r="S153" t="n">
-        <v>0.5907344513294182</v>
+        <v>0.5907340255523039</v>
       </c>
       <c r="T153" t="n">
-        <v>0.6121921229029836</v>
+        <v>0.6121916396200844</v>
       </c>
       <c r="U153" t="n">
-        <v>0.6336337893646502</v>
+        <v>0.6336333185358569</v>
       </c>
       <c r="V153" t="n">
-        <v>0.655190138395816</v>
+        <v>0.6551896790450755</v>
       </c>
     </row>
     <row r="154">
@@ -12096,7 +12096,7 @@
         <v>0.8389364294725326</v>
       </c>
       <c r="K154" t="n">
-        <v>0.8232925406788228</v>
+        <v>0.8232922259368766</v>
       </c>
       <c r="L154" t="n">
         <v>0.8098812097832117</v>
@@ -12105,31 +12105,31 @@
         <v>0.8157620465030239</v>
       </c>
       <c r="N154" t="n">
-        <v>0.8349598746273477</v>
+        <v>0.8349595266792671</v>
       </c>
       <c r="O154" t="n">
-        <v>0.8519592141770111</v>
+        <v>0.8519588519197281</v>
       </c>
       <c r="P154" t="n">
         <v>0.8718757480336995</v>
       </c>
       <c r="Q154" t="n">
-        <v>0.8875605121431955</v>
+        <v>0.8875601163479656</v>
       </c>
       <c r="R154" t="n">
-        <v>0.8934640433308044</v>
+        <v>0.8934636280620362</v>
       </c>
       <c r="S154" t="n">
-        <v>0.8888376901517457</v>
+        <v>0.8888372533852676</v>
       </c>
       <c r="T154" t="n">
-        <v>0.8839039233464462</v>
+        <v>0.8839034628651788</v>
       </c>
       <c r="U154" t="n">
-        <v>0.8788825103381173</v>
+        <v>0.8788820238384822</v>
       </c>
       <c r="V154" t="n">
-        <v>0.8722547152667202</v>
+        <v>0.8722542004574596</v>
       </c>
     </row>
     <row r="155">
@@ -12157,55 +12157,55 @@
         <v>0.06831885052531758</v>
       </c>
       <c r="F155" t="n">
-        <v>0.08153300438802084</v>
+        <v>0.08153298034933973</v>
       </c>
       <c r="G155" t="n">
-        <v>0.08652774714213736</v>
+        <v>0.08652772631337333</v>
       </c>
       <c r="H155" t="n">
-        <v>0.09185621479119034</v>
+        <v>0.09185619665984324</v>
       </c>
       <c r="I155" t="n">
-        <v>0.09529817335743848</v>
+        <v>0.09529814143010508</v>
       </c>
       <c r="J155" t="n">
-        <v>0.09802765825916865</v>
+        <v>0.09802764408373317</v>
       </c>
       <c r="K155" t="n">
-        <v>0.1000815543119547</v>
+        <v>0.1000815289805952</v>
       </c>
       <c r="L155" t="n">
-        <v>0.1020578313198142</v>
+        <v>0.1020577971634258</v>
       </c>
       <c r="M155" t="n">
-        <v>0.1064286375475799</v>
+        <v>0.1064285962231996</v>
       </c>
       <c r="N155" t="n">
-        <v>0.1114921663137297</v>
+        <v>0.1114921284652636</v>
       </c>
       <c r="O155" t="n">
-        <v>0.1149218130568877</v>
+        <v>0.1149217781286129</v>
       </c>
       <c r="P155" t="n">
-        <v>0.1186713805560173</v>
+        <v>0.1186713319034896</v>
       </c>
       <c r="Q155" t="n">
-        <v>0.1230540939833007</v>
+        <v>0.1230540410034089</v>
       </c>
       <c r="R155" t="n">
-        <v>0.1261066606801345</v>
+        <v>0.1261066109502388</v>
       </c>
       <c r="S155" t="n">
-        <v>0.1302549361620544</v>
+        <v>0.1302548825336217</v>
       </c>
       <c r="T155" t="n">
-        <v>0.1356398873144812</v>
+        <v>0.1356398300555793</v>
       </c>
       <c r="U155" t="n">
-        <v>0.1428180000400762</v>
+        <v>0.1428179393185711</v>
       </c>
       <c r="V155" t="n">
-        <v>0.1532487868415084</v>
+        <v>0.1532487227072135</v>
       </c>
     </row>
     <row r="156">
@@ -12239,49 +12239,49 @@
         <v>0.2142285760676007</v>
       </c>
       <c r="H156" t="n">
-        <v>0.2301722359008418</v>
+        <v>0.230172241636112</v>
       </c>
       <c r="I156" t="n">
-        <v>0.2401875783150603</v>
+        <v>0.2401875839543086</v>
       </c>
       <c r="J156" t="n">
-        <v>0.2484198981423792</v>
+        <v>0.2484199093281491</v>
       </c>
       <c r="K156" t="n">
-        <v>0.2548759366728039</v>
+        <v>0.2548759534615621</v>
       </c>
       <c r="L156" t="n">
-        <v>0.2614291329999514</v>
+        <v>0.2614291555919035</v>
       </c>
       <c r="M156" t="n">
-        <v>0.2742813721856892</v>
+        <v>0.2742814009141393</v>
       </c>
       <c r="N156" t="n">
-        <v>0.2889421473294418</v>
+        <v>0.2889421767746008</v>
       </c>
       <c r="O156" t="n">
-        <v>0.2990993880680869</v>
+        <v>0.2990994305844481</v>
       </c>
       <c r="P156" t="n">
-        <v>0.3099565850430179</v>
+        <v>0.3099566354668936</v>
       </c>
       <c r="Q156" t="n">
-        <v>0.3225327533322326</v>
+        <v>0.3225328125339176</v>
       </c>
       <c r="R156" t="n">
-        <v>0.3315875540125746</v>
+        <v>0.3315876230051655</v>
       </c>
       <c r="S156" t="n">
-        <v>0.3433757568358665</v>
+        <v>0.3433758440373106</v>
       </c>
       <c r="T156" t="n">
-        <v>0.3582060026970821</v>
+        <v>0.3582061025321238</v>
       </c>
       <c r="U156" t="n">
-        <v>0.3776733944745143</v>
+        <v>0.3776735083718618</v>
       </c>
       <c r="V156" t="n">
-        <v>0.4055762255388573</v>
+        <v>0.4055763636520583</v>
       </c>
     </row>
     <row r="157">
@@ -12324,10 +12324,10 @@
         <v>1.153401197706168</v>
       </c>
       <c r="K157" t="n">
-        <v>1.138533185519046</v>
+        <v>1.138534094213434</v>
       </c>
       <c r="L157" t="n">
-        <v>1.13316989848749</v>
+        <v>1.133170783513731</v>
       </c>
       <c r="M157" t="n">
         <v>1.165283268029504</v>
@@ -12339,25 +12339,25 @@
         <v>1.225650315580431</v>
       </c>
       <c r="P157" t="n">
-        <v>1.244809139069748</v>
+        <v>1.24481000569372</v>
       </c>
       <c r="Q157" t="n">
-        <v>1.263644737445783</v>
+        <v>1.26364561974371</v>
       </c>
       <c r="R157" t="n">
-        <v>1.262577269360129</v>
+        <v>1.262578174948879</v>
       </c>
       <c r="S157" t="n">
-        <v>1.268008204943928</v>
+        <v>1.268009140726766</v>
       </c>
       <c r="T157" t="n">
         <v>1.281952058057704</v>
       </c>
       <c r="U157" t="n">
-        <v>1.30851436349076</v>
+        <v>1.308515378470851</v>
       </c>
       <c r="V157" t="n">
-        <v>1.360221022703685</v>
+        <v>1.360222087155158</v>
       </c>
     </row>
     <row r="158">
@@ -12388,7 +12388,7 @@
         <v>0.2996323842520027</v>
       </c>
       <c r="G158" t="n">
-        <v>0.2924451469936739</v>
+        <v>0.2924451916977397</v>
       </c>
       <c r="H158" t="n">
         <v>0.29200164645053</v>
@@ -12397,7 +12397,7 @@
         <v>0.292301265780079</v>
       </c>
       <c r="J158" t="n">
-        <v>0.2960490804001661</v>
+        <v>0.2960491249879056</v>
       </c>
       <c r="K158" t="n">
         <v>0.3020466531925057</v>
@@ -12406,34 +12406,34 @@
         <v>0.3101072021936661</v>
       </c>
       <c r="M158" t="n">
-        <v>0.3248575114541313</v>
+        <v>0.3248575585033457</v>
       </c>
       <c r="N158" t="n">
-        <v>0.3399684176456729</v>
+        <v>0.3399684660255049</v>
       </c>
       <c r="O158" t="n">
-        <v>0.3484521221782516</v>
+        <v>0.3484521720566979</v>
       </c>
       <c r="P158" t="n">
-        <v>0.3559305523899495</v>
+        <v>0.3559306039563831</v>
       </c>
       <c r="Q158" t="n">
-        <v>0.3628624426385365</v>
+        <v>0.3628624961099543</v>
       </c>
       <c r="R158" t="n">
-        <v>0.365720475586102</v>
+        <v>0.3657205311789974</v>
       </c>
       <c r="S158" t="n">
-        <v>0.3729443377896691</v>
+        <v>0.3729443957017643</v>
       </c>
       <c r="T158" t="n">
-        <v>0.3849411978002054</v>
+        <v>0.384941258234121</v>
       </c>
       <c r="U158" t="n">
-        <v>0.4021119320178044</v>
+        <v>0.4021120583975553</v>
       </c>
       <c r="V158" t="n">
-        <v>0.4272394540984009</v>
+        <v>0.4272395203196633</v>
       </c>
     </row>
     <row r="159">
@@ -12473,7 +12473,7 @@
         <v>1.814738156660705</v>
       </c>
       <c r="J159" t="n">
-        <v>1.843391859498305</v>
+        <v>1.843394290659963</v>
       </c>
       <c r="K159" t="n">
         <v>1.883150291640592</v>
@@ -12485,22 +12485,22 @@
         <v>2.00813616428558</v>
       </c>
       <c r="N159" t="n">
-        <v>2.078662726561928</v>
+        <v>2.078665088735033</v>
       </c>
       <c r="O159" t="n">
-        <v>2.11435222473704</v>
+        <v>2.114354614742991</v>
       </c>
       <c r="P159" t="n">
-        <v>2.157252168827371</v>
+        <v>2.157254605712058</v>
       </c>
       <c r="Q159" t="n">
-        <v>2.2032133927274</v>
+        <v>2.203215898101428</v>
       </c>
       <c r="R159" t="n">
-        <v>2.206347638480934</v>
+        <v>2.206350237841491</v>
       </c>
       <c r="S159" t="n">
-        <v>2.208455187235606</v>
+        <v>2.208457907694819</v>
       </c>
       <c r="T159" t="n">
         <v>2.218386576741486</v>
@@ -12509,7 +12509,7 @@
         <v>2.249584656731004</v>
       </c>
       <c r="V159" t="n">
-        <v>2.32695129847944</v>
+        <v>2.326954552406116</v>
       </c>
     </row>
     <row r="160">
@@ -12540,52 +12540,52 @@
         <v>0.07838578815674294</v>
       </c>
       <c r="G160" t="n">
-        <v>0.08644885466729628</v>
+        <v>0.08644883006003433</v>
       </c>
       <c r="H160" t="n">
-        <v>0.09578567477242303</v>
+        <v>0.09578565230345154</v>
       </c>
       <c r="I160" t="n">
-        <v>0.1030565377827293</v>
+        <v>0.1030565170824727</v>
       </c>
       <c r="J160" t="n">
-        <v>0.1078429693585012</v>
+        <v>0.1078429310465708</v>
       </c>
       <c r="K160" t="n">
-        <v>0.1106795515480643</v>
+        <v>0.1106795159701943</v>
       </c>
       <c r="L160" t="n">
-        <v>0.1123525440564704</v>
+        <v>0.1123525108573555</v>
       </c>
       <c r="M160" t="n">
-        <v>0.1167729074839008</v>
+        <v>0.1167728762809588</v>
       </c>
       <c r="N160" t="n">
-        <v>0.1226803226950763</v>
+        <v>0.1226802783899272</v>
       </c>
       <c r="O160" t="n">
-        <v>0.1277300951869858</v>
+        <v>0.1277300389639615</v>
       </c>
       <c r="P160" t="n">
-        <v>0.1338513516236003</v>
+        <v>0.133851284468853</v>
       </c>
       <c r="Q160" t="n">
-        <v>0.1412350186197752</v>
+        <v>0.1412349542404958</v>
       </c>
       <c r="R160" t="n">
-        <v>0.147188181203844</v>
+        <v>0.1471881069160228</v>
       </c>
       <c r="S160" t="n">
-        <v>0.154325759021794</v>
+        <v>0.1543256873982274</v>
       </c>
       <c r="T160" t="n">
-        <v>0.1629148802531684</v>
+        <v>0.1629147995352029</v>
       </c>
       <c r="U160" t="n">
-        <v>0.1737720001534791</v>
+        <v>0.1737719220754653</v>
       </c>
       <c r="V160" t="n">
-        <v>0.1889529368804073</v>
+        <v>0.1889528504507307</v>
       </c>
     </row>
     <row r="161">
@@ -12692,10 +12692,10 @@
         <v>4.064435289928029</v>
       </c>
       <c r="G162" t="n">
-        <v>2.875680168495454</v>
+        <v>2.875682262126837</v>
       </c>
       <c r="H162" t="n">
-        <v>2.276089208064835</v>
+        <v>2.276091223064492</v>
       </c>
       <c r="I162" t="n">
         <v>1.970327945041769</v>
@@ -12704,10 +12704,10 @@
         <v>1.828057003399949</v>
       </c>
       <c r="K162" t="n">
-        <v>1.770540793951416</v>
+        <v>1.770542661720813</v>
       </c>
       <c r="L162" t="n">
-        <v>1.760821243117108</v>
+        <v>1.760823087778198</v>
       </c>
       <c r="M162" t="n">
         <v>1.822509933495545</v>
@@ -12716,7 +12716,7 @@
         <v>1.930641584601529</v>
       </c>
       <c r="O162" t="n">
-        <v>2.036849168703162</v>
+        <v>2.036851017261841</v>
       </c>
       <c r="P162" t="n">
         <v>2.139696996990235</v>
@@ -12725,10 +12725,10 @@
         <v>2.2035988642834</v>
       </c>
       <c r="R162" t="n">
-        <v>2.190069913263426</v>
+        <v>2.190071883206042</v>
       </c>
       <c r="S162" t="n">
-        <v>2.186562094481078</v>
+        <v>2.186564128431783</v>
       </c>
       <c r="T162" t="n">
         <v>2.179611435512339</v>
@@ -12737,7 +12737,7 @@
         <v>2.174324170083497</v>
       </c>
       <c r="V162" t="n">
-        <v>2.166103514482531</v>
+        <v>2.166105808381448</v>
       </c>
     </row>
     <row r="163">
@@ -12838,58 +12838,58 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>0.1898361286633232</v>
+        <v>0.1898360609086979</v>
       </c>
       <c r="F164" t="n">
-        <v>0.248284704564065</v>
+        <v>0.248284639264254</v>
       </c>
       <c r="G164" t="n">
-        <v>0.3071390445519896</v>
+        <v>0.3071388534674832</v>
       </c>
       <c r="H164" t="n">
-        <v>0.3621197146772338</v>
+        <v>0.3621194633579647</v>
       </c>
       <c r="I164" t="n">
-        <v>0.4042675653163385</v>
+        <v>0.4042672528801926</v>
       </c>
       <c r="J164" t="n">
-        <v>0.4333265344045609</v>
+        <v>0.4333262215704149</v>
       </c>
       <c r="K164" t="n">
-        <v>0.4498192029300595</v>
+        <v>0.4498188248253471</v>
       </c>
       <c r="L164" t="n">
-        <v>0.4525359955691864</v>
+        <v>0.4525355483994197</v>
       </c>
       <c r="M164" t="n">
-        <v>0.4603363015300469</v>
+        <v>0.4603358455191391</v>
       </c>
       <c r="N164" t="n">
-        <v>0.4735782939393575</v>
+        <v>0.4735777591492559</v>
       </c>
       <c r="O164" t="n">
-        <v>0.4886717125853542</v>
+        <v>0.488671092015961</v>
       </c>
       <c r="P164" t="n">
-        <v>0.5098762362443037</v>
+        <v>0.5098755217554705</v>
       </c>
       <c r="Q164" t="n">
-        <v>0.5297653380082837</v>
+        <v>0.5297645201893474</v>
       </c>
       <c r="R164" t="n">
-        <v>0.5360064413488028</v>
+        <v>0.53600558767607</v>
       </c>
       <c r="S164" t="n">
-        <v>0.5468446670869612</v>
+        <v>0.5468437745695834</v>
       </c>
       <c r="T164" t="n">
-        <v>0.557982554743534</v>
+        <v>0.5579815359432732</v>
       </c>
       <c r="U164" t="n">
-        <v>0.5706365284145432</v>
+        <v>0.5706354622027935</v>
       </c>
       <c r="V164" t="n">
-        <v>0.5833814690282603</v>
+        <v>0.5833803531975987</v>
       </c>
     </row>
     <row r="165">
@@ -12920,52 +12920,52 @@
         <v>0.4943597498757082</v>
       </c>
       <c r="G165" t="n">
-        <v>0.4712626088150441</v>
+        <v>0.4712624787954254</v>
       </c>
       <c r="H165" t="n">
-        <v>0.4500796639868687</v>
+        <v>0.4500794190364902</v>
       </c>
       <c r="I165" t="n">
-        <v>0.434087149788159</v>
+        <v>0.4340869165215944</v>
       </c>
       <c r="J165" t="n">
-        <v>0.4234109291852995</v>
+        <v>0.423410705389845</v>
       </c>
       <c r="K165" t="n">
-        <v>0.4130161162839391</v>
+        <v>0.413015793497752</v>
       </c>
       <c r="L165" t="n">
-        <v>0.4043066752129154</v>
+        <v>0.4043062607488661</v>
       </c>
       <c r="M165" t="n">
-        <v>0.4087967070527832</v>
+        <v>0.4087963058163732</v>
       </c>
       <c r="N165" t="n">
-        <v>0.4237660184989718</v>
+        <v>0.4237655298321332</v>
       </c>
       <c r="O165" t="n">
-        <v>0.4418741385210377</v>
+        <v>0.4418736605854138</v>
       </c>
       <c r="P165" t="n">
-        <v>0.4661635442905122</v>
+        <v>0.4661629820379033</v>
       </c>
       <c r="Q165" t="n">
-        <v>0.488396138377557</v>
+        <v>0.4883954960584547</v>
       </c>
       <c r="R165" t="n">
-        <v>0.4963239268334876</v>
+        <v>0.4963232097607935</v>
       </c>
       <c r="S165" t="n">
-        <v>0.5077280661460726</v>
+        <v>0.5077273661876326</v>
       </c>
       <c r="T165" t="n">
-        <v>0.5187528387262017</v>
+        <v>0.5187519849739606</v>
       </c>
       <c r="U165" t="n">
-        <v>0.5305343810575902</v>
+        <v>0.5305335473247598</v>
       </c>
       <c r="V165" t="n">
-        <v>0.5416561662613022</v>
+        <v>0.541655270877899</v>
       </c>
     </row>
     <row r="166">
@@ -12990,58 +12990,58 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>0.1325822594154901</v>
+        <v>0.1325821981722149</v>
       </c>
       <c r="F166" t="n">
-        <v>0.1471052762336636</v>
+        <v>0.1471051555342588</v>
       </c>
       <c r="G166" t="n">
-        <v>0.1534597218462209</v>
+        <v>0.1534595416325596</v>
       </c>
       <c r="H166" t="n">
-        <v>0.1587855595641739</v>
+        <v>0.1587853182830192</v>
       </c>
       <c r="I166" t="n">
-        <v>0.1613187414154794</v>
+        <v>0.1613184355536995</v>
       </c>
       <c r="J166" t="n">
-        <v>0.1627763714503946</v>
+        <v>0.1627760173516706</v>
       </c>
       <c r="K166" t="n">
-        <v>0.1629480892833062</v>
+        <v>0.1629476812949807</v>
       </c>
       <c r="L166" t="n">
-        <v>0.1624186722098964</v>
+        <v>0.1624182042324769</v>
       </c>
       <c r="M166" t="n">
-        <v>0.1652545112427605</v>
+        <v>0.1652539759563299</v>
       </c>
       <c r="N166" t="n">
-        <v>0.1705467991564919</v>
+        <v>0.1705461881312502</v>
       </c>
       <c r="O166" t="n">
-        <v>0.1758506603593716</v>
+        <v>0.1758499647018206</v>
       </c>
       <c r="P166" t="n">
-        <v>0.1823632826113473</v>
+        <v>0.1823624930299017</v>
       </c>
       <c r="Q166" t="n">
-        <v>0.1873315547943765</v>
+        <v>0.1873306615871026</v>
       </c>
       <c r="R166" t="n">
-        <v>0.1868011795311483</v>
+        <v>0.1868002333178785</v>
       </c>
       <c r="S166" t="n">
-        <v>0.1876366890686882</v>
+        <v>0.1876356225109613</v>
       </c>
       <c r="T166" t="n">
-        <v>0.1882720068502004</v>
+        <v>0.1882708783726944</v>
       </c>
       <c r="U166" t="n">
-        <v>0.1889927451173783</v>
+        <v>0.1889915167621713</v>
       </c>
       <c r="V166" t="n">
-        <v>0.1894930540840888</v>
+        <v>0.1894917202365255</v>
       </c>
     </row>
     <row r="167">
@@ -13066,58 +13066,58 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>2.723825153814914</v>
+        <v>2.723825382888772</v>
       </c>
       <c r="F167" t="n">
-        <v>2.756901147553716</v>
+        <v>2.756901546638768</v>
       </c>
       <c r="G167" t="n">
-        <v>2.684601105891109</v>
+        <v>2.684601600111636</v>
       </c>
       <c r="H167" t="n">
-        <v>2.691639019502857</v>
+        <v>2.691639631104269</v>
       </c>
       <c r="I167" t="n">
-        <v>2.721348692643342</v>
+        <v>2.72134944269685</v>
       </c>
       <c r="J167" t="n">
-        <v>2.761218108667101</v>
+        <v>2.761219019801555</v>
       </c>
       <c r="K167" t="n">
-        <v>2.785754810872814</v>
+        <v>2.785755856894983</v>
       </c>
       <c r="L167" t="n">
-        <v>2.794705910957574</v>
+        <v>2.794707120355503</v>
       </c>
       <c r="M167" t="n">
-        <v>2.857473782143741</v>
+        <v>2.857475184201612</v>
       </c>
       <c r="N167" t="n">
-        <v>2.960612389389387</v>
+        <v>2.960613990538211</v>
       </c>
       <c r="O167" t="n">
-        <v>3.061701416187435</v>
+        <v>3.061703251571579</v>
       </c>
       <c r="P167" t="n">
-        <v>3.188186493388721</v>
+        <v>3.188188602938933</v>
       </c>
       <c r="Q167" t="n">
-        <v>3.295033656587525</v>
+        <v>3.295036060444863</v>
       </c>
       <c r="R167" t="n">
-        <v>3.309776918242137</v>
+        <v>3.309779588866616</v>
       </c>
       <c r="S167" t="n">
-        <v>3.34789422105866</v>
+        <v>3.347897184952989</v>
       </c>
       <c r="T167" t="n">
-        <v>3.377148514818104</v>
+        <v>3.377151830113049</v>
       </c>
       <c r="U167" t="n">
-        <v>3.399365723838696</v>
+        <v>3.399369368266191</v>
       </c>
       <c r="V167" t="n">
-        <v>3.408715111346733</v>
+        <v>3.408719119355464</v>
       </c>
     </row>
     <row r="168">
@@ -13142,7 +13142,7 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>5.492316822135267</v>
+        <v>5.492320531127719</v>
       </c>
       <c r="F168" t="n">
         <v>6.093893443479351</v>
@@ -13151,49 +13151,49 @@
         <v>6.357082021114346</v>
       </c>
       <c r="H168" t="n">
-        <v>6.577656839272516</v>
+        <v>6.577659997852166</v>
       </c>
       <c r="I168" t="n">
-        <v>6.682544026907276</v>
+        <v>6.682547067964591</v>
       </c>
       <c r="J168" t="n">
-        <v>6.742878099216157</v>
+        <v>6.74288104488911</v>
       </c>
       <c r="K168" t="n">
-        <v>6.749940431249049</v>
+        <v>6.749943302032228</v>
       </c>
       <c r="L168" t="n">
-        <v>6.7279599743223</v>
+        <v>6.727965605396822</v>
       </c>
       <c r="M168" t="n">
-        <v>6.845380064987364</v>
+        <v>6.845385619462883</v>
       </c>
       <c r="N168" t="n">
-        <v>7.064546521430107</v>
+        <v>7.06455203116305</v>
       </c>
       <c r="O168" t="n">
-        <v>7.284190152090835</v>
+        <v>7.28419565863812</v>
       </c>
       <c r="P168" t="n">
-        <v>7.553896422424902</v>
+        <v>7.553904736566426</v>
       </c>
       <c r="Q168" t="n">
-        <v>7.759624618806127</v>
+        <v>7.759633042980137</v>
       </c>
       <c r="R168" t="n">
-        <v>7.737584023268862</v>
+        <v>7.737592611677946</v>
       </c>
       <c r="S168" t="n">
-        <v>7.77211358652415</v>
+        <v>7.772125329160783</v>
       </c>
       <c r="T168" t="n">
-        <v>7.798348678276766</v>
+        <v>7.798360784741013</v>
       </c>
       <c r="U168" t="n">
-        <v>7.828117845561348</v>
+        <v>7.828130390330492</v>
       </c>
       <c r="V168" t="n">
-        <v>7.848751020408163</v>
+        <v>7.848764081632653</v>
       </c>
     </row>
     <row r="169">
@@ -13218,58 +13218,58 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>0.3651929588859741</v>
+        <v>0.3651929098531467</v>
       </c>
       <c r="F169" t="n">
-        <v>0.385345495311863</v>
+        <v>0.3853453969718426</v>
       </c>
       <c r="G169" t="n">
-        <v>0.3815202273065775</v>
+        <v>0.3815200881860483</v>
       </c>
       <c r="H169" t="n">
-        <v>0.38830689621638</v>
+        <v>0.3883067002090494</v>
       </c>
       <c r="I169" t="n">
-        <v>0.4013951088320623</v>
+        <v>0.401394870457385</v>
       </c>
       <c r="J169" t="n">
-        <v>0.4184468021973405</v>
+        <v>0.4184465264794235</v>
       </c>
       <c r="K169" t="n">
-        <v>0.4344956118281528</v>
+        <v>0.4344952969540562</v>
       </c>
       <c r="L169" t="n">
-        <v>0.4460140001491236</v>
+        <v>0.4460136448153896</v>
       </c>
       <c r="M169" t="n">
-        <v>0.4666818770953917</v>
+        <v>0.4666814794852495</v>
       </c>
       <c r="N169" t="n">
-        <v>0.4973841674163155</v>
+        <v>0.4973837149966595</v>
       </c>
       <c r="O169" t="n">
-        <v>0.5322312657519466</v>
+        <v>0.5322307624948668</v>
       </c>
       <c r="P169" t="n">
-        <v>0.5742232589462131</v>
+        <v>0.5742227082167864</v>
       </c>
       <c r="Q169" t="n">
-        <v>0.614428031631422</v>
+        <v>0.6144274316353289</v>
       </c>
       <c r="R169" t="n">
-        <v>0.6375837004167961</v>
+        <v>0.6375830719004717</v>
       </c>
       <c r="S169" t="n">
-        <v>0.6651556204227371</v>
+        <v>0.6651549601674963</v>
       </c>
       <c r="T169" t="n">
-        <v>0.6915881001813267</v>
+        <v>0.6915874134653626</v>
       </c>
       <c r="U169" t="n">
-        <v>0.7176601124757653</v>
+        <v>0.7176594038186378</v>
       </c>
       <c r="V169" t="n">
-        <v>0.7425996660792505</v>
+        <v>0.7425989392964663</v>
       </c>
     </row>
     <row r="170">
@@ -13297,55 +13297,55 @@
         <v>0.2590319918199536</v>
       </c>
       <c r="F170" t="n">
-        <v>0.3415025442028061</v>
+        <v>0.3415024247454483</v>
       </c>
       <c r="G170" t="n">
-        <v>0.4006539094774664</v>
+        <v>0.4006536918992813</v>
       </c>
       <c r="H170" t="n">
-        <v>0.4376968497068626</v>
+        <v>0.4376966503275304</v>
       </c>
       <c r="I170" t="n">
-        <v>0.453543724612953</v>
+        <v>0.4535434474743901</v>
       </c>
       <c r="J170" t="n">
-        <v>0.4573290961086924</v>
+        <v>0.4573287503068991</v>
       </c>
       <c r="K170" t="n">
-        <v>0.4562497605510383</v>
+        <v>0.4562493529783375</v>
       </c>
       <c r="L170" t="n">
-        <v>0.4551810993446458</v>
+        <v>0.455180635759993</v>
       </c>
       <c r="M170" t="n">
-        <v>0.4670891448961049</v>
+        <v>0.4670886290496709</v>
       </c>
       <c r="N170" t="n">
-        <v>0.488152023029511</v>
+        <v>0.4881514578881374</v>
       </c>
       <c r="O170" t="n">
-        <v>0.5095615265608547</v>
+        <v>0.5095608459234242</v>
       </c>
       <c r="P170" t="n">
-        <v>0.5349666582062346</v>
+        <v>0.5349659330263405</v>
       </c>
       <c r="Q170" t="n">
-        <v>0.5561103777937256</v>
+        <v>0.5561096088784089</v>
       </c>
       <c r="R170" t="n">
-        <v>0.5624679529247057</v>
+        <v>0.5624670779192369</v>
       </c>
       <c r="S170" t="n">
-        <v>0.5741889829824591</v>
+        <v>0.5741880659573375</v>
       </c>
       <c r="T170" t="n">
-        <v>0.5861637230309984</v>
+        <v>0.5861627036073805</v>
       </c>
       <c r="U170" t="n">
-        <v>0.5985387406453286</v>
+        <v>0.5985376795404236</v>
       </c>
       <c r="V170" t="n">
-        <v>0.6108445345446519</v>
+        <v>0.6108433727941261</v>
       </c>
     </row>
     <row r="171">
@@ -13370,58 +13370,58 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>0.4346818742989938</v>
+        <v>0.434681833953312</v>
       </c>
       <c r="F171" t="n">
-        <v>0.4822943237762416</v>
+        <v>0.4822942440629543</v>
       </c>
       <c r="G171" t="n">
-        <v>0.5031254918830622</v>
+        <v>0.5031253332910421</v>
       </c>
       <c r="H171" t="n">
-        <v>0.5205843306708915</v>
+        <v>0.5205840918273719</v>
       </c>
       <c r="I171" t="n">
-        <v>0.5288871026718621</v>
+        <v>0.5288868207788945</v>
       </c>
       <c r="J171" t="n">
-        <v>0.5336637088537001</v>
+        <v>0.5336633805573896</v>
       </c>
       <c r="K171" t="n">
-        <v>0.5342243129420771</v>
+        <v>0.5342239760612483</v>
       </c>
       <c r="L171" t="n">
-        <v>0.5324863106827797</v>
+        <v>0.5324858755833052</v>
       </c>
       <c r="M171" t="n">
-        <v>0.5417810466018582</v>
+        <v>0.5417805941346677</v>
       </c>
       <c r="N171" t="n">
-        <v>0.5591290008138854</v>
+        <v>0.5591284329869589</v>
       </c>
       <c r="O171" t="n">
-        <v>0.5765145939666867</v>
+        <v>0.5765139972391405</v>
       </c>
       <c r="P171" t="n">
-        <v>0.5978627745930507</v>
+        <v>0.5978620397906023</v>
       </c>
       <c r="Q171" t="n">
-        <v>0.6141476527551708</v>
+        <v>0.6141468734204555</v>
       </c>
       <c r="R171" t="n">
-        <v>0.6124054655151735</v>
+        <v>0.6124046343122924</v>
       </c>
       <c r="S171" t="n">
-        <v>0.6151408800450286</v>
+        <v>0.6151399886409654</v>
       </c>
       <c r="T171" t="n">
-        <v>0.6172198724611432</v>
+        <v>0.6172189119748627</v>
       </c>
       <c r="U171" t="n">
-        <v>0.6195785913738054</v>
+        <v>0.6195775530561767</v>
       </c>
       <c r="V171" t="n">
-        <v>0.6212144993846934</v>
+        <v>0.6212133748035999</v>
       </c>
     </row>
     <row r="172">
@@ -13446,58 +13446,58 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>3.29442506403818</v>
+        <v>3.294425245436605</v>
       </c>
       <c r="F172" t="n">
-        <v>3.444024180630512</v>
+        <v>3.44402453202166</v>
       </c>
       <c r="G172" t="n">
-        <v>3.290543724106085</v>
+        <v>3.290544237174362</v>
       </c>
       <c r="H172" t="n">
-        <v>3.149583020797533</v>
+        <v>3.149583522527246</v>
       </c>
       <c r="I172" t="n">
-        <v>3.044036425087699</v>
+        <v>3.044037246390048</v>
       </c>
       <c r="J172" t="n">
-        <v>2.973121893723029</v>
+        <v>2.973122704814346</v>
       </c>
       <c r="K172" t="n">
-        <v>2.913273489148748</v>
+        <v>2.913274456405651</v>
       </c>
       <c r="L172" t="n">
-        <v>2.857171715673503</v>
+        <v>2.857172521777712</v>
       </c>
       <c r="M172" t="n">
-        <v>2.86947772219688</v>
+        <v>2.869478856942031</v>
       </c>
       <c r="N172" t="n">
-        <v>2.928413368126204</v>
+        <v>2.928414678180956</v>
       </c>
       <c r="O172" t="n">
-        <v>2.993073816381693</v>
+        <v>2.993075150167624</v>
       </c>
       <c r="P172" t="n">
-        <v>3.086070717710549</v>
+        <v>3.086072256687711</v>
       </c>
       <c r="Q172" t="n">
-        <v>3.161979471182465</v>
+        <v>3.161981237558092</v>
       </c>
       <c r="R172" t="n">
-        <v>3.1545426070055</v>
+        <v>3.154544444128051</v>
       </c>
       <c r="S172" t="n">
-        <v>3.173755816189194</v>
+        <v>3.173757931167084</v>
       </c>
       <c r="T172" t="n">
-        <v>3.187179563456529</v>
+        <v>3.187181789500801</v>
       </c>
       <c r="U172" t="n">
-        <v>3.19780322139948</v>
+        <v>3.197805790981623</v>
       </c>
       <c r="V172" t="n">
-        <v>3.20321212776272</v>
+        <v>3.203214864088956</v>
       </c>
     </row>
     <row r="173">
@@ -13534,10 +13534,10 @@
         <v>0.2665532003054678</v>
       </c>
       <c r="I173" t="n">
-        <v>0.2738276075245076</v>
+        <v>0.2738265035767906</v>
       </c>
       <c r="J173" t="n">
-        <v>0.2765128119266945</v>
+        <v>0.2765117910153678</v>
       </c>
       <c r="K173" t="n">
         <v>0.2783253223040184</v>
@@ -13549,31 +13549,31 @@
         <v>0.2941479048787243</v>
       </c>
       <c r="N173" t="n">
-        <v>0.3130391535439042</v>
+        <v>0.3130383552414146</v>
       </c>
       <c r="O173" t="n">
-        <v>0.3330982931825425</v>
+        <v>0.3330975325348053</v>
       </c>
       <c r="P173" t="n">
-        <v>0.3566180488664995</v>
+        <v>0.3566173202552471</v>
       </c>
       <c r="Q173" t="n">
-        <v>0.378151714006769</v>
+        <v>0.3781510131391649</v>
       </c>
       <c r="R173" t="n">
-        <v>0.3896572272316214</v>
+        <v>0.3896558744571147</v>
       </c>
       <c r="S173" t="n">
-        <v>0.4050216316338812</v>
+        <v>0.4050203212214092</v>
       </c>
       <c r="T173" t="n">
-        <v>0.4205417689081217</v>
+        <v>0.4205404965228893</v>
       </c>
       <c r="U173" t="n">
-        <v>0.4365887168526512</v>
+        <v>0.4365874785384673</v>
       </c>
       <c r="V173" t="n">
-        <v>0.4525501647019077</v>
+        <v>0.4525489580945256</v>
       </c>
     </row>
     <row r="174">
@@ -13598,58 +13598,58 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>1.29758968757616</v>
+        <v>1.297589743958397</v>
       </c>
       <c r="F174" t="n">
-        <v>1.365746171085875</v>
+        <v>1.365746254107313</v>
       </c>
       <c r="G174" t="n">
-        <v>1.362540379966555</v>
+        <v>1.362540475775305</v>
       </c>
       <c r="H174" t="n">
-        <v>1.383349043662704</v>
+        <v>1.383349152857</v>
       </c>
       <c r="I174" t="n">
-        <v>1.411032888505203</v>
+        <v>1.411033025622912</v>
       </c>
       <c r="J174" t="n">
-        <v>1.467609246109567</v>
+        <v>1.467609440523607</v>
       </c>
       <c r="K174" t="n">
-        <v>1.534412915333704</v>
+        <v>1.534413170593148</v>
       </c>
       <c r="L174" t="n">
-        <v>1.591458983316286</v>
+        <v>1.591459304235492</v>
       </c>
       <c r="M174" t="n">
-        <v>1.660887092088772</v>
+        <v>1.660887499537847</v>
       </c>
       <c r="N174" t="n">
-        <v>1.735289237092136</v>
+        <v>1.735289707618225</v>
       </c>
       <c r="O174" t="n">
-        <v>1.795895395243235</v>
+        <v>1.795895952771456</v>
       </c>
       <c r="P174" t="n">
-        <v>1.862164253452227</v>
+        <v>1.862164891086102</v>
       </c>
       <c r="Q174" t="n">
-        <v>1.914429461895426</v>
+        <v>1.914430171959252</v>
       </c>
       <c r="R174" t="n">
-        <v>1.915958824486175</v>
+        <v>1.915959635803511</v>
       </c>
       <c r="S174" t="n">
-        <v>1.935178886137366</v>
+        <v>1.935179791499269</v>
       </c>
       <c r="T174" t="n">
-        <v>1.952093685945019</v>
+        <v>1.952094719511066</v>
       </c>
       <c r="U174" t="n">
-        <v>1.968185639410206</v>
+        <v>1.968186794241774</v>
       </c>
       <c r="V174" t="n">
-        <v>1.979670369876162</v>
+        <v>1.979671635872982</v>
       </c>
     </row>
     <row r="175">
@@ -13689,43 +13689,43 @@
         <v>0.4739287033991562</v>
       </c>
       <c r="J175" t="n">
-        <v>0.5240156880381033</v>
+        <v>0.5240152234551223</v>
       </c>
       <c r="K175" t="n">
-        <v>0.5641202564527575</v>
+        <v>0.5641198281463283</v>
       </c>
       <c r="L175" t="n">
         <v>0.5954251104012847</v>
       </c>
       <c r="M175" t="n">
-        <v>0.6405218556432715</v>
+        <v>0.6405214848913011</v>
       </c>
       <c r="N175" t="n">
-        <v>0.6964637936023551</v>
+        <v>0.6964634441264991</v>
       </c>
       <c r="O175" t="n">
-        <v>0.7509801965941472</v>
+        <v>0.75097986633923</v>
       </c>
       <c r="P175" t="n">
-        <v>0.8116348346328943</v>
+        <v>0.8116345221507645</v>
       </c>
       <c r="Q175" t="n">
-        <v>0.8660517984378623</v>
+        <v>0.8660515029701888</v>
       </c>
       <c r="R175" t="n">
-        <v>0.8943202392300703</v>
+        <v>0.8943199601729708</v>
       </c>
       <c r="S175" t="n">
-        <v>0.9292971550887849</v>
+        <v>0.9292966278628368</v>
       </c>
       <c r="T175" t="n">
-        <v>0.9646975134414638</v>
+        <v>0.9646970145933041</v>
       </c>
       <c r="U175" t="n">
-        <v>0.9999021954522302</v>
+        <v>0.9999019592093612</v>
       </c>
       <c r="V175" t="n">
-        <v>1.031762385649795</v>
+        <v>1.031761938084227</v>
       </c>
     </row>
     <row r="176">
@@ -13826,58 +13826,58 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>0.7178431979049175</v>
+        <v>0.7178431870365028</v>
       </c>
       <c r="F177" t="n">
-        <v>1.019031169710418</v>
+        <v>1.019031190664352</v>
       </c>
       <c r="G177" t="n">
-        <v>1.280643496723023</v>
+        <v>1.280643578500498</v>
       </c>
       <c r="H177" t="n">
-        <v>1.464688779065253</v>
+        <v>1.464688940405832</v>
       </c>
       <c r="I177" t="n">
-        <v>1.545015385888752</v>
+        <v>1.545015596318049</v>
       </c>
       <c r="J177" t="n">
-        <v>1.561595734404186</v>
+        <v>1.56159598518469</v>
       </c>
       <c r="K177" t="n">
-        <v>1.544292125721666</v>
+        <v>1.544292409279093</v>
       </c>
       <c r="L177" t="n">
-        <v>1.537435421541234</v>
+        <v>1.537435731010307</v>
       </c>
       <c r="M177" t="n">
-        <v>1.583263850474639</v>
+        <v>1.583264231821765</v>
       </c>
       <c r="N177" t="n">
-        <v>1.664726902850407</v>
+        <v>1.664727362955716</v>
       </c>
       <c r="O177" t="n">
-        <v>1.752736784950131</v>
+        <v>1.75273734354165</v>
       </c>
       <c r="P177" t="n">
-        <v>1.85164129539379</v>
+        <v>1.851641963671244</v>
       </c>
       <c r="Q177" t="n">
-        <v>1.926244378809778</v>
+        <v>1.92624515804688</v>
       </c>
       <c r="R177" t="n">
-        <v>1.934941309059108</v>
+        <v>1.934942187865337</v>
       </c>
       <c r="S177" t="n">
-        <v>1.952979453540078</v>
+        <v>1.952980445670781</v>
       </c>
       <c r="T177" t="n">
-        <v>1.969286777522049</v>
+        <v>1.96928788193056</v>
       </c>
       <c r="U177" t="n">
-        <v>1.989002154883527</v>
+        <v>1.989003399920156</v>
       </c>
       <c r="V177" t="n">
-        <v>2.005759542698307</v>
+        <v>2.005760943575603</v>
       </c>
     </row>
     <row r="178">
@@ -13914,46 +13914,46 @@
         <v>0.2353563317655483</v>
       </c>
       <c r="I178" t="n">
-        <v>0.2377104681081569</v>
+        <v>0.237707960296323</v>
       </c>
       <c r="J178" t="n">
-        <v>0.2387117592708667</v>
+        <v>0.2387094377817708</v>
       </c>
       <c r="K178" t="n">
-        <v>0.238224580829057</v>
+        <v>0.2382224165283318</v>
       </c>
       <c r="L178" t="n">
-        <v>0.2372792290134415</v>
+        <v>0.2372772001014456</v>
       </c>
       <c r="M178" t="n">
-        <v>0.2420679279375847</v>
+        <v>0.242066013827531</v>
       </c>
       <c r="N178" t="n">
-        <v>0.2512270440137327</v>
+        <v>0.2512252275163031</v>
       </c>
       <c r="O178" t="n">
-        <v>0.2605191377645066</v>
+        <v>0.2605174037216029</v>
       </c>
       <c r="P178" t="n">
-        <v>0.2717411561116843</v>
+        <v>0.2717394921628008</v>
       </c>
       <c r="Q178" t="n">
         <v>0.2808087255372072</v>
       </c>
       <c r="R178" t="n">
-        <v>0.2820471436486123</v>
+        <v>0.2820455917476112</v>
       </c>
       <c r="S178" t="n">
-        <v>0.2854847873361676</v>
+        <v>0.2854832803111705</v>
       </c>
       <c r="T178" t="n">
-        <v>0.2886046846233127</v>
+        <v>0.2886032164575509</v>
       </c>
       <c r="U178" t="n">
-        <v>0.2916082231152493</v>
+        <v>0.2916067889176684</v>
       </c>
       <c r="V178" t="n">
-        <v>0.2943043042199391</v>
+        <v>0.2943028995401078</v>
       </c>
     </row>
     <row r="179">
@@ -14020,7 +14020,7 @@
         <v>1.051967890265763</v>
       </c>
       <c r="S179" t="n">
-        <v>1.091601607494816</v>
+        <v>1.091596488084573</v>
       </c>
       <c r="T179" t="n">
         <v>1.127474104705316</v>
